--- a/processed_ruby_restored_xlsx/sc101_数日後：サバゲ～倉庫.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc101_数日後：サバゲ～倉庫.ss.xlsx
@@ -1067,8 +1067,8 @@
       <c r="B40" s="1" t="inlineStr">
         <is>
           <t>And it’s already eight, and I’ve got breakfast to
-make, cleaning, laundry… aaaah！ There’s no way there’s
-enough time！</t>
+make, cleaning, laundry… aaaah！ There’s no way
+there’s enough time！</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1284,8 +1284,8 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>I hurried to hide it not only because of the time, but
-also so she wouldn't notice.</t>
+          <t>I hurried to hide it not only because of the time,
+but also so she wouldn't notice.</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1300,8 +1300,8 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>For that reason too, I'm really glad Miru-chan was the
-one who came to wake me….</t>
+          <t>For that reason too, I'm really glad Miru-chan was
+the one who came to wake me….</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1469,8 +1469,8 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>...But Rin-chan still looks sleepy, collapsed over the
-table... somehow, she's just melting.</t>
+          <t>...But Rin-chan still looks sleepy, collapsed over
+the table... somehow, she's just melting.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,8 +1530,8 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「Oh... no, you don't have to apologize — you're always
-taking care of us！」</t>
+          <t>「Oh... no, you don't have to apologize — you're
+always taking care of us！」</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1729,7 +1729,8 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan says that as she rubs at Rin-chan's temples.</t>
+          <t>Miru-chan says that as she rubs at Rin-chan's
+temples.</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1851,8 +1852,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... Rin-chan, you don't perk up until you've had
-breakfast, right？」</t>
+          <t>「Ufufu... Rin-chan, you don't perk up until you've
+had breakfast, right？」</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1867,8 +1868,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who had been watching the scene with a
-fond smile, teased Rin-chan with a soft laugh.</t>
+          <t>Rurichiyo-chan, who had been watching the scene with
+a fond smile, teased Rin-chan with a soft laugh.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2144,8 +2145,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>「W-well... don't things like that happen sometimes...?
-Right, Nono-chan?」</t>
+          <t>「W-well... don't things like that happen
+sometimes...? Right, Nono-chan?」</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2176,7 +2177,8 @@
       <c r="B112" s="1" t="inlineStr">
         <is>
           <t>「Y-yes！ This is what they call a nocturnal erection —
-a physiological thing that happens to men, basically！」</t>
+a physiological thing that happens to men,
+basically！」</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2281,8 +2283,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>...Everyone was wearing an awkward, unfamiliar sort of
-embarrassed smile.</t>
+          <t>...Everyone was wearing an awkward, unfamiliar sort
+of embarrassed smile.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2315,8 +2317,8 @@
       <c r="B121" s="1" t="inlineStr">
         <is>
           <t>You taught me the right knowledge and cleared up my
-misunderstandings, which is great, but it's not always
-true.</t>
+misunderstandings, which is great, but it's not
+always true.</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2332,8 +2334,8 @@
       <c r="B122" s="1" t="inlineStr">
         <is>
           <t>Starting with sex education, and even sneaking a look
-at erotic books, they’ve probably got certain thoughts
-now that they know more.</t>
+at erotic books, they’ve probably got certain
+thoughts now that they know more.</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2378,7 +2380,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>I couldn't bear it anymore, so I left the living room.</t>
+          <t>I couldn't bear it anymore, so I left the living
+room.</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2468,8 +2471,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>When class ends, Miru-chan immediately starts slacking
-off.</t>
+          <t>When class ends, Miru-chan immediately starts
+slacking off.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2484,9 +2487,9 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Maybe it was because it was a subject I was bad at and
-that made it hard, but even so, that was a blatantly
-obvious attitude.</t>
+          <t>Maybe it was because it was a subject I was bad at
+and that made it hard, but even so, that was a
+blatantly obvious attitude.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2501,9 +2504,9 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Not only that, but I've actually had things on my mind
-about Miru-chan for a long time, so I might as well
-say them now.</t>
+          <t>Not only that, but I've actually had things on my
+mind about Miru-chan for a long time, so I might as
+well say them now.</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2593,8 +2596,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>It's painful to scold her for a smile like that, but I
-opened my mouth because I thought it was for
+          <t>It's painful to scold her for a smile like that, but
+I opened my mouth because I thought it was for
 Miru-chan's own good.</t>
         </is>
       </c>
@@ -2625,8 +2628,8 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>「I think Miru-chan should properly use polite language
-when Nono-chan is the teacher.」</t>
+          <t>「I think Miru-chan should properly use polite
+language when Nono-chan is the teacher.」</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2779,9 +2782,9 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>...It’s probably just more comfortable being on friend
-terms than with a teacher, so I can understand how she
-feels...</t>
+          <t>...It’s probably just more comfortable being on
+friend terms than with a teacher, so I can understand
+how she feels...</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2797,7 +2800,8 @@
       <c r="B152" s="1" t="inlineStr">
         <is>
           <t>Looking over, Nono-chan-sensei is sitting daintily on
-a chair, swinging her legs while doing some paperwork.</t>
+a chair, swinging her legs while doing some
+paperwork.</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2812,7 +2816,8 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>She really doesn't look much like a teacher, though...</t>
+          <t>She really doesn't look much like a teacher,
+though...</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2903,7 +2908,8 @@
       <c r="B159" s="1" t="inlineStr">
         <is>
           <t>「If you could prove that Nono-chan is the teacher,
-you'd feel like you have to use polite speech, right？」</t>
+you'd feel like you have to use polite speech,
+right？」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3421,8 +3427,8 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>This bluntness is so Miru-chan, but her way of putting
-it is so barefaced that I can't say anything.</t>
+          <t>This bluntness is so Miru-chan, but her way of
+putting it is so barefaced that I can't say anything.</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3788,7 +3794,8 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>「Okay. Then Miruku-chan, please hold that over there.」</t>
+          <t>「Okay. Then Miruku-chan, please hold that over
+there.」</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3804,8 +3811,8 @@
       <c r="B218" s="1" t="inlineStr">
         <is>
           <t>Holding both ends of the sheet together, Nono-chan,
-while getting into position to spread it out, calls to
-Miru-chan.</t>
+while getting into position to spread it out, calls
+to Miru-chan.</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -4385,7 +4392,8 @@
       <c r="B256" s="1" t="inlineStr">
         <is>
           <t>But of all times, Miru-chan had her skirt flipped up
-while she was bent over, so of course she was furious.</t>
+while she was bent over, so of course she was
+furious.</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4490,8 +4498,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Since it was said without malice, she probably doesn't
-even know how to snap back.</t>
+          <t>Since it was said without malice, she probably
+doesn't even know how to snap back.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4506,7 +4514,8 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>Instead of retorting, Miru-chan raises a water pistol.</t>
+          <t>Instead of retorting, Miru-chan raises a water
+pistol.</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4581,7 +4590,8 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan also pulls a water pistol out from somewhere.</t>
+          <t>Rin-chan also pulls a water pistol out from
+somewhere.</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -5545,8 +5555,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I’ll go buy Rurichiyo-chan’s and Nono-chan’s by
-after school.」</t>
+          <t>「Okay, I’ll go buy Rurichiyo-chan’s and Nono-chan’s
+by after school.」</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5651,7 +5661,8 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>"...And just like that, my participation was decided."</t>
+          <t>"...And just like that, my participation was
+decided."</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5743,8 +5754,8 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「Ah, I have a little suggestion for Janitor-sensei, so
-let's talk before we go shopping...！」</t>
+          <t>「Ah, I have a little suggestion for Janitor-sensei,
+so let's talk before we go shopping...！」</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5880,9 +5891,9 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who volunteered to be the host, stands in a
-proud, wide-legged pose wearing bloomers and holding a
-water gun in one hand.</t>
+          <t>Nono-chan, who volunteered to be the host, stands in
+a proud, wide-legged pose wearing bloomers and
+holding a water gun in one hand.</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6446,8 +6457,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>「If tearing means you lose, then if I cover it with my
-hand I wouldn't lose, right？」</t>
+          <t>「If tearing means you lose, then if I cover it with
+my hand I wouldn't lose, right？」</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6585,7 +6596,8 @@
       <c r="B400" s="1" t="inlineStr">
         <is>
           <t>「Fouls...? Hitting, kicking and things like that are
-banned, but other than that I think no rules is fine！」</t>
+banned, but other than that I think no rules is
+fine！」</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6811,8 +6823,8 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>They said they'd do it from the afternoon, so everyone
-is already all excited.</t>
+          <t>They said they'd do it from the afternoon, so
+everyone is already all excited.</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6842,8 +6854,8 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'm going to count to ten now. By then, scatter
-out, and on three — start all at once！」</t>
+          <t>「Okay, I'm going to count to ten now. By then,
+scatter out, and on three — start all at once！」</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -7561,8 +7573,8 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>Pushed by Miru-chan's momentum, or was that Rin-chan's
-plan…？</t>
+          <t>Pushed by Miru-chan's momentum, or was that
+Rin-chan's plan…？</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7853,8 +7865,8 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>...It's just girls horsing around with each other, how
-heartwarming.</t>
+          <t>...It's just girls horsing around with each other,
+how heartwarming.</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -8435,8 +8447,9 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>『Rurichiyo~！ I heard from Sacchan at the dagashi shop！
-You're going to settle it with water guns, right~？』</t>
+          <t>『Rurichiyo~！ I heard from Sacchan at the dagashi
+shop！ You're going to settle it with water guns,
+right~？』</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -9033,8 +9046,8 @@
       <c r="B560" s="1" t="inlineStr">
         <is>
           <t>That said, it wasn't really about getting
-Kikuchiyo-baa-chan's present — she was just parched to
-begin with.</t>
+Kikuchiyo-baa-chan's present — she was just parched
+to begin with.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9434,8 +9447,8 @@
       <c r="B586" s="1" t="inlineStr">
         <is>
           <t>While Rurichiyo was floundering... or rather, she was
-cornered because she'd run out of water, so she had no
-other choice.</t>
+cornered because she'd run out of water, so she had
+no other choice.</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9633,9 +9646,9 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>She seemed to instinctively try to shield the poi with
-her hand, but the volume of the spray wouldn't allow
-it.</t>
+          <t>She seemed to instinctively try to shield the poi
+with her hand, but the volume of the spray wouldn't
+allow it.</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -10108,8 +10121,8 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>…Before I knew it, Rin-chan and Nono-chan were nowhere
-to be seen.</t>
+          <t>…Before I knew it, Rin-chan and Nono-chan were
+nowhere to be seen.</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -10277,8 +10290,8 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「……Okay, I get it！ Now we're safe no matter where they
-come from！」</t>
+          <t>「……Okay, I get it！ Now we're safe no matter where
+they come from！」</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10642,8 +10655,8 @@
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
-          <t>「Wow... Nono-chan, amazing...！ How are you not getting
-hit！？」</t>
+          <t>「Wow... Nono-chan, amazing...！ How are you not
+getting hit！？」</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -11425,8 +11438,8 @@
       <c r="B716" s="1" t="inlineStr">
         <is>
           <t>Nono-chan calculated the firing line logically,
-Rin-chan provided the secret weapon, and together they
-launched this operation...！</t>
+Rin-chan provided the secret weapon, and together
+they launched this operation...！</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11805,8 +11818,8 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>Everyone who lost is cheering me on... but they're all
-standing behind Rurichiyo-chan.</t>
+          <t>Everyone who lost is cheering me on... but they're
+all standing behind Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -11986,8 +11999,8 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>I can understand that, but I still can't really accept
-it.</t>
+          <t>I can understand that, but I still can't really
+accept it.</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12032,8 +12045,9 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, brandishing an overwhelmingly powerful
-weapon, looked at me with a rare, wicked grin.</t>
+          <t>Rurichiyo-chan, brandishing an overwhelmingly
+powerful weapon, looked at me with a rare, wicked
+grin.</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -12093,8 +12107,8 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>But I still had a chance... my water gun was full, and
-since my hands are bigger than everyone else's, I
+          <t>But I still had a chance... my water gun was full,
+and since my hands are bigger than everyone else's, I
 could guard the poi more easily.</t>
         </is>
       </c>
@@ -12826,8 +12840,8 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>Miru, doused in a huge amount of water, wiped her face
-with her hand and grimaced.</t>
+          <t>Miru, doused in a huge amount of water, wiped her
+face with her hand and grimaced.</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -13037,8 +13051,8 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>When Rurichiyo-chan, who caused this situation, looked
-down and apologized, Rin-chan and Nono-chan
+          <t>When Rurichiyo-chan, who caused this situation,
+looked down and apologized, Rin-chan and Nono-chan
 immediately jumped in to back her up.</t>
         </is>
       </c>
@@ -13175,8 +13189,8 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>It's great that the girls are having fun. I watch them
-fondly.</t>
+          <t>It's great that the girls are having fun. I watch
+them fondly.</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -13237,8 +13251,8 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>Their cheeks reddened from exertion and excitement are
-the best.</t>
+          <t>Their cheeks reddened from exertion and excitement
+are the best.</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -13329,8 +13343,8 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>Getting doused with a ton of water from the squirt gun
-would tear a thin poi right away anyway.</t>
+          <t>Getting doused with a ton of water from the squirt
+gun would tear a thin poi right away anyway.</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13741,9 +13755,9 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan and everyone else focused their attacks
-on my face, and the second round ended in a quick
-retirement...</t>
+          <t>Rurichiyo-chan and everyone else focused their
+attacks on my face, and the second round ended in a
+quick retirement...</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -13774,8 +13788,8 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>There were a lot of poi, so we kept up the pretense of
-it being a contest, but the appearance of the huge
+          <t>There were a lot of poi, so we kept up the pretense
+of it being a contest, but the appearance of the huge
 water gun seemed to set everyone's hearts on fire.</t>
         </is>
       </c>
@@ -13929,7 +13943,8 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, we should make sure you don't catch a cold...」</t>
+          <t>「Oh my, we should make sure you don't catch a
+cold...」</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -14250,8 +14265,8 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan and Rurichiyo-chan both offer to help at the
-same time.</t>
+          <t>Nono-chan and Rurichiyo-chan both offer to help at
+the same time.</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -14893,9 +14908,9 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>I said that, paying attention to where Miru-chan stood
-holding one end, and then started walking with a
-heave-ho.</t>
+          <t>I said that, paying attention to where Miru-chan
+stood holding one end, and then started walking with
+a heave-ho.</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -15685,8 +15700,8 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>I say I’m taking it easy on purpose, but really put my
-weight into trying to open the door.</t>
+          <t>I say I’m taking it easy on purpose, but really put
+my weight into trying to open the door.</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -15791,8 +15806,8 @@
       </c>
       <c r="B1002" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... uh... maybe something's come loose or gone out
-of alignment...？」</t>
+          <t>「Mmm... uh... maybe something's come loose or gone
+out of alignment...？」</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -15854,8 +15869,8 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>But Miru-chan, worried the door won’t open, looks half
-on the verge of tears.</t>
+          <t>But Miru-chan, worried the door won’t open, looks
+half on the verge of tears.</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -16280,8 +16295,8 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>When I pulled back a little and looked at her straight
-on, Miru-chan's eyes darted about.</t>
+          <t>When I pulled back a little and looked at her
+straight on, Miru-chan's eyes darted about.</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -16312,7 +16327,8 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>Alright, as I thought, hugging you was the right move！</t>
+          <t>Alright, as I thought, hugging you was the right
+move！</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -16327,8 +16343,9 @@
       </c>
       <c r="B1037" s="1" t="inlineStr">
         <is>
-          <t>I had become confident in my own judgment, but thought
-it might be a bit of a problem in a different sense.</t>
+          <t>I had become confident in my own judgment, but
+thought it might be a bit of a problem in a different
+sense.</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -16343,8 +16360,9 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's face is right up close, and the warmth and
-scent hit me straight in the head with a little jolt！</t>
+          <t>Miru-chan's face is right up close, and the warmth
+and scent hit me straight in the head with a little
+jolt！</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -17548,8 +17566,8 @@
       </c>
       <c r="B1117" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan started to say something, but I deliberately
-slid my tongue between.</t>
+          <t>Miru-chan started to say something, but I
+deliberately slid my tongue between.</t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -17626,8 +17644,8 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>But why does it feel like all the strength has drained
-from her body...？</t>
+          <t>But why does it feel like all the strength has
+drained from her body...？</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17763,8 +17781,8 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>The tongues' mucous membranes tangled and the sound of
-saliva popping rang out.</t>
+          <t>The tongues' mucous membranes tangled and the sound
+of saliva popping rang out.</t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -17886,8 +17904,8 @@
       </c>
       <c r="B1139" s="1" t="inlineStr">
         <is>
-          <t>But on the other hand, she doesn't seem to dislike our
-tongues tangling.</t>
+          <t>But on the other hand, she doesn't seem to dislike
+our tongues tangling.</t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -18071,7 +18089,8 @@
       </c>
       <c r="B1151" s="1" t="inlineStr">
         <is>
-          <t>This was the third time she'd called me during a kiss.</t>
+          <t>This was the third time she'd called me during a
+kiss.</t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -18789,8 +18808,8 @@
       <c r="B1198" s="1" t="inlineStr">
         <is>
           <t>「Ah... no！ Rin-chan, you saved me！ Actually the door
-wouldn't open！ I was just trying to figure out what to
-do about it, right, Miru-chan！？」</t>
+wouldn't open！ I was just trying to figure out what
+to do about it, right, Miru-chan！？」</t>
         </is>
       </c>
       <c r="C1198" t="n">
@@ -19004,8 +19023,8 @@
       <c r="B1212" s="1" t="inlineStr">
         <is>
           <t>「From the outside you can push the handle to unlock
-it, and from the inside you can just lift the latch to
-open it easily.」</t>
+it, and from the inside you can just lift the latch
+to open it easily.」</t>
         </is>
       </c>
       <c r="C1212" t="n">
@@ -19477,8 +19496,8 @@
       </c>
       <c r="B1243" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan raised her hand and let out a breath as if to
-psych herself up.</t>
+          <t>Rin-chan raised her hand and let out a breath as if
+to psych herself up.</t>
         </is>
       </c>
       <c r="C1243" t="n">
@@ -19660,9 +19679,9 @@
       </c>
       <c r="B1255" s="1" t="inlineStr">
         <is>
-          <t>Because Rin-chan opened the storage door for me, I was
-able to carry things in smoothly without putting them
-down.</t>
+          <t>Because Rin-chan opened the storage door for me, I
+was able to carry things in smoothly without putting
+them down.</t>
         </is>
       </c>
       <c r="C1255" t="n">
@@ -20087,9 +20106,9 @@
       </c>
       <c r="B1283" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... with this, the vibration from closing the door
-could shift the tripod legs and they might get jammed
-in the rail.」</t>
+          <t>「Hmm... with this, the vibration from closing the
+door could shift the tripod legs and they might get
+jammed in the rail.」</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -20365,8 +20384,8 @@
       </c>
       <c r="B1301" s="1" t="inlineStr">
         <is>
-          <t>I'll think about where to put it later — for now, this
-should do.</t>
+          <t>I'll think about where to put it later — for now,
+this should do.</t>
         </is>
       </c>
       <c r="C1301" t="n">
@@ -20504,7 +20523,8 @@
       </c>
       <c r="B1310" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan pretends to be expressionless and looks away.</t>
+          <t>Rin-chan pretends to be expressionless and looks
+away.</t>
         </is>
       </c>
       <c r="C1310" t="n">
@@ -20733,8 +20753,8 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is a bit curious, but she's shy, so she hates
-being poked at like that.</t>
+          <t>Rin-chan is a bit curious, but she's shy, so she
+hates being poked at like that.</t>
         </is>
       </c>
       <c r="C1325" t="n">
@@ -20870,7 +20890,8 @@
       </c>
       <c r="B1334" s="1" t="inlineStr">
         <is>
-          <t>Seizing the chance, I said that and urged Rin-chan on.</t>
+          <t>Seizing the chance, I said that and urged Rin-chan
+on.</t>
         </is>
       </c>
       <c r="C1334" t="n">
@@ -21006,7 +21027,8 @@
       </c>
       <c r="B1343" s="1" t="inlineStr">
         <is>
-          <t>Huh, isn’t this situation... actually really great...？</t>
+          <t>Huh, isn’t this situation... actually really
+great...？</t>
         </is>
       </c>
       <c r="C1343" t="n">
@@ -21521,8 +21543,8 @@
       </c>
       <c r="B1377" s="1" t="inlineStr">
         <is>
-          <t>When I casually change the subject, Rin-chan hurriedly
-nods.</t>
+          <t>When I casually change the subject, Rin-chan
+hurriedly nods.</t>
         </is>
       </c>
       <c r="C1377" t="n">
@@ -21628,8 +21650,8 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>「I mean, like, in the empty gym storeroom, secretly, a
-smooch.」</t>
+          <t>「I mean, like, in the empty gym storeroom, secretly,
+a smooch.」</t>
         </is>
       </c>
       <c r="C1384" t="n">
@@ -21929,7 +21951,8 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>I gently leaned in and pressed her lips to Rin-chan's.</t>
+          <t>I gently leaned in and pressed her lips to
+Rin-chan's.</t>
         </is>
       </c>
       <c r="C1404" t="n">
@@ -21990,8 +22013,8 @@
       </c>
       <c r="B1408" s="1" t="inlineStr">
         <is>
-          <t>A hesitant sigh is basically saying, what should we do
-now?</t>
+          <t>A hesitant sigh is basically saying, what should we
+do now?</t>
         </is>
       </c>
       <c r="C1408" t="n">
@@ -22051,8 +22074,8 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>When I licked her lips with my tongue, Rin-chan jumped
-and opened her eyes wide.</t>
+          <t>When I licked her lips with my tongue, Rin-chan
+jumped and opened her eyes wide.</t>
         </is>
       </c>
       <c r="C1412" t="n">
@@ -22817,8 +22840,8 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>When I opened my eyes halfway and looked, Rin-chan was
-bright red but wearing a determined expression.</t>
+          <t>When I opened my eyes halfway and looked, Rin-chan
+was bright red but wearing a determined expression.</t>
         </is>
       </c>
       <c r="C1462" t="n">
@@ -23230,9 +23253,9 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>But I was holding down the water gun's turret part and
-Rin-chan was grabbing the tripod, making for a pretty
-mismatched, awkward scene.</t>
+          <t>But I was holding down the water gun's turret part
+and Rin-chan was grabbing the tripod, making for a
+pretty mismatched, awkward scene.</t>
         </is>
       </c>
       <c r="C1489" t="n">
@@ -23539,8 +23562,8 @@
       </c>
       <c r="B1509" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan said that, she obediently turned on her
-heel.</t>
+          <t>When Miru-chan said that, she obediently turned on
+her heel.</t>
         </is>
       </c>
       <c r="C1509" t="n">
@@ -23738,8 +23761,8 @@
       <c r="B1522" s="1" t="inlineStr">
         <is>
           <t>Because we're close she blurts things out without
-embarrassment, but when she concedes something she can
-do it properly.</t>
+embarrassment, but when she concedes something she
+can do it properly.</t>
         </is>
       </c>
       <c r="C1522" t="n">
@@ -23771,8 +23794,8 @@
       <c r="B1524" s="1" t="inlineStr">
         <is>
           <t>I thought this before the kiss too, but Rin-chan is
-basically shy, so I shouldn't make her aware of things
-that would embarrass her.</t>
+basically shy, so I shouldn't make her aware of
+things that would embarrass her.</t>
         </is>
       </c>
       <c r="C1524" t="n">
@@ -24182,8 +24205,8 @@
       </c>
       <c r="B1551" s="1" t="inlineStr">
         <is>
-          <t>Given Rurichiyo-chan's personality, she probably finds
-helping out very rewarding.</t>
+          <t>Given Rurichiyo-chan's personality, she probably
+finds helping out very rewarding.</t>
         </is>
       </c>
       <c r="C1551" t="n">
@@ -24409,8 +24432,8 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>As Rurichiyo-chan says, we'll need to tidy up a bit to
-fit everything neatly.</t>
+          <t>As Rurichiyo-chan says, we'll need to tidy up a bit
+to fit everything neatly.</t>
         </is>
       </c>
       <c r="C1566" t="n">
@@ -24441,8 +24464,8 @@
       <c r="B1568" s="1" t="inlineStr">
         <is>
           <t>「At a glance, what comes to mind is stacking the
-scoreboards, moving the vaulting horse, and putting it
-in that space...」</t>
+scoreboards, moving the vaulting horse, and putting
+it in that space...」</t>
         </is>
       </c>
       <c r="C1568" t="n">
@@ -24472,8 +24495,8 @@
       </c>
       <c r="B1570" s="1" t="inlineStr">
         <is>
-          <t>「Ah… if that's the case, I'll have to move the mat and
-the ball holder first, what a hassle…」</t>
+          <t>「Ah… if that's the case, I'll have to move the mat
+and the ball holder first, what a hassle…」</t>
         </is>
       </c>
       <c r="C1570" t="n">
@@ -24503,7 +24526,8 @@
       </c>
       <c r="B1572" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, calling it a hassle? You must do it properly！」</t>
+          <t>「Oh my, calling it a hassle? You must do it
+properly！」</t>
         </is>
       </c>
       <c r="C1572" t="n">
@@ -24550,8 +24574,8 @@
       </c>
       <c r="B1575" s="1" t="inlineStr">
         <is>
-          <t>「Nah, it's a hassle, so I figured there must be a more
-efficient way...」</t>
+          <t>「Nah, it's a hassle, so I figured there must be a
+more efficient way...」</t>
         </is>
       </c>
       <c r="C1575" t="n">
@@ -24674,8 +24698,8 @@
       </c>
       <c r="B1583" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who was about to argue further, gave a
-small sneeze.</t>
+          <t>Rurichiyo-chan, who was about to argue further, gave
+a small sneeze.</t>
         </is>
       </c>
       <c r="C1583" t="n">
@@ -24827,8 +24851,8 @@
       <c r="B1593" s="1" t="inlineStr">
         <is>
           <t>She seems willing to accept my help, but feels bad
-that my assistance is only half-done... something like
-that.</t>
+that my assistance is only half-done... something
+like that.</t>
         </is>
       </c>
       <c r="C1593" t="n">
@@ -25119,8 +25143,8 @@
       </c>
       <c r="B1612" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it, it was just the two of us inside the
-gym storage room with the door shut.</t>
+          <t>Before I knew it, it was just the two of us inside
+the gym storage room with the door shut.</t>
         </is>
       </c>
       <c r="C1612" t="n">
@@ -25320,8 +25344,8 @@
       </c>
       <c r="B1625" s="1" t="inlineStr">
         <is>
-          <t>As I found myself staring, Rurichiyo-chan fidgeted and
-blushed.</t>
+          <t>As I found myself staring, Rurichiyo-chan fidgeted
+and blushed.</t>
         </is>
       </c>
       <c r="C1625" t="n">
@@ -25457,7 +25481,8 @@
       </c>
       <c r="B1634" s="1" t="inlineStr">
         <is>
-          <t>She continues, as if trying to hide her embarrassment.</t>
+          <t>She continues, as if trying to hide her
+embarrassment.</t>
         </is>
       </c>
       <c r="C1634" t="n">
@@ -26187,8 +26212,8 @@
       </c>
       <c r="B1682" s="1" t="inlineStr">
         <is>
-          <t>She made a reluctant face when asking for a kiss, so I
-think she wasn't really ready.</t>
+          <t>She made a reluctant face when asking for a kiss, so
+I think she wasn't really ready.</t>
         </is>
       </c>
       <c r="C1682" t="n">
@@ -26482,8 +26507,8 @@
       </c>
       <c r="B1701" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan exhaled awkwardly through her half-open
-mouth.</t>
+          <t>Rurichiyo-chan exhaled awkwardly through her
+half-open mouth.</t>
         </is>
       </c>
       <c r="C1701" t="n">
@@ -26514,7 +26539,8 @@
       <c r="B1703" s="1" t="inlineStr">
         <is>
           <t>I leaned in for a smooch because of the vibe, and
-since another chance came up I went for a tongue kiss.</t>
+since another chance came up I went for a tongue
+kiss.</t>
         </is>
       </c>
       <c r="C1703" t="n">
@@ -26666,8 +26692,8 @@
       </c>
       <c r="B1713" s="1" t="inlineStr">
         <is>
-          <t>She was clumsy, but I felt like she was doing her best
-to respond to me.</t>
+          <t>She was clumsy, but I felt like she was doing her
+best to respond to me.</t>
         </is>
       </c>
       <c r="C1713" t="n">
@@ -26835,7 +26861,8 @@
       </c>
       <c r="B1724" s="1" t="inlineStr">
         <is>
-          <t>「Chuba！ Kuchu...chuchu！ N'ff...chuba, kuchu, chuu...！」</t>
+          <t>「Chuba！ Kuchu...chuchu！ N'ff...chuba, kuchu,
+chuu...！」</t>
         </is>
       </c>
       <c r="C1724" t="n">
@@ -26941,8 +26968,8 @@
       </c>
       <c r="B1731" s="1" t="inlineStr">
         <is>
-          <t>「Fwah...ah, ah...Oji-sama...fuu, nnn...naah, nfu！ Fuu,
-fuuu...！」</t>
+          <t>「Fwah...ah, ah...Oji-sama...fuu, nnn...naah, nfu！
+Fuu, fuuu...！」</t>
         </is>
       </c>
       <c r="C1731" t="n">
@@ -26958,8 +26985,8 @@
       <c r="B1732" s="1" t="inlineStr">
         <is>
           <t>Sticking my tongue out in return, Rurichiyo-chan did
-the same, and our tongues slid together, wetly tangled
-around each other.</t>
+the same, and our tongues slid together, wetly
+tangled around each other.</t>
         </is>
       </c>
       <c r="C1732" t="n">
@@ -26990,7 +27017,8 @@
       <c r="B1734" s="1" t="inlineStr">
         <is>
           <t>The hesitation I felt just moments ago has vanished
-somewhere, and in its place a pure happiness wells up.</t>
+somewhere, and in its place a pure happiness wells
+up.</t>
         </is>
       </c>
       <c r="C1734" t="n">
@@ -27050,8 +27078,8 @@
       </c>
       <c r="B1738" s="1" t="inlineStr">
         <is>
-          <t>「Smack！ Ssmack...~...slrrp！ Nnngh... nhaa！ Fuh, faa...
-nn！」</t>
+          <t>「Smack！ Ssmack...~...slrrp！ Nnngh... nhaa！ Fuh,
+faa... nn！」</t>
         </is>
       </c>
       <c r="C1738" t="n">
@@ -27553,8 +27581,8 @@
       </c>
       <c r="B1771" s="1" t="inlineStr">
         <is>
-          <t>「Ahh！ I started to lose track partway through... I got
-way too carried away...！」</t>
+          <t>「Ahh！ I started to lose track partway through... I
+got way too carried away...！」</t>
         </is>
       </c>
       <c r="C1771" t="n">
@@ -27569,8 +27597,8 @@
       </c>
       <c r="B1772" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan gets excited in a way that's both happy
-and embarrassed.</t>
+          <t>Rurichiyo-chan gets excited in a way that's both
+happy and embarrassed.</t>
         </is>
       </c>
       <c r="C1772" t="n">
@@ -27786,9 +27814,9 @@
       </c>
       <c r="B1786" s="1" t="inlineStr">
         <is>
-          <t>By the time I called out in a panic it was already too
-late — Rurichiyo-chan had run straight into the closed
-door.</t>
+          <t>By the time I called out in a panic it was already
+too late — Rurichiyo-chan had run straight into the
+closed door.</t>
         </is>
       </c>
       <c r="C1786" t="n">
@@ -28051,8 +28079,8 @@
       </c>
       <c r="B1803" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan is also turning her face away from me a
-little.</t>
+          <t>Rurichiyo-chan is also turning her face away from me
+a little.</t>
         </is>
       </c>
       <c r="C1803" t="n">
@@ -28512,8 +28540,8 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah！ I'm sorry！ My eyes just wandered to something
-else…」</t>
+          <t>「Ah, ah！ I'm sorry！ My eyes just wandered to
+something else…」</t>
         </is>
       </c>
       <c r="C1833" t="n">
@@ -28558,9 +28586,9 @@
       </c>
       <c r="B1836" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan skipped grades and kept moving ahead, so she
-probably doesn't know about the usual PE stuff kids
-do.</t>
+          <t>Nono-chan skipped grades and kept moving ahead, so
+she probably doesn't know about the usual PE stuff
+kids do.</t>
         </is>
       </c>
       <c r="C1836" t="n">
@@ -28669,8 +28697,8 @@
       </c>
       <c r="B1843" s="1" t="inlineStr">
         <is>
-          <t>「Hmm… that water gun is big, so there's no space where
-it fits neatly…」</t>
+          <t>「Hmm… that water gun is big, so there's no space
+where it fits neatly…」</t>
         </is>
       </c>
       <c r="C1843" t="n">
@@ -29328,8 +29356,8 @@
       </c>
       <c r="B1886" s="1" t="inlineStr">
         <is>
-          <t>Well, even at a sports festival, we probably won't use
-half of the stuff here, though.</t>
+          <t>Well, even at a sports festival, we probably won't
+use half of the stuff here, though.</t>
         </is>
       </c>
       <c r="C1886" t="n">
@@ -29547,9 +29575,9 @@
       </c>
       <c r="B1900" s="1" t="inlineStr">
         <is>
-          <t>I accidentally blurted it out even though it was about
-nighttime mat exercises... What do I do, how do I
-follow this up?</t>
+          <t>I accidentally blurted it out even though it was
+about nighttime mat exercises... What do I do, how do
+I follow this up?</t>
         </is>
       </c>
       <c r="C1900" t="n">
@@ -29852,8 +29880,8 @@
       </c>
       <c r="B1920" s="1" t="inlineStr">
         <is>
-          <t>「No, don't you think if you do a straddle forward roll
-over me you'll understand somehow？」</t>
+          <t>「No, don't you think if you do a straddle forward
+roll over me you'll understand somehow？」</t>
         </is>
       </c>
       <c r="C1920" t="n">
@@ -30019,7 +30047,8 @@
       </c>
       <c r="B1931" s="1" t="inlineStr">
         <is>
-          <t>「Y- I think Janitor-sensei is pervy！ That's not okay！」</t>
+          <t>「Y- I think Janitor-sensei is pervy！ That's not
+okay！」</t>
         </is>
       </c>
       <c r="C1931" t="n">
@@ -30094,8 +30123,8 @@
       </c>
       <c r="B1936" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, her puffed-up cheeks flushed red, continued
-to let out muffled groans.</t>
+          <t>Nono-chan, her puffed-up cheeks flushed red,
+continued to let out muffled groans.</t>
         </is>
       </c>
       <c r="C1936" t="n">
@@ -30279,8 +30308,8 @@
       </c>
       <c r="B1948" s="1" t="inlineStr">
         <is>
-          <t>They keep arguing about it like they know what they're
-talking about, but I'm getting dizzy….</t>
+          <t>They keep arguing about it like they know what
+they're talking about, but I'm getting dizzy….</t>
         </is>
       </c>
       <c r="C1948" t="n">
@@ -30528,8 +30557,8 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>I can feel her warmth perfectly... and there's a scent
-too...！</t>
+          <t>I can feel her warmth perfectly... and there's a
+scent too...！</t>
         </is>
       </c>
       <c r="C1964" t="n">
@@ -30559,7 +30588,8 @@
       </c>
       <c r="B1966" s="1" t="inlineStr">
         <is>
-          <t>「Um... Janitor-sensei？ A-are you reflecting on it...？」</t>
+          <t>「Um... Janitor-sensei？ A-are you reflecting on
+it...？」</t>
         </is>
       </c>
       <c r="C1966" t="n">
@@ -31213,8 +31243,8 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>But despite being flustered, she doesn't show any sign
-of disliking it.</t>
+          <t>But despite being flustered, she doesn't show any
+sign of disliking it.</t>
         </is>
       </c>
       <c r="C2009" t="n">
@@ -32239,7 +32269,8 @@
       </c>
       <c r="B2076" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan’s tongue began to move the same way as mine.</t>
+          <t>Nono-chan’s tongue began to move the same way as
+mine.</t>
         </is>
       </c>
       <c r="C2076" t="n">
@@ -32284,8 +32315,8 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>「fah, nng... chu, chu！ chub！ fuu！ chuchu, chuk！ chuba！
-fuh！」</t>
+          <t>「fah, nng... chu, chu！ chub！ fuu！ chuchu, chuk！
+chuba！ fuh！」</t>
         </is>
       </c>
       <c r="C2079" t="n">
@@ -32467,8 +32498,8 @@
       <c r="B2091" s="1" t="inlineStr">
         <is>
           <t>...Once we both pulled our faces away, it became
-suddenly embarrassing and we both turned our heads the
-other way.</t>
+suddenly embarrassing and we both turned our heads
+the other way.</t>
         </is>
       </c>
       <c r="C2091" t="n">
@@ -32697,8 +32728,8 @@
       </c>
       <c r="B2106" s="1" t="inlineStr">
         <is>
-          <t>...Looking back at her, Nono had tears gleaming in her
-eyes and her mouth was all slack and melted.</t>
+          <t>...Looking back at her, Nono had tears gleaming in
+her eyes and her mouth was all slack and melted.</t>
         </is>
       </c>
       <c r="C2106" t="n">
@@ -33036,9 +33067,9 @@
       </c>
       <c r="B2128" s="1" t="inlineStr">
         <is>
-          <t>Well, Nono-chan is a teacher too, so it doesn't matter
-who helped, but she sounded like she was about to
-blurt the truth out without being pressed.</t>
+          <t>Well, Nono-chan is a teacher too, so it doesn't
+matter who helped, but she sounded like she was about
+to blurt the truth out without being pressed.</t>
         </is>
       </c>
       <c r="C2128" t="n">

--- a/processed_ruby_restored_xlsx/sc101_数日後：サバゲ～倉庫.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc101_数日後：サバゲ～倉庫.ss.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaah...！」</t>
+          <t>「Yaaawn...！」</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Man, I'm kinda tired.</t>
+          <t>I'm kind of tired.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -544,7 +544,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>...It's been a few days since Nono-chan came.</t>
+          <t>...It's already been several days since Nono-chan
+came.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -623,8 +624,8 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Girls getting along with each other like that is a
-good thing, I think.</t>
+          <t>I think it's nice when girls get along with each
+other.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -639,8 +640,8 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>As for me... I'm kinda getting pushed around by
-everyone... I guess？</t>
+          <t>As for me... I'm kinda being bossed around by
+everyone... I guess?</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -656,7 +657,7 @@
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>They probably don't mean anything by it, but since
-they unconsciously tempt me, it drives me crazy.</t>
+they unintentionally tempt me, it's unbearable.</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -671,7 +672,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Really... I can't take it...！！</t>
+          <t>Really... I can't resist it...!!</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -716,7 +717,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>「Haaayooon！」</t>
+          <t>"Morniiiing~!"</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -746,7 +747,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>「Fugoa！？」</t>
+          <t>「Guh!?」</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -853,8 +854,8 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>…Then Miru-chan's face filled my view, and I got a
-shock in my chest.</t>
+          <t>…Then Miru-chan's face suddenly filled my vision, and
+my heart skipped a beat.</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -869,8 +870,9 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Also, being right up close to the scent of a little
-kid is way too intense for a groggy morning brain…</t>
+          <t>Besides, having the scent of a little girl right up
+close is far too intense for my groggy, morning-dazed
+head…</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,8 +947,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>I scratched my head, as if to cover up the sudden,
-private embarrassment.</t>
+          <t>I scratched my head as if to hide my slight
+embarrassment.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1066,9 +1068,9 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>And it’s already eight, and I’ve got breakfast to
-make, cleaning, laundry… aaaah！ There’s no way
-there’s enough time！</t>
+          <t>But it's already 8 o'clock!? I've got breakfast to
+make, cleaning, laundry... Aaah! No matter how you
+look at it, there's not enough time!</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1083,7 +1085,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>I snapped wide awake！！</t>
+          <t>I was suddenly wide awake!!</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1113,8 +1115,8 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah... I’ll be right there too, so Miru-chan, go
-on ahead to everyone！」</t>
+          <t>Ah... I'll be there in a moment too, so Miru-chan, go
+on ahead and join everyone!</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1159,8 +1161,8 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Because I was flustered, Miru-chan simply nodded and
-left the room.</t>
+          <t>Probably because I was flustered, Miru-chan nodded
+obediently and left the room.</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>「………………haah」</t>
+          <t>「………………Haa!」</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1205,7 +1207,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>When I was alone, I first let out a sigh.</t>
+          <t>Once I was alone, I sighed.</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1220,8 +1222,8 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Having a girl when I wake up… no, being woken up by a
-girl is nice….</t>
+          <t>There's a girl when I wake up… no, being woken up by
+a girl is nice too…</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1236,9 +1238,8 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>And if she's that close right after waking up,
-something's already at its peak first thing in the
-morning！</t>
+          <t>Besides, if she's that close right after waking up,
+something's already at its peak!</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1268,8 +1269,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>But the problem is the time, and of course the
-'morning wood.'</t>
+          <t>But the problem was the time, and, as usual, my
+morning wood.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1284,8 +1285,8 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>I hurried to hide it not only because of the time,
-but also so she wouldn't notice.</t>
+          <t>The reason I acted flustered wasn't just because of
+the time, but also to keep her from noticing this.</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1331,7 +1332,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>「Sorry everyone, we all overslept！」</t>
+          <t>「Sorry, everyone, we all overslept！」</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1346,9 +1347,8 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>I quickly changed, pressed my morning erection down
-with my pants, and apologized as I entered the living
-room.</t>
+          <t>I quickly changed, held my morning erection down with
+my pants, and entered the living room, apologizing.</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama, good day.」</t>
+          <t>「Good morning, Oji-sama.」</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>「Niini, mornin'… kuu…」</t>
+          <t>「Niini, mornin'… mmm…」</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1469,8 +1469,9 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>...But Rin-chan still looks sleepy, collapsed over
-the table... somehow, she's just melting.</t>
+          <t>...But Rin-chan still looks sleepy, slumped over the
+table... I don't know how to put it — she's just so
+relaxed.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1561,8 +1562,9 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>「That’s right. Oji-sama is always doing my best, so
-it’s understandable if I oversleep once in a while.」</t>
+          <t>「That’s right. Oji-sama is always doing his best, so
+it’s understandable if he oversleeps once in a
+while.」</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1637,8 +1639,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Encouraged by everyone's kind words, my chest grows
-warm.</t>
+          <t>Encouraged by everyone's kind words, I felt a warmth
+in my chest.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1668,7 +1670,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>「Niini... is dinner not ready yet？」</t>
+          <t>「Niini... is breakfast ready yet?」</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1714,7 +1716,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>「Rin？ Get up already~？」</t>
+          <t>「Rin? Come on, wake up already~」</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1729,8 +1731,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan says that as she rubs at Rin-chan's
-temples.</t>
+          <t>Saying that, Miru-chan rubs Rin-chan's temples.</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1790,8 +1791,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>「W-well, now, Miru-chan. It's my fault for
-oversleeping, so it's fine...」</t>
+          <t>W-well, Miru-chan. It's my fault for oversleeping, so
+it's okay...</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1821,8 +1822,9 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>It's nice to be treated kindly after screwing up, but
-being deliberately hurried actually sharpens me up.</t>
+          <t>It's nice to be treated kindly after making a
+mistake, but being deliberately rushed actually helps
+me pull myself together.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1852,8 +1854,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... Rin-chan, you don't perk up until you've
-had breakfast, right？」</t>
+          <t>「Ufufu... Rin-chan doesn't get energetic until she's
+had breakfast, does she?」</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1884,8 +1886,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Then Rin-chan suddenly sat up and lifted her face,
-staring intently at me.</t>
+          <t>Then Rin-chan sat bolt upright, looked up at me, and
+stared intently.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1915,7 +1917,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>「Niini is…」</t>
+          <t>「Niini...」</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1930,7 +1932,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>However, my words die off there.</t>
+          <t>However, my words trailed off there.</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1960,7 +1962,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Nn？」</t>
+          <t>「Hm?」</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1975,9 +1977,9 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Tilting my head a little to prompt her casually,
-Rin-chan opened and closed her mouth as she continued
-speaking.</t>
+          <t>I tilted my head slightly to prompt her casually, and
+Rin-chan, opening and closing her mouth, picked up
+where she left off.</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2007,8 +2009,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>「Niini's... already energetic this morning,
-huh........」</t>
+          <t>「Niini... you're so energetic this morning........」</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2023,7 +2024,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>And then she buried her face into the table again...</t>
+          <t>Then she slumped forward onto the table again.</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2145,8 +2146,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>「W-well... don't things like that happen
-sometimes...? Right, Nono-chan?」</t>
+          <t>「W-well... that sort of thing can happen sometimes,
+right, Nono-chan?」</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2176,9 +2177,8 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes！ This is what they call a nocturnal erection —
-a physiological thing that happens to men,
-basically！」</t>
+          <t>"Y-yes! This is what's called a nocturnal erection —
+a physiological phenomenon that happens to men!"</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2283,8 +2283,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>...Everyone was wearing an awkward, unfamiliar sort
-of embarrassed smile.</t>
+          <t>...Everyone was wearing a strange, wry smile they had
+never shown before.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2316,9 +2316,9 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>You taught me the right knowledge and cleared up my
-misunderstandings, which is great, but it's not
-always true.</t>
+          <t>It's good that she taught me the right information
+and cleared up my misunderstanding, but that's not
+always correct.</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaah... it's over...」</t>
+          <t>「Phew... it's over...」</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2487,9 +2487,9 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Maybe it was because it was a subject I was bad at
-and that made it hard, but even so, that was a
-blatantly obvious attitude.</t>
+          <t>She might have found it hard because it was a subject
+she was bad at, but even so, that was a pretty
+blatant attitude.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, suddenly in contrast, breaks into a smile.</t>
+          <t>In contrast, Miru-chan breaks into a smile.</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>「I’m saying ‘desu’ and ‘masu,’ too, okay？」</t>
+          <t>"I do use 'desu' and 'masu,' you know?"</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2689,8 +2689,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>「Uhh... but Nono-chan is our sensei, and she's a
-friend too...」</t>
+          <t>「Hmm... but Nono-chan is our sensei, and she's also a
+friend...」</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2720,8 +2720,9 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>「Well, I get how you feel, but you have to know the
-difference between a teacher and a friend, okay？」</t>
+          <t>「Well, I get how you feel, but you need to be able to
+tell the difference between a sensei and a friend,
+okay?」</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2751,7 +2752,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>「U... muuu...」</t>
+          <t>「Ugh... mmm...」</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2782,9 +2783,9 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>...It’s probably just more comfortable being on
-friend terms than with a teacher, so I can understand
-how she feels...</t>
+          <t>...She's probably more comfortable being friends than
+with a sensei, so I can't say I don't understand how
+she feels...</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2799,9 +2800,8 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Looking over, Nono-chan-sensei is sitting daintily on
-a chair, swinging her legs while doing some
-paperwork.</t>
+          <t>When I glanced over, Nono-chan-sensei was perched on
+a chair, swinging her legs as she did some writing.</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>She really doesn't look much like a teacher,
+          <t>Nono-chan-sensei doesn't really look like a teacher,
 though...</t>
         </is>
       </c>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>「Then... shall we try a little experiment?」</t>
+          <t>Then... shall we give it a try?</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2907,9 +2907,9 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>「If you could prove that Nono-chan is the teacher,
-you'd feel like you have to use polite speech,
-right？」</t>
+          <t>If it were proven that Nono-chan is the teacher,
+you'd feel like you had to use polite language,
+right?</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>「Teacher, what's 554×15？」</t>
+          <t>「Sensei, what's 554×15?」</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>「8310.」</t>
+          <t>"It's 8,310."</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>I start calculating on my smartphone, slower than
+          <t>I start calculating on my phone, a moment after
 Nono-chan.</t>
         </is>
       </c>
@@ -3091,8 +3091,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>I meant to show how amazing Nono-chan is, but she's
-even faster than I expected and I can't keep up
+          <t>I was going to show how amazing Nono-chan is, but it
+exceeded my expectations, and I couldn't keep up with
 explaining it to Miru-chan.</t>
         </is>
       </c>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Wait, don't just pull something like that...!</t>
+          <t>Wait—don't just do something on a whim like that...</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan, what's 14×21？」</t>
+          <t>"Miru-chan, what's 14×21?"</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>「Mmmmmm... so much」</t>
+          <t>Mmm... a lot.</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>「Hey, think about it properly.」</t>
+          <t>Hey, think about it properly.</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>「But I hate Kei-san…」</t>
+          <t>「But I hate calculations……」</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3427,8 +3427,8 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>This bluntness is so Miru-chan, but her way of
-putting it is so barefaced that I can't say anything.</t>
+          <t>This frankness is so like Miru-chan, but her way of
+putting it is so blunt that I can't say anything.</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>「…Anyway, you admit that I'm a teacher, right？」</t>
+          <t>「…Anyway, you admit he's a sensei, right?」</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>「Mm...that's amazing, teacher.」</t>
+          <t>"Mm... that's amazing, teacher."</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3518,9 +3518,8 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>As for Nono-chan, she's still hunched over her desk
-like that — I even half-wonder if she hasn't noticed
-us.</t>
+          <t>As for Nono-chan, she's still at her desk — I even
+wonder if she hasn't noticed us.</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3625,7 +3624,7 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>「It's lunch~！」</t>
+          <t>"Lunchbox~!"</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3670,8 +3669,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>Everyone's favorite lunch break — I always come to
-this place.</t>
+          <t>Everyone loves lunch break — we always come to this
+place.</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3718,7 +3717,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>「I’ll lay out the sheet today！」</t>
+          <t>"Today, I'll spread out the picnic sheet!"</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3748,7 +3747,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>「Oh！ Then I’ll help you, Miru！」</t>
+          <t>"Ah! Then I’ll help!"</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3794,8 +3793,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>「Okay. Then Miruku-chan, please hold that over
-there.」</t>
+          <t>Okay. Then, Miruku-chan, please hold that side.</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3810,8 +3808,8 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>Holding both ends of the sheet together, Nono-chan,
-while getting into position to spread it out, calls
+          <t>When the two of them took hold of the sheet's ends,
+Nono-chan, getting into position to spread it, called
 to Miru-chan.</t>
         </is>
       </c>
@@ -3842,7 +3840,8 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>「Okay？ On the count of three, we'll pull, all right？」</t>
+          <t>"Okay? On the count of three, we'll pull together,
+all right?"</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3872,7 +3871,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>「Yesss！　Heave-ho！」</t>
+          <t>「Okay！　Heave-ho！」</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3902,7 +3901,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>「Hyaaaa！？」</t>
+          <t>「Eeeek！？」</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3917,8 +3916,9 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>...We agreed to play tug-of-war, but Miru-chan jumped
-the gun, and Nono-chan pitches forward.</t>
+          <t>...Even though we said we'd pull on the count,
+Miru-chan jumped the gun, and Nono-chan stumbled
+forward.</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>「S-Stop it, Miruku-chan, you're too fast！」</t>
+          <t>「W-Wait, Miruku-chan, that's too fast!」</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>「Yesss！　Tei！」</t>
+          <t>「Okay! Heave!」</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>「Awawawawa！」</t>
+          <t>Aah! Aah! Aah! Aah!</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4100,7 +4100,7 @@
       <c r="B237" s="1" t="inlineStr">
         <is>
           <t>Miru-chan is as impatient as ever, and Nono-chan is
-being tossed around by it.</t>
+being tossed around by her.</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4130,7 +4130,8 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>I watched warmly as the two spread out the sheet.</t>
+          <t>I watched, feeling warm, as the two spread out the
+sheet.</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4160,7 +4161,7 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>「............fu」</t>
+          <t>「............Heh」</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4175,7 +4176,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>Then, Rin-chan suddenly moved up to Miru-chan...</t>
+          <t>Then, Rin-chan abruptly approached Miru-chan...</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4205,7 +4206,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>「Hyaaa！？」</t>
+          <t>「Eeeek!?」</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4220,8 +4221,8 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>While spreading the sheet, I lifted up Miru-chan’s
-skirt as she leaned forward….</t>
+          <t>While they were spreading out the sheet, Rin lifted
+up Miru-chan’s skirt as Miru leaned forward….</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4236,8 +4237,9 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>Because I was bent forward, my skirt flipped right up
-and my panties were totally exposed！</t>
+          <t>Because Miru-chan was leaning forward, her skirt
+flipped right up and her panties were completely
+exposed!</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4252,7 +4254,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>...Rin-chan, seriously, what timing for pranks!</t>
+          <t>...Rin-chan, of all times to pull a prank!</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4297,8 +4299,8 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>「MiruMiru's panties today are koala-print... they're
-super cute, so everyone's gonna be happy today」</t>
+          <t>"Miru-chan's panties today are koala-print... they're
+super cute, so everyone should be happy today"</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4313,8 +4315,8 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>As I silently offered my thanks, Rin-chan turned back
-to me and said.</t>
+          <t>As I was silently expressing my gratitude, Rin-chan
+turned to face me and said.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4345,8 +4347,8 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>I was all rushed this morning, so you pushed it off
-until noon, huh.</t>
+          <t>You were rushed this morning, so you carried it over
+until noon, huh?</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4376,7 +4378,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>「Nngghhh！ Why do you always flip up my skirt！？」</t>
+          <t>"Wahhh! Why do you always lift up my skirt!?"</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4392,7 +4394,7 @@
       <c r="B256" s="1" t="inlineStr">
         <is>
           <t>But of all times, Miru-chan had her skirt flipped up
-while she was bent over, so of course she was
+just as she bent forward, so she was understandably
 furious.</t>
         </is>
       </c>
@@ -4423,7 +4425,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>「...That's Rin's hobby.」</t>
+          <t>「...Because that's Rin's hobby.」</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4468,7 +4470,7 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>「G-gununu...！」</t>
+          <t>「G-grr...！」</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4498,8 +4500,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Since it was said without malice, she probably
-doesn't even know how to snap back.</t>
+          <t>Because it was said without malice, Miru-chan
+probably doesn't know how to reply.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4514,7 +4516,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>Instead of retorting, Miru-chan raises a water
+          <t>Instead of snapping back, Miru-chan raised a water
 pistol.</t>
         </is>
       </c>
@@ -4545,7 +4547,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>「Rin！ If it comes to this, it's a duel！」</t>
+          <t>Rin! Then it's a showdown!</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4575,7 +4577,7 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>「Very well, then it's a duel...！」</t>
+          <t>"Very well, then it's a duel!"</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4606,8 +4608,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>A duel, huh... Maybe I should try to chide them a
-little.</t>
+          <t>A duel, huh... Maybe I should admonish them a bit.</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4667,7 +4668,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>「In that case, shall we join in too？」</t>
+          <t>「In that case, shall we join in as well?」</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4698,8 +4699,8 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>Maybe she hadn't been following the flow, because she
-looked innocently delighted.</t>
+          <t>Perhaps Rurichiyo-chan hadn't been following the flow
+of events; she seemed innocently delighted.</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4729,7 +4730,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>「A water-gun battle, right！ Yay！ I won't lose！」</t>
+          <t>A water-gun fight, huh! Yay! I won't lose!</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4744,8 +4745,8 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Maybe seeing Rurichiyo-chan doing something fun,
-Nono-chan eagerly chimed in too.</t>
+          <t>Maybe because she saw Rurichiyo-chan and thought
+she'd do something fun, Nono-chan eagerly joined in.</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4775,7 +4776,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Hmph！ Then Miru will definitely win！」</t>
+          <t>Hmph! Then I'm definitely going to win!</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4790,8 +4791,8 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan rode the momentum and proclaimed victory
-early on.</t>
+          <t>Miru-chan went with the flow and quickly declared
+victory.</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4837,7 +4838,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>「Fuu... I'll take you all down at once...！」</t>
+          <t>"Hmph... I'll take you all down at once!"</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4882,8 +4883,8 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>「Ah... but that's a problem... I don't have a water
-gun, you know？」</t>
+          <t>「Ah... that's a problem... I don't have a water
+pistol, you know?」</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4929,7 +4930,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Oh... Rurichiyo-chan, nice move...</t>
+          <t>Wow... Rurichiyo-chan, not bad...</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4944,9 +4945,9 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>So it was a plan to make them think you came on all
-innocent and stop Miru-chan and Rin-chan's quarrel,
-huh.</t>
+          <t>So it was a plan to make them think she had
+innocently joined in to stop Miru-chan and Rin-chan's
+quarrel, huh.</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4976,7 +4977,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>「Is that so... what a shame...」</t>
+          <t>「Oh... that's too bad...」</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4991,7 +4992,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan says with a half-bothered look on her face.</t>
+          <t>Nono-chan says with a half-embarrassed look.</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5006,9 +5007,8 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>She'd been going along with the mood and gotten
-serious, so she probably felt like she’d been let
-down.</t>
+          <t>They'd gotten carried away and taken it seriously, so
+they probably felt a bit let down.</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>「It's okay. Niini will go buy it for us.」</t>
+          <t>"It's okay. Niini will go buy them for us."</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, you're right！ ...Huh？」</t>
+          <t>「Yeah, that's right! …Huh?」</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, please.」</t>
+          <t>「Okay, please.」</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5190,7 +5190,8 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>「They sell it at the usual dagashi shop, you know？」</t>
+          <t>They sell them at the usual traditional snack shop,
+you know?</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5296,7 +5297,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>「...So that's how it turns out.」</t>
+          <t>「...I guess that's how it is.」</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5311,8 +5312,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>Hmm... That’s a blunt thing to say, but it comes from
-innocence.</t>
+          <t>Hmm... An uninhibited remark born of innocence.</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5357,8 +5357,8 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who had been up for it for a moment, looks
-at me with an expectant, slightly hesitant gaze.</t>
+          <t>Nono-chan, who had been keen for a moment, looked at
+me with an expectant, slightly hesitant gaze.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>…Well, as long as I can see that happy face,
+          <t>…Well, if it means seeing those happy faces, then
 anything's fine.</t>
         </is>
       </c>
@@ -5555,8 +5555,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I’ll go buy Rurichiyo-chan’s and Nono-chan’s
-by after school.」</t>
+          <t>"All right, I’ll go buy Rurichiyo-chan’s and
+Nono-chan’s before the end of the school day."</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>「Eh？ Onii-chan, you aren't going to do it？」</t>
+          <t>「Ehh? Onii-chan, aren't you going to do it?」</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5677,8 +5677,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>"This was supposed to be a contest between Miru-chan
-and Rin-chan to begin with, but... oh well."</t>
+          <t>This was supposed to be a contest between Miru-chan
+and Rin-chan to begin with, but... oh well.</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5708,8 +5708,8 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>「So, the match will be after school... and for now,
-let's have lunch！」</t>
+          <t>All right, the match will be after school... For now,
+let's have lunch!</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan took the lead, and it was lunchtime.</t>
+          <t>Nono-chan took the lead, and everyone had lunch.</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>A proposal from Nono-chan, huh...</t>
+          <t>Nono-chan's suggestion, huh...</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>And then, after school came... .</t>
+          <t>And then, after school came...</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>「Okay, here's the explanation of the rules！」</t>
+          <t>All right, here's the explanation of the rules!</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5891,9 +5891,9 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who volunteered to be the host, stands in
-a proud, wide-legged pose wearing bloomers and
-holding a water gun in one hand.</t>
+          <t>Nono-chan, who volunteered to act as the MC, stood
+proudly in a wide-legged stance, wearing bloomers and
+holding a water pistol in one hand.</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5923,8 +5923,8 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>「This water-gun match is an all-participant survival
-game. In other words, everyone is an enemy！」</t>
+          <t>This water-gun match is a survival game with everyone
+participating. In other words, everyone is an enemy!</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5954,9 +5954,9 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>「You can pour as much water as you like, but I’ve
-prepared something that, if it’s poured on this, you
-lose... Janitor-sensei, please.」</t>
+          <t>It's fine to get splashed with water as much as you
+like, but I've prepared something—if water hits this,
+you lose... Janitor-sensei, please.</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6001,8 +6001,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Following Nono-chan's lead, I took out and showed the
-item we were going to use this time.</t>
+          <t>Following Nono-chan's lead, she took out the item
+we'd be using this time and showed it to us.</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6017,8 +6017,8 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>It was the paper net used for scooping goldfish. The
-proper name, it seems, is poi.</t>
+          <t>It was the paper net used for goldfish scooping. Its
+proper name, it seems, is 'poi'.</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>「Oh... how official...！」</t>
+          <t>「Whoa... this is getting serious...!」</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>「My! What a wonderful idea!」</t>
+          <t>「Oh my! What a wonderful idea!」</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>「But Oji-sama, when did you get these ready？」</t>
+          <t>「But, Oji-sama, when did you prepare that?」</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>「...Yeah. I actually planned to make something
+          <t>「...Yeah. I was actually planning to make something
 simpler, though.」</t>
         </is>
       </c>
@@ -6260,9 +6260,9 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「But when I asked the snack shop lady if she had
-anything, she brought these out. She probably used
-them at a festival.」</t>
+          <t>But when I asked the owner of the traditional snack
+shop if she had anything, she brought these out. They
+were probably used at a festival.</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan looked somehow proud.</t>
+          <t>Rin-chan looked somewhat proud.</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>I handed out headbands with poi attached to everyone.</t>
+          <t>I handed out headbands fitted with poi to everyone.</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>「Yes yes—question time!」</t>
+          <t>「Okay, okay—question time!」</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6457,8 +6457,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>「If tearing means you lose, then if I cover it with
-my hand I wouldn't lose, right？」</t>
+          <t>If the rule is that you lose when it gets torn, then
+if I cover it with my hand I wouldn't lose, would I?</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6473,8 +6473,8 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan said that and actually covered the poi with
-her hand.</t>
+          <t>Saying that, Miruku actually covered the poi with her
+hand.</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -6534,8 +6534,8 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>But, huh, there might actually be some detailed rules
-about that, right？</t>
+          <t>But I wonder if there are actually some specific
+rules about that?</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>「Teacher？ Are there any fouls？」</t>
+          <t>「Sensei? Are there any fouls?」</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6595,9 +6595,9 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>「Fouls...? Hitting, kicking and things like that are
-banned, but other than that I think no rules is
-fine！」</t>
+          <t>Fouls...? Hitting, kicking, and the like are
+prohibited, but other than that, I think it's fine to
+have no rules!</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>「I want you to call it 'dynamic'！」</t>
+          <t>I'd like you to say "dynamic"!</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -6672,8 +6672,8 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>You can tell everyone is looking forward to it, so
-Nono-chan throws herself back confidently.</t>
+          <t>I could tell everyone was looking forward to it, so
+Nono-chan threw herself back confidently.</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>「...So that's that, any questions？」</t>
+          <t>「...So that's it—any questions?」</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>「There isn't, ma'am.」</t>
+          <t>「There are none.」</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>They each hold a water pistol and say something.</t>
+          <t>Everyone raised their water guns and spoke.</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6823,8 +6823,8 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>They said they'd do it from the afternoon, so
-everyone is already all excited.</t>
+          <t>They said they'd start in the afternoon, so everyone
+is already excited.</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6854,8 +6854,9 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'm going to count to ten now. By then,
-scatter out, and on three — start all at once！」</t>
+          <t>Okay, I'll count to ten now. Until then, scatter out
+and spread apart — on my mark, we'll all start
+together!</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6885,7 +6886,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>「O-n-e！」</t>
+          <t>「Okay? One!」</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6931,8 +6932,8 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>「Rin！ I haven't forgotten you！ I'm gonna make you all
-soggy...！」</t>
+          <t>"Rin! I haven't forgotten about you! I'll drench
+you...!"</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6962,7 +6963,7 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>「Fuh... you're ten years too early, MiruMiru...！」</t>
+          <t>"Heh... MiruMiru, you're ten years too early...!"</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -6977,8 +6978,8 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan and Rin-chan said that to each other and
-stormed off in opposite directions.</t>
+          <t>Miru-chan and Rin-chan exchanged those words and
+scattered off in opposite directions.</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7008,7 +7009,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Nii~！」</t>
+          <t>「T-w-o！」</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7068,7 +7069,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>「What shall we do? They're all enemies, aren't they?」</t>
+          <t>'What shall we do,' you ask? Everyone's an enemy, you
+know?</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7144,7 +7146,7 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>「Saaaan！」</t>
+          <t>「Three!」</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7189,7 +7191,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>「Juuuu！　Ready！　Start！！」</t>
+          <t>「Ten! Okay! Start!!」</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7204,8 +7206,8 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan finishes the count, and the water-gun
-survival begins！</t>
+          <t>...Nono-chan finished counting, and the water-gun
+survival began!</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -7220,8 +7222,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>I hide in the shadow of the school building and watch
-how everyone is doing.</t>
+          <t>I keep myself hidden in the shadows of the school
+building and watch everyone.</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7251,7 +7253,7 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>「Ooooooohhhhh~~~~！」</t>
+          <t>「Oooooooh~~~！」</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7281,8 +7283,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>She thrusts her water gun forward, keeping an all-out
-offensive stance.</t>
+          <t>She pushes her water gun forward, remaining firmly on
+the offensive.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7312,7 +7314,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「........Ah！」</t>
+          <t>「...Ah！」</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7327,8 +7329,8 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>As I watched, thinking 'that's impressive,' I noticed
-Miru-chan's little bit of cheating... no, technique.</t>
+          <t>As I watched, thinking 'impressive,' I noticed
+Miru-chan's little cheat—no, technique.</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -7343,8 +7345,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>...Miru-chan has the poi held vertically so it can't
-be broken from the front！！</t>
+          <t>...Miru-chan has attached the poi vertically so it
+won't be torn from the front!!</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7389,7 +7391,7 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, also confident, doesn't hide and faces them
+          <t>Rin-chan is bold too; she doesn't hide and meets her
 head-on.</t>
         </is>
       </c>
@@ -7435,8 +7437,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, being shrewd herself, has the poi held
-vertically.</t>
+          <t>Rin-chan, likewise crafty, keeps her poi vertical.</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7467,7 +7468,7 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>So we were thinking the same thing, huh….</t>
+          <t>Looks like we're thinking the same thing, huh...</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7497,7 +7498,7 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Rin！ Brace yourself！」</t>
+          <t>「Rin! Get ready!」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7542,7 +7543,7 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>「...Hiu！」</t>
+          <t>「...Eek！」</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7573,8 +7574,8 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>Pushed by Miru-chan's momentum, or was that
-Rin-chan's plan…？</t>
+          <t>Was Rin-chan pushed back by Miru-chan's momentum, or
+was it Rin-chan's strategy...?</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7604,7 +7605,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan, it's a match！」</t>
+          <t>"Rurichiyo-chan, let's have a match!"</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7696,7 +7697,7 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>「Hey！　Hey！」</t>
+          <t>「Take that! Take that!」</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -7711,8 +7712,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>A stream of water whooshes and splashes onto
-Rurichiyo-chan's arm.</t>
+          <t>A spray of water whooshes onto Rurichiyo-chan's arm.</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>「Hyaa… you got me! Take this!」</t>
+          <t>"Eek... You did it! Take this!"</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>「Hya！？ I-I'm not losing！」</t>
+          <t>Hyaa!? I-I'm not going to lose!</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7850,7 +7850,8 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>Yet neither stops moving to close the distance.</t>
+          <t>However, both of them freeze in place and don't even
+try to close the distance.</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7865,8 +7866,7 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>...It's just girls horsing around with each other,
-how heartwarming.</t>
+          <t>It's endearing to see the girls playing together.</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>「Ri-Rin！ Don't run away！」</t>
+          <t>"R-Rin! Don't run away!"</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7957,8 +7957,8 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t>「Kufufu... I'm not running away anymore. MiruMiru,
-you're about to run out of water, right...?」</t>
+          <t>Heh heh... I won't run away anymore. MiruMiru, your
+water's almost gone, right...!</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>「What？　Aaah！？」</t>
+          <t>Eh? Aaah!?</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8003,8 +8003,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Miru, being told that by Rin-chan, hurriedly looks at
-her water gun.</t>
+          <t>After Rin-chan said that, Miru-chan hurriedly looks
+at her own water gun.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>「Kuf, kufufu...！ MiruMiru, prepare yourself.」</t>
+          <t>Heh heh heh...! MiruMiru, prepare yourself.</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>「Eii！　Eeei！」</t>
+          <t>Ei! E~i!</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>「Hooiya！　Hooiya！」</t>
+          <t>Hoiya! Hoiya!</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8125,8 +8125,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>The roughhousing between Rurichiyo-chan and Nono-chan
-keeps going as usual.</t>
+          <t>On Rurichiyo-chan and Nono-chan's side, their playful
+sparring continues as usual.</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>I feel awkward joining either side...</t>
+          <t>I'm hesitant to join either of them...</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8156,8 +8156,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>Well, it's nice enough to just watch from the
-sidelines.</t>
+          <t>Well, it's nice to just watch from the sidelines.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8172,7 +8171,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>I sit down and watch everyone playing...</t>
+          <t>I sit down and watch over everyone as they play...</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8187,7 +8186,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>Balbalbalbalbalbalbal！！！</t>
+          <t>Pew pew pew pew pew pew!!!</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8217,7 +8216,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>「Wha...！？」</t>
+          <t>What...!?</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8232,8 +8231,8 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>Hearing a helicopter, I scramble and look up at the
-sky.</t>
+          <t>At the sound of a helicopter, I hurriedly looked up
+at the sky.</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8263,8 +8262,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>『Ru-ri-chi-yo~！ It's Baba-chama~！ Baba-chama is
-here~...！』</t>
+          <t>『Rurichiyo~! Baba-chama~! Baba-chama's here~...!』</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8279,7 +8277,7 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>Of course, it's Kikuchiyo-baa-chan...</t>
+          <t>As I thought, it's Kikuchiyo-baa-chan...</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8294,8 +8292,8 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>Just like last time, she's calling down through a
-loudspeaker from the sky.</t>
+          <t>As before, she's calling out from the sky over a
+loudspeaker.</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8325,7 +8323,7 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>「Grandmama！？」</t>
+          <t>Grandmother!?</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8357,7 +8355,8 @@
       <c r="B515" s="1" t="inlineStr">
         <is>
           <t>No—it's not just Rurichiyo-chan; everyone else looks
-up too, and there's a brief ceasefire.</t>
+up too, and they've paused fighting for the time
+being.</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8387,7 +8386,7 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>「W-what did she come for...？」</t>
+          <t>W-what did she come here for...?</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -8447,9 +8446,9 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>『Rurichiyo~！ I heard from Sacchan at the dagashi
-shop！ You're going to settle it with water guns,
-right~？』</t>
+          <t>『Rurichiyo~! I heard from Sacchan at the traditional
+snack shop! You're going to have a water-gun
+showdown, right~?』</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8480,8 +8479,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>Oh, so you were talking about what to do when buying
-water guns and poi at the traditional snack shop.</t>
+          <t>I see — Sacchan at the dagashi shop told her about
+what they'd do when buying water guns and poi.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8496,7 +8495,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>Did that get to Kikuchiyo-baa-chan?</t>
+          <t>Had that reached Kikuchiyo-baa-chan?</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8572,7 +8571,7 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>『I'll leave my present at the watering trough！』</t>
+          <t>『I'll leave my present at the drinking fountain!』</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8602,8 +8601,8 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>『First come, first served！ Everyone use it nicely,
-okay~！』</t>
+          <t>But it's first-come, first-served! Make sure you all
+share it nicely, okay~!</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8695,7 +8694,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>「Ah… thanks.」</t>
+          <t>「Ah... hello.」</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8710,8 +8709,8 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>Feeling like our eyes met, I bowed, and the woman
-bowed back before hurrying off.</t>
+          <t>I felt our eyes meet, so I bowed; the woman returned
+my bow and hurried away.</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -8757,7 +8756,7 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>『Rurichiyo~！ Fight！ Alrighty then~！』</t>
+          <t>『Rurichiyo~! Go for it! Okay then~!』</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -8833,7 +8832,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>Barubarubarubarubaru！！！</t>
+          <t>Rumble rumble rumble rumble rumble rumble!!!</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -8924,7 +8923,7 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>「...！」</t>
+          <t>「…!!」</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -8970,7 +8969,7 @@
       </c>
       <c r="B555" s="1" t="inlineStr">
         <is>
-          <t>「Ah！？ Uh, um… I won't let you！」</t>
+          <t>"Ah!? Uh... um... I won't let you do that!"</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -9015,7 +9014,7 @@
       </c>
       <c r="B558" s="1" t="inlineStr">
         <is>
-          <t>「Ugh…！　Aaaahhh！　Dammit！」</t>
+          <t>「Ugh…! Aaaahhh! Jeez!」</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -9046,8 +9045,8 @@
       <c r="B560" s="1" t="inlineStr">
         <is>
           <t>That said, it wasn't really about getting
-Kikuchiyo-baa-chan's present — she was just parched
-to begin with.</t>
+Kikuchiyo-baa-chan's present — Rurichiyo-chan was
+just parched to begin with.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9077,7 +9076,7 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>「MiruMiru… I won't let you get away…！」</t>
+          <t>「Miru-chan… I won't let you get away…!」</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9123,7 +9122,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>「………………！ Hey, everyone, wait a sec！」</t>
+          <t>「………………！ Wait a moment, everyone!」</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9185,7 +9184,7 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>「………………!？!」</t>
+          <t>「………………!!?」</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9215,7 +9214,7 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, hello everyone.」</t>
+          <t>「Oh, hello, everyone.」</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9245,7 +9244,7 @@
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
-          <t>「………………!？!」</t>
+          <t>「………………!!?」</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9260,9 +9259,8 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>Everyone who had rushed over to the drinking area
-stopped dead in their tracks at once, their
-expressions twitching….</t>
+          <t>Everyone who had rushed over to the water trough
+froze in place, their expressions tightening…</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -9292,8 +9290,8 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>On a short three-legged stand sat a rotating water
-gun, like a heavy machine gun… a Gatling gun！</t>
+          <t>Mounted on a short tripod was a rotating water gun —
+like a heavy machine gun… a Gatling gun!</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9324,7 +9322,7 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t>So this is what you were installing earlier！？</t>
+          <t>So that's what was being installed earlier!?</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -9354,7 +9352,7 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>「...Hm？ What are we supposed to do with this？」</t>
+          <t>Huh? What should we do with this?</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -9384,9 +9382,9 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>Pulling the trigger should make water come out just
-like the one you're holding now, but the shape is so
-different she probably can't tell.</t>
+          <t>Pulling the trigger would make water come out just
+like the one we have now, but its shape is so
+different that she probably wouldn't recognize it.</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9416,7 +9414,7 @@
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
-          <t>「...Now！」</t>
+          <t>「…Now's our chance!」</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -9446,9 +9444,9 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>While Rurichiyo was floundering... or rather, she was
-cornered because she'd run out of water, so she had
-no other choice.</t>
+          <t>While Rurichiyo-chan hesitated... or rather, she’d
+been backed into a corner because she’d run out of
+water, so she had no other option.</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9478,7 +9476,7 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>「...！」</t>
+          <t>「…!」</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9523,7 +9521,7 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>「Umm... ah！？」</t>
+          <t>「Um... Ah!?」</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -9538,7 +9536,7 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>Vwooooooooooooosh！！！</t>
+          <t>Whirrrrrrrrr!!!</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9568,7 +9566,7 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>「Whoah！？　Waa！？」</t>
+          <t>「Whoa!? Wah!?」</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9615,7 +9613,7 @@
       </c>
       <c r="B597" s="1" t="inlineStr">
         <is>
-          <t>「Whoa！？　Puwaaaah！」</t>
+          <t>「Whoa!? Pwaaah!」</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -9630,8 +9628,8 @@
       </c>
       <c r="B598" s="1" t="inlineStr">
         <is>
-          <t>The force of the spray shifted the stream, and it
-accidentally landed a clean hit on Miru.</t>
+          <t>The force of the water shifted the shot's trajectory,
+and it accidentally scored a clean hit on Miru-chan.</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -9646,9 +9644,9 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>She seemed to instinctively try to shield the poi
-with her hand, but the volume of the spray wouldn't
-allow it.</t>
+          <t>Miru-chan seemed to instinctively try to shield the
+poi with her hand, but the spray's force made that
+impossible.</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -9663,7 +9661,7 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>Miru, you're out—.</t>
+          <t>Miru-chan, you're out!</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -9784,8 +9782,8 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>Saying that, Rin-chan is using Miru as a shield while
-protecting the poi.</t>
+          <t>As for Rin-chan, she's using Miru-chan as a shield to
+protect the poi.</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9815,7 +9813,7 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>「Ri‑Rin~~~！ I'll get you back for this later！！！」</t>
+          <t>「R-Rin~~~! I'll get you back for this later!!!」</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -9862,7 +9860,7 @@
         <is>
           <t>...She probably hid instinctively because she was
 following Miru-chan, but I have to take my hat off to
-that craftiness.</t>
+that quick thinking.</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -9892,7 +9890,7 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ah！ This is it, isn't it...！」</t>
+          <t>「Mmm... ah! This must be it...!」</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -9953,7 +9951,7 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>The water stops, and Miru collapses.</t>
+          <t>The spray stops, and Miru-chan collapses.</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -9983,7 +9981,7 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「W-wait, Miru…！」</t>
+          <t>"W-wait, Miru-chan...!"</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -9998,8 +9996,8 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>I rushed over to Miru, grabbed her by both armpits,
-and started to pull her away.</t>
+          <t>I rushed over to Miru-chan, took her under both arms,
+and began to pull her away.</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -10029,7 +10027,7 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chaaaan, I'm so sorry！」</t>
+          <t>「Miruku-chaaaan, I'm so sorry!」</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10045,7 +10043,7 @@
       <c r="B625" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan waves her hand apologetically, but she
-won't let go of the Gatling gun in her hands.</t>
+doesn't let go of the Gatling gun she's holding.</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10106,7 +10104,7 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>「………………huh？」</t>
+          <t>「………………Huh？」</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -10137,7 +10135,7 @@
       </c>
       <c r="B631" s="1" t="inlineStr">
         <is>
-          <t>Looks like they slipped away sometime earlier.</t>
+          <t>Apparently they slipped away before I noticed.</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -10167,7 +10165,7 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>「…Hmm？ Where did the two of them go, I wonder？」</t>
+          <t>Hmm? I wonder where the two of them went.</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10182,8 +10180,8 @@
       </c>
       <c r="B634" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan notices they're gone too and looks
-around.</t>
+          <t>Rurichiyo-chan also notices that the two are gone and
+is looking around.</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -10244,7 +10242,7 @@
       </c>
       <c r="B638" s="1" t="inlineStr">
         <is>
-          <t>She pulled the trigger, released it.</t>
+          <t>She kept pulling and releasing the trigger.</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -10290,8 +10288,8 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「……Okay, I get it！ Now we're safe no matter where
-they come from！」</t>
+          <t>…Yes, understood! With this, we'll be fine no matter
+where they come from!</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10306,7 +10304,8 @@
       </c>
       <c r="B642" s="1" t="inlineStr">
         <is>
-          <t>She beams, having mastered handling the Gatling gun.</t>
+          <t>Rurichiyo was elated, having mastered how to handle
+the Gatling gun.</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -10366,7 +10365,7 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>「H-heh, heh… Is that so…？」</t>
+          <t>「H-huh... Heh heh... I wonder about that...?」</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10471,8 +10470,9 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan pointed, I saw Nono-chan appear and
-dash toward the drinking fountain.</t>
+          <t>When I looked in the direction Miru-chan pointed,
+Nono-chan appeared and ran toward the drinking
+fountain.</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>Eh... could she really be charging straight on...？</t>
+          <t>Eh... is she really going to charge straight in...?</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10532,8 +10532,8 @@
       </c>
       <c r="B657" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan spots Nono-chan, aims a Gatling gun
-that way and sprays water...！</t>
+          <t>Rurichiyo-chan spots Nono-chan, aims the Gatling gun
+at her and sprays water...!</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>「Hehe... you won't hit me！」</t>
+          <t>"Heh heh... you're not going to hit me!"</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>I can see Rin-chan behind her too, that’s not just my
+          <t>I can see Rin-chan back there too, that's not just my
 imagination, right?</t>
         </is>
       </c>
@@ -10655,8 +10655,8 @@
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
-          <t>「Wow... Nono-chan, amazing...！ How are you not
-getting hit！？」</t>
+          <t>"Wow... Nono-chan, amazing...! How are they not
+hitting you?!"</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -10761,8 +10761,8 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>I started explaining to Miru-chan while watching the
-path Nono-chan was running.</t>
+          <t>I began explaining to Miru-chan as I watched the path
+Nono-chan was taking.</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -10792,9 +10792,9 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan read that Gatling’s ammo-feed lag… see,
-once it fires, there’s a tiny pause before the next
-round comes out, right？」</t>
+          <t>「Nono-chan read that Gatling’s water-feed lag… see,
+once it fires, there’s a short pause before the next
+shot comes out, right？」</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10854,9 +10854,9 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>「Also, the water has force, so once you fire it, it's
-hard to change it mid-course... if it shifts to the
-side then you won't be able to hit it.」</t>
+          <t>Also, the water has momentum, so once it's fired it's
+hard to change its course mid-flight... if you
+sidestep at that moment, you won't get hit.</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -10886,8 +10886,8 @@
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
-          <t>「Well, sometimes like when Miru-chan got hit, it gets
-pushed by the momentum and changes...」</t>
+          <t>「Well, sometimes, like when Miru-chan was hit, the
+stream can be pushed off course by the force...」</t>
         </is>
       </c>
       <c r="C680" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>「Muu... so, did Miru lose by a fluke？」</t>
+          <t>"Mmm... so did I lose by a fluke?"</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... I guess that'll be how it is... ah！」</t>
+          <t>Hmm... I guess that's how it goes... Ah!</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -11053,9 +11053,9 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>I see — with a water balloon there's no hassle of
-aiming with a water gun, so I can go after
-Rurichiyo-chan's poi…！</t>
+          <t>I see — with a water balloon, there's no need to
+bother aiming with a water gun, so Nono-chan can aim
+for Rurichiyo-chan's poi…!</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>But when did they put water balloons out...？</t>
+          <t>But when did Nono-chan get a water balloon...?</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！？　Ye-eah！」</t>
+          <t>「Nngh!? Hyaaah!」</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11130,7 +11130,8 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>「If you get this close it's already useless... Hei！」</t>
+          <t>「If you get this close, it's already useless... Take
+this!」</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -11192,7 +11193,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>「Kyaaaaah...！」</t>
+          <t>「Eeeeek!」</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -11207,8 +11208,9 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>...But Rurichiyo―chan, already backing away, slackens
-her grip, and the jet's force throws off her aim―！</t>
+          <t>...But Rurichiyo-chan, already backing away, eased
+up, and the force of the water caused her aim to
+wobble—!</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -11238,7 +11240,7 @@
       </c>
       <c r="B703" s="1" t="inlineStr">
         <is>
-          <t>「Fuwa！　Puuu！？」</t>
+          <t>「Puff! Pffft!?」</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -11253,9 +11255,9 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>...Amazingly, the misdirected jet glances the water
-balloon, knocking it off course and straight into
-Nono-chan's face！</t>
+          <t>Incredibly, the stray spray deflected the water
+balloon, sending it flying straight into Nono-chan's
+face!</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11270,7 +11272,7 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>The impact even rips the thin poi along with it...</t>
+          <t>The force even tore through the thin poi as well...</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11406,7 +11408,7 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>...Could it really be a coordinated play？</t>
+          <t>...An unexpected team-up?</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11421,8 +11423,8 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>That means the water balloons from earlier must've
-been secretly held by Rin-chan.</t>
+          <t>That means Rin-chan must have been hiding the water
+balloon from earlier.</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -11437,9 +11439,9 @@
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan calculated the firing line logically,
-Rin-chan provided the secret weapon, and together
-they launched this operation...！</t>
+          <t>Nono-chan had logically read the line of fire,
+Rin-chan provided the secret weapon, and with that
+they carried out this plan...!</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11484,8 +11486,8 @@
       </c>
       <c r="B719" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, with a water gun pressed right up
-close, couldn't do anything...！</t>
+          <t>With a water gun pressed against her at point-blank
+range, Rurichiyo-chan could do nothing...!</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -11515,7 +11517,7 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>「Huh...！」</t>
+          <t>「Gasp...！」</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -11530,8 +11532,8 @@
       </c>
       <c r="B722" s="1" t="inlineStr">
         <is>
-          <t>...Just one second, but Rin-chan carefully took aim
-and is now pulling the trigger！</t>
+          <t>...It's only a single second, but Rin-chan, having
+carefully taken aim, now squeezes the trigger!</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -11546,7 +11548,7 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>Pohyu~.</t>
+          <t>Pffft~.</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -11667,7 +11669,7 @@
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>「Gyaaaaaaa！」</t>
+          <t>「Gyaaaaaah！」</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -11682,7 +11684,7 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>...What a thing.</t>
+          <t>...What on earth is this?</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -11743,7 +11745,7 @@
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
-          <t>「Niini-cha~n, do your best~！」</t>
+          <t>「Onii-chan, you can do it~!」</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -11773,7 +11775,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>「Niini, fight~！」</t>
+          <t>「Niini, go for it~！」</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -11803,7 +11805,7 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei, pleeease hit the bad guy！」</t>
+          <t>Janitor-sensei, pleeease hit them!</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -11924,7 +11926,8 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>「We don't know where the water's gonna fly...！」</t>
+          <t>「We don't know where the water's going to come flying
+from...!」</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -11954,7 +11957,7 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>「We gotta fill it up now...」</t>
+          <t>We have to fill it with water while we still can...</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -12045,9 +12048,9 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, brandishing an overwhelmingly
-powerful weapon, looked at me with a rare, wicked
-grin.</t>
+          <t>Rurichiyo-chan, holding an overwhelmingly powerful
+weapon, fixed her gaze on me with an unusually wicked
+expression.</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -12107,9 +12110,9 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>But I still had a chance... my water gun was full,
-and since my hands are bigger than everyone else's, I
-could guard the poi more easily.</t>
+          <t>But there's still a chance... my water gun is full,
+and because my hands are bigger than everyone else's,
+it's easier for me to guard the poi.</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -12140,7 +12143,8 @@
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
-          <t>...But the power of that gatling gun is unknown.</t>
+          <t>...But the firepower of that Gatling gun is
+uncertain.</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -12155,8 +12159,8 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>While I hesitated like that, everyone's voices flew
-over.</t>
+          <t>As I hesitated like that, I heard everyone's voices
+calling out.</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -12186,7 +12190,7 @@
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan~！ Ha~urry~ up~！」</t>
+          <t>「Onii-chan~! Hurry up~!」</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -12216,7 +12220,7 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>「Niini, have you made up your mind？」</t>
+          <t>「Niini, have you made up your mind?」</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -12246,7 +12250,7 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>「If it's Janitor-sensei, I can do it, you know~...！」</t>
+          <t>「If it's Janitor-sensei, he can do it, you know~...！」</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -12261,8 +12265,8 @@
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>Those words all seem to have their own agendas, but
-nothing will start unless we do something for now.</t>
+          <t>Everyone seems to have their own motives, but nothing
+will happen unless we act.</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -12478,7 +12482,7 @@
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>「Well then, steel yourself」</t>
+          <t>Now then, please brace yourself.</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -12508,7 +12512,7 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah...」</t>
+          <t>Ah... ah...</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -12538,7 +12542,8 @@
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I shielded the poi with both hands...！</t>
+          <t>With that in mind, I shielded the poi with both
+hands...!</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -12553,7 +12558,7 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12568,7 +12573,7 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>「Oh...？」</t>
+          <t>Oh...？</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12583,8 +12588,9 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>But then, with a strange sound, the main hose came
-off, and the rushing water writhed like a snake.</t>
+          <t>No sooner had I heard a strange noise than the hose
+on the main unit came loose and, driven by the
+rushing water, writhed like a snake.</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -12599,7 +12605,7 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12614,7 +12620,7 @@
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
-          <t>「Ay, ayay！？」</t>
+          <t>Ah—yaaah!?</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -12644,7 +12650,7 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>「Eh？　Nyaaah！？」</t>
+          <t>Eh? Nyaaaah!?</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -12674,7 +12680,7 @@
       </c>
       <c r="B797" s="1" t="inlineStr">
         <is>
-          <t>「Nyoo！？　Oh...！？」</t>
+          <t>Whoa!? Oh...!?</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -12704,7 +12710,7 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>「Waaah, puh-puh...！'」</t>
+          <t>Waaah—pfft pfft...!</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -12749,7 +12755,7 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>「Ah—ah—...」</t>
+          <t>Ah—ah—...</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -12764,8 +12770,8 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>I hurried to the water tap area, shut the faucet, and
-stopped the flow.</t>
+          <t>I rushed to the water tap and, for the time being,
+turned off the faucet to stop the water.</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -12795,7 +12801,7 @@
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>「Everyone, are you okay？」</t>
+          <t>Everyone, are you okay？</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -12825,7 +12831,7 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... drenched~...」</t>
+          <t>Waaah... I'm all soaked~...</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -12840,8 +12846,8 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>Miru, doused in a huge amount of water, wiped her
-face with her hand and grimaced.</t>
+          <t>Miru-chan, drenched in a lot of water, wiped her face
+with her hand and grimaced.</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -12871,7 +12877,7 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... uuu...'」</t>
+          <t>Mmm... uuu...</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -12901,7 +12907,7 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>「Mmm—! Puwa! Ahh! You startled me!」</t>
+          <t>Mmm—n! Pwah! Ahh! I was so surprised!</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -12931,7 +12937,7 @@
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
-          <t>「Whaaa— I'm so surprised...！」</t>
+          <t>Whaaa— that surprised me~...!</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -12946,7 +12952,7 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>Everyone else is wiping their face, too.</t>
+          <t>The others were wiping their faces, too.</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -12976,7 +12982,7 @@
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>「Ah... everyone. I'm terribly sorry...」</t>
+          <t>Ah... everyone. I'm terribly sorry...</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -13051,9 +13057,9 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>When Rurichiyo-chan, who caused this situation,
-looked down and apologized, Rin-chan and Nono-chan
-immediately jumped in to back her up.</t>
+          <t>When Rurichiyo-chan, who had caused the situation,
+hung her head and apologized, Rin-chan and Nono-chan
+immediately stepped in to support her.</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -13128,7 +13134,7 @@
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
-          <t>「Ah... that's true, everyone's soaked, isn't she.」</t>
+          <t>"Ah... that's right, everyone's soaked, aren't they?"</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -13205,7 +13211,7 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>...But my eyes are glued to their figures.</t>
+          <t>...But I can't take my eyes off them.</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -13220,7 +13226,7 @@
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
-          <t>The droplets trickling from their hair sparkle.</t>
+          <t>Droplets trickling down from their hair sparkle.</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -13235,8 +13241,8 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>The white gym uniform clinging to their skin and
-becoming slightly translucent is nice.</t>
+          <t>I like the white gym uniforms clinging to their skin
+and becoming slightly see-through.</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -13251,7 +13257,7 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>Their cheeks reddened from exertion and excitement
+          <t>Their cheeks, flushed from exercise and excitement,
 are the best.</t>
         </is>
       </c>
@@ -13267,8 +13273,8 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>Ooohhh... unexpectedly, this is the perfect
-location...！</t>
+          <t>Ohhh... of all things, this turned out to be the
+perfect spot...!</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -13298,7 +13304,7 @@
       </c>
       <c r="B838" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Ruri-chan's target...！」</t>
+          <t>"Ah... Ruri-chan's mark...!"</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -13343,8 +13349,9 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>Getting doused with a ton of water from the squirt
-gun would tear a thin poi right away anyway.</t>
+          <t>Since they were drenched with a large amount of
+water—more than just being sprayed by a squirt gun—a
+thin poi would tear immediately.</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13404,7 +13411,7 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>「Uuuuh~ I guess that's how it is, huh...！」</t>
+          <t>Uuu~n... I guess so...!</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -13419,7 +13426,7 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan nods back at Rin-chan's words.</t>
+          <t>Nono-chan nods in response to Rin-chan's words.</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -13449,7 +13456,7 @@
       </c>
       <c r="B848" s="1" t="inlineStr">
         <is>
-          <t>「Ah...........ah！ I won！？ Yes！」</t>
+          <t>「Ah... ahh! I won!? Yay!」</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -13464,9 +13471,9 @@
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>I had been secretly enjoying everyone's soaked,
-see-through gym uniforms, and in a flustered, gleeful
-rush I showed them off.</t>
+          <t>I had been secretly savoring everyone's wet,
+see-through gym uniforms, and, flustered and
+delighted, I couldn't help but show it.</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -13496,7 +13503,7 @@
       </c>
       <c r="B851" s="1" t="inlineStr">
         <is>
-          <t>「Mmm...！　Muuu...！」</t>
+          <t>Mmm...！　Muuu...！</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -13526,7 +13533,7 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>「H-hmph...！」</t>
+          <t>H-hmph...！</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -13541,8 +13548,9 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>...As if on purpose to hide their ulterior motives,
-Miru-chan and Rin-chan let out frustrated sighs.</t>
+          <t>...Perhaps they'd deliberately acted playful to hide
+their ulterior motives; Miru-chan and Rin-chan let
+out frustrated sighs.</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -13557,9 +13565,8 @@
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
-          <t>I only got the spoils by chance, so maybe I
-accidentally lit the fire under that competitive
-streak...</t>
+          <t>I only ended up reaping the spoils, so maybe I
+accidentally sparked their competitive streaks...</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -13619,7 +13626,8 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>Even though she's soaking wet, she never learns, huh.</t>
+          <t>Even though they're soaking wet, they never learn, do
+they?</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13634,7 +13642,7 @@
       </c>
       <c r="B860" s="1" t="inlineStr">
         <is>
-          <t>...Thinking that, Nono-chan raised her hand.</t>
+          <t>As I was thinking that, Nono-chan raised her hand.</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -13710,7 +13718,7 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>Sqqquiiirt！</t>
+          <t>Squiiirt!</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -13755,9 +13763,9 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan and everyone else focused their
-attacks on my face, and the second round ended in a
-quick retirement...</t>
+          <t>Everyone, including Rurichiyo-chan, concentrated
+their attacks on my face, and I was forced to retire
+from the second round early...</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -13788,9 +13796,9 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>There were a lot of poi, so we kept up the pretense
-of it being a contest, but the appearance of the huge
-water gun seemed to set everyone's hearts on fire.</t>
+          <t>There were a lot of poi, so it at least took the form
+of a contest, but the appearance of the huge water
+gun seemed to set everyone's hearts on fire.</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -13805,8 +13813,9 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>Or rather, it was just fun to get totally drenched, I
-guess...</t>
+          <t>Whether you'd call it lighting a fire in them, or
+simply that they enjoyed getting thoroughly
+drenched...</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -13836,7 +13845,7 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>「Ah—！ This feels so good！」</t>
+          <t>「Aaah! It feels so good!」</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13866,8 +13875,9 @@
       </c>
       <c r="B875" s="1" t="inlineStr">
         <is>
-          <t>Once you're wet, she probably thought, it doesn't
-matter how much more you get soaked—bring it on.</t>
+          <t>Once they were already wet, they probably thought,
+'It doesn't matter how much more we get soaked—bring
+it on.'</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -13912,8 +13922,8 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's initial heat seems to have cooled off, and
-along with that her body has started to chill too.</t>
+          <t>Rin-chan's momentary excitement has died down, and
+she's started to feel cold as well.</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -13974,7 +13984,7 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>「Shall we wrap things up then？」</t>
+          <t>「Shall we wrap things up, then?」</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -14051,7 +14061,7 @@
       </c>
       <c r="B887" s="1" t="inlineStr">
         <is>
-          <t>「Ehh？ Already over~？」</t>
+          <t>「Ehh? Already over~?」</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -14128,7 +14138,7 @@
       </c>
       <c r="B892" s="1" t="inlineStr">
         <is>
-          <t>「Muu~...」</t>
+          <t>「Mmm~...」</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -14174,8 +14184,8 @@
       </c>
       <c r="B895" s="1" t="inlineStr">
         <is>
-          <t>「Okay, you all go change first. I'll put this back in
-the shed.」</t>
+          <t>"Alright, everyone go change first. I'll put this
+away in the storeroom and be right back."</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -14190,7 +14200,7 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>I say that and pick up the water gun.</t>
+          <t>I said that and picked up the water gun.</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -14220,7 +14230,7 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ I'll help then！」</t>
+          <t>「Oh! I'll help, then!」</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -14296,7 +14306,7 @@
       </c>
       <c r="B903" s="1" t="inlineStr">
         <is>
-          <t>「Yesss！ Miru'll help too！」</t>
+          <t>「Yesss! Miru-chan will help too!」</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -14326,7 +14336,7 @@
       </c>
       <c r="B905" s="1" t="inlineStr">
         <is>
-          <t>「R-Rin will too...！」</t>
+          <t>R-Rin'll help too...!</t>
         </is>
       </c>
       <c r="C905" t="n">
@@ -14357,7 +14367,7 @@
       </c>
       <c r="B907" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>Hajime":""</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -14402,7 +14412,7 @@
       </c>
       <c r="B910" s="1" t="inlineStr">
         <is>
-          <t>「Then Miru will help！」</t>
+          <t>Alright, Miru will help!</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -14447,9 +14457,8 @@
       </c>
       <c r="B913" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan is the first to respond to my words, and
-Rin-chan follows, raising her hand like she's chasing
-after her.</t>
+          <t>Miru-chan is the first to react to my words, and
+Rin-chan follows suit, raising her hand as well.</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -14479,7 +14488,7 @@
       </c>
       <c r="B915" s="1" t="inlineStr">
         <is>
-          <t>「Miru will do it~！」</t>
+          <t>"I'll help~!"</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -14524,8 +14533,8 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>...Which makes it odd, because they're bumping into
-each other.</t>
+          <t>...That makes it strange, since they're all competing
+with each other.</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -14540,8 +14549,8 @@
       </c>
       <c r="B919" s="1" t="inlineStr">
         <is>
-          <t>They really did say it well: the more they fight, the
-closer they are.</t>
+          <t>As the saying goes, the more you quarrel, the closer
+you are.</t>
         </is>
       </c>
       <c r="C919" t="n">
@@ -14571,7 +14580,7 @@
       </c>
       <c r="B921" s="1" t="inlineStr">
         <is>
-          <t>「Ahem！ I, being the teacher, will go！」</t>
+          <t>Ahem! As your sensei, I'll go!</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -14617,8 +14626,8 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>「No, Great-Grandmother brought it, so of course I
-should help.」</t>
+          <t>No — since Great-Grandmother brought it, it's only
+natural that I should help.</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -14680,7 +14689,7 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>Who are you going to get to help you...？</t>
+          <t>Who should I ask to help...?</t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -14725,7 +14734,7 @@
       </c>
       <c r="B931" s="1" t="inlineStr">
         <is>
-          <t>Let's get Rin-chan to help us.</t>
+          <t>I'll ask Rin-chan to help.</t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -14740,7 +14749,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>Have Miru-chan help me</t>
+          <t>Ask Miru-chan to help</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -14770,7 +14779,7 @@
       </c>
       <c r="B934" s="1" t="inlineStr">
         <is>
-          <t>「Then, Miru-chan, help me.」</t>
+          <t>Alright then, Miru-chan, help me.</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -14800,7 +14809,7 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>「Yeah！ Then I'll hold it with you too！」</t>
+          <t>「Yeah! Then Miru will help hold it too!」</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -14846,7 +14855,7 @@
       </c>
       <c r="B939" s="1" t="inlineStr">
         <is>
-          <t>「........Ugh.」</t>
+          <t>「…Ugh.」</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -14861,8 +14870,8 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>If anything it throws off the balance, but since she
-asked, I can't exactly say no.</t>
+          <t>It'll actually throw off the balance, but since I
+asked her, I can't very well tell her not to.</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14908,9 +14917,9 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>I said that, paying attention to where Miru-chan
-stood holding one end, and then started walking with
-a heave-ho.</t>
+          <t>I said that, kept an eye on where Miru-chan, who was
+holding one end, was standing, and set off, heaving
+it along.</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -14985,8 +14994,9 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>Because Miru-chan opened the storage door, we could
-carry it in without unloading anything.</t>
+          <t>Because Miru-chan opened the storage room door for
+me, we were able to carry it in without having to set
+the load down.</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15016,7 +15026,7 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>「Now, where should we put this…」</t>
+          <t>「Now, where should I put this…」</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -15046,7 +15056,7 @@
       </c>
       <c r="B952" s="1" t="inlineStr">
         <is>
-          <t>「Hmm… hmmm？」</t>
+          <t>「Hmm... hmm?」</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -15077,8 +15087,8 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>She's probably thinking with me, but the way she
-copies me is cute.</t>
+          <t>Miru-chan's probably thinking it over with me, but
+it's cute how she ends up copying me.</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -15108,7 +15118,7 @@
       </c>
       <c r="B956" s="1" t="inlineStr">
         <is>
-          <t>「…Miru-chan, where do you think is good？」</t>
+          <t>「…Miru-chan, where do you think we should put it?」</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -15138,7 +15148,7 @@
       </c>
       <c r="B958" s="1" t="inlineStr">
         <is>
-          <t>「Nn…！？ Uh, um… maybe… there？」</t>
+          <t>「Mmm…!? Uh, um… maybe… there?」</t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -15185,8 +15195,8 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>But I already asked her, so I'll humor Miru-chan and
-do as she says.</t>
+          <t>But since I asked her, I'll defer to Miru-chan and do
+as she says.</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -15247,7 +15257,7 @@
       <c r="B965" s="1" t="inlineStr">
         <is>
           <t>If a tripod leg slipped and got caught in the door
-track, it'd be a pain the next time we opened it.</t>
+track, it'd be a hassle the next time I opened it.</t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -15308,7 +15318,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>「Close it？」</t>
+          <t>「Shall I close it?」</t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -15368,7 +15378,7 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>「Okay！ I’m closing it！」</t>
+          <t>「Okay! I'll close it!」</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15383,7 +15393,7 @@
       </c>
       <c r="B974" s="1" t="inlineStr">
         <is>
-          <t>Rattle...！</t>
+          <t>Rattle...!</t>
         </is>
       </c>
       <c r="C974" t="n">
@@ -15428,8 +15438,8 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan closed the door for me, but there was this
-awful sound...</t>
+          <t>Miru-chan closed the door for me, but I heard an
+unpleasant noise...</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -15459,7 +15469,7 @@
       </c>
       <c r="B979" s="1" t="inlineStr">
         <is>
-          <t>「Thanks. This time, try opening it.」</t>
+          <t>「Thanks. Now try opening it.」</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -15489,7 +15499,7 @@
       </c>
       <c r="B981" s="1" t="inlineStr">
         <is>
-          <t>「Heeey!　Heave—hoo...!　Heave...hoo...!」</t>
+          <t>Okay! Heave-ho...! Heave...!</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -15519,7 +15529,7 @@
       </c>
       <c r="B983" s="1" t="inlineStr">
         <is>
-          <t>「…It won't open.」</t>
+          <t>…It won't open.</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -15564,7 +15574,7 @@
       </c>
       <c r="B986" s="1" t="inlineStr">
         <is>
-          <t>「Okay, okay, sorry about that」</t>
+          <t>Okay, okay, sorry about that</t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -15579,7 +15589,7 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>On behalf of Miru-chan, I open the door.</t>
+          <t>I open the door for Miru-chan.</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -15624,7 +15634,7 @@
       </c>
       <c r="B990" s="1" t="inlineStr">
         <is>
-          <t>…Huh. It won't open？</t>
+          <t>Huh... it won't open?</t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -15654,7 +15664,7 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>「Huh? Wait — am I locked in?」</t>
+          <t>Huh? Wait — did we get locked in?</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -15684,8 +15694,7 @@
       </c>
       <c r="B994" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha, you're overreacting. It's just a little
-stiff.」</t>
+          <t>Ahaha, you're overreacting. It's just a little stiff.</t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -15700,8 +15709,8 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>I say I’m taking it easy on purpose, but really put
-my weight into trying to open the door.</t>
+          <t>I say I'm taking it easy on purpose, but I really put
+my full strength into trying to open the door.</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -15731,7 +15740,7 @@
       </c>
       <c r="B997" s="1" t="inlineStr">
         <is>
-          <t>「........！」</t>
+          <t>「…!」</t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -15746,7 +15755,7 @@
       </c>
       <c r="B998" s="1" t="inlineStr">
         <is>
-          <t>………Huh？！</t>
+          <t>...Huh?!</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -15806,8 +15815,8 @@
       </c>
       <c r="B1002" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... uh... maybe something's come loose or gone
-out of alignment...？」</t>
+          <t>Mmm... hmm... maybe the door's gotten out of
+alignment...?</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -15837,7 +15846,7 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>「…huh…fuu…uuu…！」</t>
+          <t>「…huff…ugh…!」</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -15853,8 +15862,8 @@
       <c r="B1005" s="1" t="inlineStr">
         <is>
           <t>I felt a little anxious that the door wouldn’t open,
-but optimistically thought I could just go out the
-window if it came to that.</t>
+but optimistically thought we could just get out
+through the window if it came to that.</t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -15869,8 +15878,8 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>But Miru-chan, worried the door won’t open, looks
-half on the verge of tears.</t>
+          <t>But Miru-chan, worried that the door won’t open, is
+nearly in tears.</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15945,7 +15954,7 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>That face about to cry is so cute….</t>
+          <t>That about-to-cry face is so cute...</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -15976,8 +15985,8 @@
       </c>
       <c r="B1013" s="1" t="inlineStr">
         <is>
-          <t>Energetic Miru-chan is full of healthy charm, but I
-realized her being weak like this is attractive too.</t>
+          <t>Energetic Miru-chan exudes a healthy charm, but I
+realized that her vulnerable side is attractive too.</t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -15992,7 +16001,8 @@
       </c>
       <c r="B1014" s="1" t="inlineStr">
         <is>
-          <t>Her pure fragility hits my chest with a thud.</t>
+          <t>Her pure vulnerability pierces my chest with a
+thudding jolt.</t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -16037,7 +16047,7 @@
       </c>
       <c r="B1017" s="1" t="inlineStr">
         <is>
-          <t>「Hey, Onii-chan... what are you going to do...？」</t>
+          <t>“Hey, Onii-chan... what should we do...?”</t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -16052,8 +16062,8 @@
       </c>
       <c r="B1018" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan pouts her lips into a frown and looks back
-up at me.</t>
+          <t>Miru-chan pulls her lips into a frown and looks back
+at me.</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -16113,7 +16123,7 @@
       </c>
       <c r="B1022" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ？」</t>
+          <t>「Ah...?」</t>
         </is>
       </c>
       <c r="C1022" t="n">
@@ -16143,8 +16153,8 @@
       </c>
       <c r="B1024" s="1" t="inlineStr">
         <is>
-          <t>To calm her down, physical affection like our usual
-skinship is the best.</t>
+          <t>To reassure her, it's best to give her our usual
+physical affection.</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -16159,8 +16169,8 @@
       </c>
       <c r="B1025" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan always hugs me... so I thought it would be
-good if I did this for her.</t>
+          <t>Miru-chan always hugs me too... so I thought it would
+be best to do the same for her.</t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -16190,7 +16200,7 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>「Ah... auuu...」</t>
+          <t>「Ah... aahhh...」</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -16205,7 +16215,7 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan emits a small moan.</t>
+          <t>Miru-chan lets out a small moan.</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -16220,7 +16230,7 @@
       </c>
       <c r="B1029" s="1" t="inlineStr">
         <is>
-          <t>Was hugging her the right thing to do？</t>
+          <t>Was hugging her the right thing to do?</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -16250,7 +16260,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>「...Are you calm now？」</t>
+          <t>"…Have you calmed down?"</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -16280,7 +16290,7 @@
       </c>
       <c r="B1033" s="1" t="inlineStr">
         <is>
-          <t>「Huh...？ Ah, ah... yeah...」</t>
+          <t>Eh...? A-ah... y-yeah...</t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -16327,8 +16337,8 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>Alright, as I thought, hugging you was the right
-move！</t>
+          <t>Alright, as I thought, hugging Miru-chan was the
+right move!</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -16343,9 +16353,9 @@
       </c>
       <c r="B1037" s="1" t="inlineStr">
         <is>
-          <t>I had become confident in my own judgment, but
-thought it might be a bit of a problem in a different
-sense.</t>
+          <t>I, who had gained confidence in my own judgment,
+thought it might be a little problematic in a
+different way.</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -16360,9 +16370,8 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's face is right up close, and the warmth
-and scent hit me straight in the head with a little
-jolt！</t>
+          <t>Miru-chan's face is right up close, and her warmth
+and scent send a little thrill through my head.</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16407,8 +16416,8 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>I feel like I'm doing something I shouldn't, and
-ashamed of it, I can't help averting my eyes.</t>
+          <t>I feel guilty about having these forbidden feelings,
+and I can't help but look away.</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16468,7 +16477,7 @@
       </c>
       <c r="B1045" s="1" t="inlineStr">
         <is>
-          <t>「Hah... y-yes！？」</t>
+          <t>「Ah... y-yes!?」</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16498,7 +16507,7 @@
       </c>
       <c r="B1047" s="1" t="inlineStr">
         <is>
-          <t>Even I think I'm acting strangely anxious.</t>
+          <t>Even I have to admit I'm getting oddly flustered.</t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -16513,8 +16522,7 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>It's because of these hands I've been holding like
-this.</t>
+          <t>It's because my hands are still holding her.</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -16529,8 +16537,8 @@
       </c>
       <c r="B1049" s="1" t="inlineStr">
         <is>
-          <t>I did it to put them at ease, and now that I've
-succeeded, there's no reason to keep it up forever.</t>
+          <t>I did this to calm her down, and now that it's
+worked, there's no reason to stay like this forever.</t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -16590,7 +16598,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... fu, mu—... a-choo...！」</t>
+          <t>「...Mmm... mmm... Achoo!」</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -16665,7 +16673,7 @@
       </c>
       <c r="B1058" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... you're warm... heh」</t>
+          <t>「Mmm... you're warm, aren't you... ehehe」</t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -16680,7 +16688,7 @@
       </c>
       <c r="B1059" s="1" t="inlineStr">
         <is>
-          <t>Then Miru-chan came and hugged me.</t>
+          <t>Then Miru-chan hugged me too.</t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -16727,7 +16735,7 @@
       <c r="B1062" s="1" t="inlineStr">
         <is>
           <t>I might be getting carried away by the situation and
-making a huge misunderstanding, but I might not be.</t>
+completely misreading things, but maybe I'm not.</t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -16757,8 +16765,8 @@
       </c>
       <c r="B1064" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Miru-chan... i-if we kiss, it'll get even
-warmer, you know？」</t>
+          <t>「Ah... Miru-chan... ch-chu—if I kiss you, you'll get
+even warmer, okay?」</t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -16788,7 +16796,7 @@
       </c>
       <c r="B1066" s="1" t="inlineStr">
         <is>
-          <t>「Eh...？ Ahaha, really...？」</t>
+          <t>「Eh...? Ahaha, is that so...?」</t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -16925,7 +16933,7 @@
       </c>
       <c r="B1075" s="1" t="inlineStr">
         <is>
-          <t>「O-okay then... I'm gonna...」</t>
+          <t>"O-okay then... I'll do it, okay?"</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -16955,7 +16963,7 @@
       </c>
       <c r="B1077" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ？」</t>
+          <t>「Mmm...?」</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -17000,7 +17008,7 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnfuu...」</t>
+          <t>「Nn... n, nfuuh...」</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -17015,8 +17023,8 @@
       </c>
       <c r="B1081" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan twitched, but she just let out a small
-breath and bore it.</t>
+          <t>Miru-chan flinched, but she endured it with only a
+light exhale.</t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -17106,7 +17114,7 @@
       </c>
       <c r="B1087" s="1" t="inlineStr">
         <is>
-          <t>「Fuu, faaa... ah, au... u, uuu...」</t>
+          <t>「Fuu, faaah... ah, auh... uh, uuu...」</t>
         </is>
       </c>
       <c r="C1087" t="n">
@@ -17121,7 +17129,8 @@
       </c>
       <c r="B1088" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan stayed still, letting out shy little sighs.</t>
+          <t>Miru-chan remained still, letting out a quiet,
+restrained sigh.</t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -17182,7 +17191,7 @@
       </c>
       <c r="B1092" s="1" t="inlineStr">
         <is>
-          <t>「Umu... ugh, nnn...！」</t>
+          <t>Mmm... uh, nnn...!</t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -17197,8 +17206,8 @@
       </c>
       <c r="B1093" s="1" t="inlineStr">
         <is>
-          <t>When I pressed my lips harder in the heat of the
-moment, Miru-chan shook her head in a little no-no.</t>
+          <t>When I pressed my lips hard on impulse, Miru-chan
+shook her head and protested, "No, no."</t>
         </is>
       </c>
       <c r="C1093" t="n">
@@ -17228,7 +17237,7 @@
       </c>
       <c r="B1095" s="1" t="inlineStr">
         <is>
-          <t>I thought that and pulled my face back.</t>
+          <t>Thinking that, I pulled back.</t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -17289,8 +17298,8 @@
       </c>
       <c r="B1099" s="1" t="inlineStr">
         <is>
-          <t>「Fa... ah, aaah...？ Afu, nmu... nn！ Nn... fu, fa...
-ah！」</t>
+          <t>"Fah... ah, aaah...? Ah... nmm... nn! Nn... fuh,
+fah... ah!"</t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -17368,7 +17377,7 @@
       </c>
       <c r="B1104" s="1" t="inlineStr">
         <is>
-          <t>「Amuu, rero, rerorero...！」</t>
+          <t>「Amuu, rero, rerorero...!」</t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -17398,7 +17407,7 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nmu... nn, nnu~... nn~...」</t>
+          <t>「Nn... nmu... nn... nnu~... nn~...」</t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -17429,8 +17438,8 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>I see a childlike innocence in the lips she presses
-together so tightly.</t>
+          <t>I see a childlike innocence in Miru-chan's tightly
+pressed lips.</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -17445,7 +17454,7 @@
       </c>
       <c r="B1109" s="1" t="inlineStr">
         <is>
-          <t>Ah... I can't stand it, Miru-chan！</t>
+          <t>Ah... I can't resist it, Miru-chan!</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -17475,7 +17484,7 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>「Lero, lerolerolerorero...！」</t>
+          <t>"rero, rerorerorerero...!"</t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -17505,7 +17514,7 @@
       </c>
       <c r="B1113" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn, nnnn... Nn-ah！」</t>
+          <t>Nn... nn... nnnn... Nn-ah...!</t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -17551,7 +17560,7 @@
       </c>
       <c r="B1116" s="1" t="inlineStr">
         <is>
-          <t>「Nnya... Onii-chan... this... ah！？」</t>
+          <t>Nn— Onii-chan... this— ah!?</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -17567,7 +17576,7 @@
       <c r="B1117" s="1" t="inlineStr">
         <is>
           <t>Miru-chan started to say something, but I
-deliberately slid my tongue between.</t>
+deliberately slid my tongue into her mouth.</t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -17612,8 +17621,7 @@
       </c>
       <c r="B1120" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nha... ah！ Ah, afuu, nn！ Yaa... ah！ Ah,
-afu...！」</t>
+          <t>Nn... nna... ah! Ah, ahh, nn! Yaa... ah! Ah, ahh...!</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -17628,7 +17636,7 @@
       </c>
       <c r="B1121" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, toyed with by my tongue, let out ragged
+          <t>Toyed with by my tongue, Miru-chan lets out ragged
 breaths.</t>
         </is>
       </c>
@@ -17644,8 +17652,8 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>But why does it feel like all the strength has
-drained from her body...？</t>
+          <t>But why has all the strength drained from her
+body...?</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17675,7 +17683,7 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Miru-chan...」</t>
+          <t>Ah... Miru-chan...</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -17705,7 +17713,7 @@
       </c>
       <c r="B1126" s="1" t="inlineStr">
         <is>
-          <t>「Nnff... Onii, hyan... fua！？」</t>
+          <t>Nnff... Onii-chan, hyan... fua!?</t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -17720,7 +17728,8 @@
       </c>
       <c r="B1127" s="1" t="inlineStr">
         <is>
-          <t>When our tongues met, Miru-chan's voice bounced up.</t>
+          <t>When our tongues met, Miru-chan let out a small,
+startled sound.</t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -17735,7 +17744,8 @@
       </c>
       <c r="B1128" s="1" t="inlineStr">
         <is>
-          <t>Feeling that response, I pushed my tongue in harder.</t>
+          <t>Feeling that response in her voice, I forced my
+tongue in even more forcefully.</t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -17765,8 +17775,8 @@
       </c>
       <c r="B1130" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh... nna, chu, chuku！ Nnffu... chu, chuku！ Ppu,
-uuu...！」</t>
+          <t>「Nn... nna, smooch, smuck! Nnff... smooch, smuck!
+Pff, uuh...!」</t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -17781,8 +17791,8 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>The tongues' mucous membranes tangled and the sound
-of saliva popping rang out.</t>
+          <t>The mucous membranes of our tongues intertwined, and
+the sound of saliva popping could be heard.</t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -17858,8 +17868,8 @@
       </c>
       <c r="B1136" s="1" t="inlineStr">
         <is>
-          <t>「chu, chuku！ n, n...！ faa... chu, chuku！ npu！ fuu,
-fuuu...！」</t>
+          <t>「Chu, chuku! Nn, nn...! Faa... chu, chuku! Npu! Fuu,
+fuuu...!」</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -17874,7 +17884,7 @@
       </c>
       <c r="B1137" s="1" t="inlineStr">
         <is>
-          <t>...As expected, Miru-chan still reacts to the sounds.</t>
+          <t>...As I thought, Miru-chan reacts to the sound.</t>
         </is>
       </c>
       <c r="C1137" t="n">
@@ -17889,7 +17899,7 @@
       </c>
       <c r="B1138" s="1" t="inlineStr">
         <is>
-          <t>At that moment, is she feeling embarrassed, I wonder?</t>
+          <t>I wonder if she was embarrassed at that moment.</t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -17904,8 +17914,8 @@
       </c>
       <c r="B1139" s="1" t="inlineStr">
         <is>
-          <t>But on the other hand, she doesn't seem to dislike
-our tongues tangling.</t>
+          <t>But on the other hand, she doesn't mind our tongues
+being entwined.</t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -17920,7 +17930,7 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>Is she thinking it's pleasurable... maybe？</t>
+          <t>I wonder if Miru-chan is enjoying this...</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -17950,8 +17960,8 @@
       </c>
       <c r="B1142" s="1" t="inlineStr">
         <is>
-          <t>「chu, chuku！ n, fuu...！ ah, afu... n, nnn！ faa...
-aa...！」</t>
+          <t>「chu, chuku! n, fuu...! ah, afu... n, nn! faa...
+aa...!」</t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -17981,7 +17991,7 @@
       </c>
       <c r="B1144" s="1" t="inlineStr">
         <is>
-          <t>「chu, chu........！」</t>
+          <t>「chu, chu...!」</t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -17996,8 +18006,8 @@
       </c>
       <c r="B1145" s="1" t="inlineStr">
         <is>
-          <t>When I opened my eyes a little, Miru-chan had her
-half-open eyes all glazed over.</t>
+          <t>When I squinted and looked, Miru-chan's half-open
+eyes were glazed.</t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -18012,7 +18022,7 @@
       </c>
       <c r="B1146" s="1" t="inlineStr">
         <is>
-          <t>She must be enjoying the kiss itself.</t>
+          <t>Miru-chan must be enjoying the kiss itself.</t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -18057,8 +18067,8 @@
       </c>
       <c r="B1149" s="1" t="inlineStr">
         <is>
-          <t>「aah...! fu, n'aah... afuu, aa...! oni,
-onii-chaaaan...!!」</t>
+          <t>「aah...! fu, n'aah... afu, aa...! Onii,
+Onii-chaaaan...!!」</t>
         </is>
       </c>
       <c r="C1149" t="n">
@@ -18073,8 +18083,8 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>Getting carried away by kissing, Miru-chan called me
-while panting heavily.</t>
+          <t>I got carried away and was teasing her with kisses
+when Miru-chan, panting heavily, called out to me.</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -18089,8 +18099,8 @@
       </c>
       <c r="B1151" s="1" t="inlineStr">
         <is>
-          <t>This was the third time she'd called me during a
-kiss.</t>
+          <t>This was the third time Miru-chan had called me in
+the middle of a kiss.</t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -18120,8 +18130,8 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>...Reluctantly, I pulled my tongue back and drew my
-face away.</t>
+          <t>...Reluctantly, I retracted my tongue and pulled my
+face back.</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -18197,7 +18207,7 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>「Ah... could it have been hard for you？」</t>
+          <t>"Ah... were you uncomfortable?"</t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -18227,7 +18237,7 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>「fuu, fuu... u, uun, I'm okay...」</t>
+          <t>「Pant, pant... N-no, I'm okay...」</t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -18242,7 +18252,7 @@
       </c>
       <c r="B1161" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan said that with an embarrassed smile.</t>
+          <t>Miru-chan said that with a wry smile.</t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -18257,8 +18267,7 @@
       </c>
       <c r="B1162" s="1" t="inlineStr">
         <is>
-          <t>Ah... did I get a little carried away and selfish
-there？</t>
+          <t>Ah... was I being a bit selfish just now?</t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -18334,7 +18343,8 @@
       </c>
       <c r="B1167" s="1" t="inlineStr">
         <is>
-          <t>「Miru, I gave Onii-chan a grown-up kiss... ehehe！」</t>
+          <t>"Miru just had an adult kiss with Onii-chan...
+ehehe!"</t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -18349,7 +18359,7 @@
       </c>
       <c r="B1168" s="1" t="inlineStr">
         <is>
-          <t>And, she smiles bashfully...</t>
+          <t>Then Miru-chan smiles bashfully...</t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -18411,7 +18421,7 @@
       </c>
       <c r="B1172" s="1" t="inlineStr">
         <is>
-          <t>「………………hh—aaah！」</t>
+          <t>「………………ahhh—！」</t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -18517,7 +18527,7 @@
       <c r="B1179" s="1" t="inlineStr">
         <is>
           <t>But the next moment I remembered the kiss with
-Miru-chan and felt happy.</t>
+Miru-chan and couldn't help feeling happy.</t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -18532,8 +18542,8 @@
       </c>
       <c r="B1180" s="1" t="inlineStr">
         <is>
-          <t>With this kind of mood, would it be okay to ask for
-another kiss？</t>
+          <t>Given this mood, would it be okay to say 'Let's kiss
+again'?</t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -18578,7 +18588,7 @@
       </c>
       <c r="B1183" s="1" t="inlineStr">
         <is>
-          <t>「Nnu~？ Oniii~chan！？ What's up~？」</t>
+          <t>Mmm~? Onii-chan~!? What's the matter~?</t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -18593,8 +18603,8 @@
       </c>
       <c r="B1184" s="1" t="inlineStr">
         <is>
-          <t>When I stayed quiet, Miru-chan got all cocky and said
-it in a teasing tone.</t>
+          <t>When I stayed silent, Miru-chan got a little cocky
+and said it in a teasing tone.</t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -18609,7 +18619,7 @@
       </c>
       <c r="B1185" s="1" t="inlineStr">
         <is>
-          <t>Yeah, this atmosphere... is good.</t>
+          <t>Yeah... this atmosphere is nice.</t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -18715,8 +18725,8 @@
       </c>
       <c r="B1192" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought so, the faint expression faded
-into a blank, emotionless face.</t>
+          <t>No sooner had I thought that than her faint
+expression shifted into a blank, expressionless look.</t>
         </is>
       </c>
       <c r="C1192" t="n">
@@ -18746,7 +18756,7 @@
       </c>
       <c r="B1194" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！ N-no, that's not it！？ It's nothing！？」</t>
+          <t>Ah...! N-no, that's not it!? It's nothing!?</t>
         </is>
       </c>
       <c r="C1194" t="n">
@@ -18776,8 +18786,8 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>...But the more she does, the more suspicious it
-actually looks.</t>
+          <t>...But no matter how you look at it, it just looks
+more suspicious.</t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -18839,7 +18849,7 @@
       </c>
       <c r="B1200" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah！ I was in trouble, really！？」</t>
+          <t>「Y-yeah! I was in trouble, okay!?」</t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -18885,7 +18895,7 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>「Man, as expected of Rin-chan！ Good, good！」</t>
+          <t>"Phew— as expected of Rin-chan! Thank goodness!"</t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -18915,7 +18925,7 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>「...The door opened totally normally, though？」</t>
+          <t>「...The door just opened normally, though?」</t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -18960,8 +18970,8 @@
       </c>
       <c r="B1208" s="1" t="inlineStr">
         <is>
-          <t>Hit by Rin-chan's cold tone, I looked again at the
-storage door.</t>
+          <t>Taken aback by Rin-chan's cold tone, I took another
+look at the door to the storage room.</t>
         </is>
       </c>
       <c r="C1208" t="n">
@@ -19022,9 +19032,9 @@
       </c>
       <c r="B1212" s="1" t="inlineStr">
         <is>
-          <t>「From the outside you can push the handle to unlock
-it, and from the inside you can just lift the latch
-to open it easily.」</t>
+          <t>From the outside it releases if you push the handle,
+and from the inside you can easily open it by lifting
+the knob.</t>
         </is>
       </c>
       <c r="C1212" t="n">
@@ -19054,7 +19064,7 @@
       </c>
       <c r="B1214" s="1" t="inlineStr">
         <is>
-          <t>「Gah, jeez... Onii-chan, you're so careless~」</t>
+          <t>Ah, geez... Onii-chan, you're so careless~</t>
         </is>
       </c>
       <c r="C1214" t="n">
@@ -19069,8 +19079,8 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>As I said that to sort out the situation, Miru-chan
-jumped back in.</t>
+          <t>When I voiced the situation to sort things out,
+Miru-chan jumped in again.</t>
         </is>
       </c>
       <c r="C1215" t="n">
@@ -19130,7 +19140,7 @@
       </c>
       <c r="B1219" s="1" t="inlineStr">
         <is>
-          <t>Sketchy... Rin-chan's eyes seemed to say.</t>
+          <t>Fishy... Rin-chan's eyes said as much.</t>
         </is>
       </c>
       <c r="C1219" t="n">
@@ -19191,7 +19201,7 @@
       </c>
       <c r="B1223" s="1" t="inlineStr">
         <is>
-          <t>「O-okay！」</t>
+          <t>「Y-yes!」</t>
         </is>
       </c>
       <c r="C1223" t="n">
@@ -19236,7 +19246,7 @@
       </c>
       <c r="B1226" s="1" t="inlineStr">
         <is>
-          <t>「W-well then, I should probably get changed too...」</t>
+          <t>"W-well then, I should probably go change too..."</t>
         </is>
       </c>
       <c r="C1226" t="n">
@@ -19251,8 +19261,8 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>I left the storage and shut the door, murmuring that
-to myself.</t>
+          <t>I left the storage room and closed the door,
+muttering that to myself.</t>
         </is>
       </c>
       <c r="C1227" t="n">
@@ -19297,8 +19307,8 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is still staring at me, all intent-like as
-ever.</t>
+          <t>Rin-chan was still staring at me with that cold,
+glowering look.</t>
         </is>
       </c>
       <c r="C1230" t="n">
@@ -19313,9 +19323,8 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>It's less troublesome than having her ask a bunch of
-questions, but on the other hand it really hits me
-hard mentally….</t>
+          <t>It's less of a hassle than being asked a bunch of
+questions, but it really weighs on me emotionally...</t>
         </is>
       </c>
       <c r="C1231" t="n">
@@ -19360,7 +19369,7 @@
       </c>
       <c r="B1234" s="1" t="inlineStr">
         <is>
-          <t>「Ah…Rin-chan, thanks. Ahaha…」</t>
+          <t>Ah…Rin-chan, thanks. Ahaha…</t>
         </is>
       </c>
       <c r="C1234" t="n">
@@ -19406,7 +19415,7 @@
       </c>
       <c r="B1237" s="1" t="inlineStr">
         <is>
-          <t>「…Heh！」</t>
+          <t>…There!</t>
         </is>
       </c>
       <c r="C1237" t="n">
@@ -19421,7 +19430,7 @@
       </c>
       <c r="B1238" s="1" t="inlineStr">
         <is>
-          <t>Then Rin-chan kicked the back of my knee…</t>
+          <t>Then Rin-chan kicked me in the back of the knee…</t>
         </is>
       </c>
       <c r="C1238" t="n">
@@ -19451,7 +19460,7 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>「Well then, shall I have Rin-chan help me？」</t>
+          <t>Then maybe I'll have Rin-chan help me?</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19481,7 +19490,7 @@
       </c>
       <c r="B1242" s="1" t="inlineStr">
         <is>
-          <t>「Okay. Mufuu…！」</t>
+          <t>Okay. Heh heh…!</t>
         </is>
       </c>
       <c r="C1242" t="n">
@@ -19512,8 +19521,9 @@
       </c>
       <c r="B1244" s="1" t="inlineStr">
         <is>
-          <t>Even if the fired-up feeling immediately fizzled out,
-I appreciated the fact she wanted to help.</t>
+          <t>Even if the enthusiasm Rin-chan put in immediately
+drained away, that's forgivable; I appreciated her
+willingness to help.</t>
         </is>
       </c>
       <c r="C1244" t="n">
@@ -19543,8 +19553,8 @@
       </c>
       <c r="B1246" s="1" t="inlineStr">
         <is>
-          <t>「I'll go put these away, everyone else go change
-first.」</t>
+          <t>I'll go put these away — everyone else, go change
+first.</t>
         </is>
       </c>
       <c r="C1246" t="n">
@@ -19574,7 +19584,7 @@
       </c>
       <c r="B1248" s="1" t="inlineStr">
         <is>
-          <t>「Rin-chan, come with me, okay?」</t>
+          <t>Rin-chan, come with me, okay?</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -19604,7 +19614,7 @@
       </c>
       <c r="B1250" s="1" t="inlineStr">
         <is>
-          <t>「Ryo-kai~」</t>
+          <t>Got it~</t>
         </is>
       </c>
       <c r="C1250" t="n">
@@ -19634,7 +19644,7 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>「Niini, the storage's open…！」</t>
+          <t>Niini, the storeroom's open…！</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -19664,7 +19674,7 @@
       </c>
       <c r="B1254" s="1" t="inlineStr">
         <is>
-          <t>「Alright, then I'll bring them in.」</t>
+          <t>Alright, then I'll bring them in.</t>
         </is>
       </c>
       <c r="C1254" t="n">
@@ -19679,9 +19689,9 @@
       </c>
       <c r="B1255" s="1" t="inlineStr">
         <is>
-          <t>Because Rin-chan opened the storage door for me, I
-was able to carry things in smoothly without putting
-them down.</t>
+          <t>Thanks to Rin-chan opening the storage door, I was
+able to bring everything in smoothly without having
+to set it down.</t>
         </is>
       </c>
       <c r="C1255" t="n">
@@ -19711,7 +19721,7 @@
       </c>
       <c r="B1257" s="1" t="inlineStr">
         <is>
-          <t>「Now, where should I put these…?」</t>
+          <t>Well, where should I put these away…?</t>
         </is>
       </c>
       <c r="C1257" t="n">
@@ -19741,7 +19751,7 @@
       </c>
       <c r="B1259" s="1" t="inlineStr">
         <is>
-          <t>「There's a spot right there.」</t>
+          <t>There's a spot right there.</t>
         </is>
       </c>
       <c r="C1259" t="n">
@@ -19772,8 +19782,8 @@
       </c>
       <c r="B1261" s="1" t="inlineStr">
         <is>
-          <t>It’s true that nothing’s placed there, but it’s near
-the entrance so it’s not a very good spot, is it?</t>
+          <t>Admittedly there’s nothing there, but it’s near the
+entrance, so it’s probably not a very good spot.</t>
         </is>
       </c>
       <c r="C1261" t="n">
@@ -19863,7 +19873,8 @@
       </c>
       <c r="B1267" s="1" t="inlineStr">
         <is>
-          <t>Ugh... I ended up denying it by my own standards.</t>
+          <t>Ugh... I couldn't help but dismiss it based on my own
+standards.</t>
         </is>
       </c>
       <c r="C1267" t="n">
@@ -19893,7 +19904,7 @@
       </c>
       <c r="B1269" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ But let’s try putting it there for now…！」</t>
+          <t>"Ah! But let's try putting them there for now...!"</t>
         </is>
       </c>
       <c r="C1269" t="n">
@@ -19955,7 +19966,7 @@
       </c>
       <c r="B1273" s="1" t="inlineStr">
         <is>
-          <t>「Oh… we managed to put it…！」</t>
+          <t>"Oh... you got it in...!"</t>
         </is>
       </c>
       <c r="C1273" t="n">
@@ -19985,7 +19996,7 @@
       </c>
       <c r="B1275" s="1" t="inlineStr">
         <is>
-          <t>「Yeah… you got it in…」</t>
+          <t>"Yeah... we managed to get it in..."</t>
         </is>
       </c>
       <c r="C1275" t="n">
@@ -20030,7 +20041,7 @@
       </c>
       <c r="B1278" s="1" t="inlineStr">
         <is>
-          <t>「...So, it's no good after all？」</t>
+          <t>「...Is it still no good?」</t>
         </is>
       </c>
       <c r="C1278" t="n">
@@ -20060,8 +20071,8 @@
       </c>
       <c r="B1280" s="1" t="inlineStr">
         <is>
-          <t>Because they denied it at first, they probably
-convinced themselves it wouldn't work.</t>
+          <t>Because I dismissed it at first, Rin-chan probably
+convinced herself it wouldn't work.</t>
         </is>
       </c>
       <c r="C1280" t="n">
@@ -20106,9 +20117,9 @@
       </c>
       <c r="B1283" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... with this, the vibration from closing the
-door could shift the tripod legs and they might get
-jammed in the rail.」</t>
+          <t>「Hmm... as it is, the vibration when the door closes
+could shift the tripod's legs and cause them to get
+stuck in the rail.」</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -20153,7 +20164,7 @@
       </c>
       <c r="B1286" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan asks back, but it's hard to explain...</t>
+          <t>Rin-chan asked again, but it was hard to explain...</t>
         </is>
       </c>
       <c r="C1286" t="n">
@@ -20183,7 +20194,7 @@
       </c>
       <c r="B1288" s="1" t="inlineStr">
         <is>
-          <t>「In short, it's like this. First, I'll close the
+          <t>「Basically, here's what I mean. First, I'll close the
 door.」</t>
         </is>
       </c>
@@ -20199,7 +20210,7 @@
       </c>
       <c r="B1289" s="1" t="inlineStr">
         <is>
-          <t>Clunk...！</t>
+          <t>Clunk...!</t>
         </is>
       </c>
       <c r="C1289" t="n">
@@ -20214,8 +20225,8 @@
       </c>
       <c r="B1290" s="1" t="inlineStr">
         <is>
-          <t>I closed the storeroom door and then actually moved
-the tripod, shifting it to show.</t>
+          <t>I closed the storeroom door, then actually moved the
+tripod to demonstrate how it would shift.</t>
         </is>
       </c>
       <c r="C1290" t="n">
@@ -20245,8 +20256,8 @@
       </c>
       <c r="B1292" s="1" t="inlineStr">
         <is>
-          <t>「See？ If there isn't enough proper space, your leg
-might get caught in this rail.」</t>
+          <t>See? If there isn't enough clearance, the tripod's
+legs might get caught in this rail.</t>
         </is>
       </c>
       <c r="C1292" t="n">
@@ -20276,7 +20287,7 @@
       </c>
       <c r="B1294" s="1" t="inlineStr">
         <is>
-          <t>「Ho... I see.」</t>
+          <t>「Oh... I see.」</t>
         </is>
       </c>
       <c r="C1294" t="n">
@@ -20322,7 +20333,7 @@
       </c>
       <c r="B1297" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... ah, if I adjust the angle... like this.」</t>
+          <t>Mmm... ah, if I adjust the angle... like this.</t>
         </is>
       </c>
       <c r="C1297" t="n">
@@ -20337,9 +20348,9 @@
       </c>
       <c r="B1298" s="1" t="inlineStr">
         <is>
-          <t>I adjusted my legs so they wouldn't get stuck in the
-door rail, then gave the water gun a bit of a rough
-shake.</t>
+          <t>I adjusted the tripod legs to an angle so they
+wouldn't get caught in the door rail, then gave the
+water gun a bit of a rough shake.</t>
         </is>
       </c>
       <c r="C1298" t="n">
@@ -20400,8 +20411,8 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>More than that, I want to change out of these soaking
-wet clothes right now...</t>
+          <t>Right now, I want to change out of these soaking wet
+clothes...</t>
         </is>
       </c>
       <c r="C1302" t="n">
@@ -20477,8 +20488,8 @@
       </c>
       <c r="B1307" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's sudden words were so unexpected that I
-stupidly asked back like an idiot.</t>
+          <t>Rin-chan's sudden remark was so unexpected that I
+couldn't help asking back, sounding like an idiot.</t>
         </is>
       </c>
       <c r="C1307" t="n">
@@ -20508,7 +20519,7 @@
       </c>
       <c r="B1309" s="1" t="inlineStr">
         <is>
-          <t>「…huh, ugh…」</t>
+          <t>「…huff…ugh…」</t>
         </is>
       </c>
       <c r="C1309" t="n">
@@ -20539,7 +20550,7 @@
       </c>
       <c r="B1311" s="1" t="inlineStr">
         <is>
-          <t>But I could understand what Rin-chan was imagining.</t>
+          <t>But I could tell what Rin-chan was imagining.</t>
         </is>
       </c>
       <c r="C1311" t="n">
@@ -20554,8 +20565,8 @@
       </c>
       <c r="B1312" s="1" t="inlineStr">
         <is>
-          <t>What she meant was the whole
-make-out-in-the-PE-storage-room kind of scenario.</t>
+          <t>What Rin-chan meant was the whole 'making out in the
+gym storage room' kind of scenario.</t>
         </is>
       </c>
       <c r="C1312" t="n">
@@ -20630,8 +20641,8 @@
       </c>
       <c r="B1317" s="1" t="inlineStr">
         <is>
-          <t>My expectations swelled, and I ended up blurting out
-something she probably didn't want to be told…</t>
+          <t>My excitement swelled, and I couldn't help blurting
+out words Rin-chan probably wouldn't want to hear…</t>
         </is>
       </c>
       <c r="C1317" t="n">
@@ -20707,7 +20718,7 @@
       </c>
       <c r="B1322" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... u, uuuh... fushu~...」</t>
+          <t>「Mmm... u, uuuuh... psshh...」</t>
         </is>
       </c>
       <c r="C1322" t="n">
@@ -20722,8 +20733,8 @@
       </c>
       <c r="B1323" s="1" t="inlineStr">
         <is>
-          <t>But that show of spirit instantly deflated like a
-balloon with the air let out.</t>
+          <t>But that burst of bravado deflated instantly, like a
+balloon that had lost its air.</t>
         </is>
       </c>
       <c r="C1323" t="n">
@@ -20738,7 +20749,7 @@
       </c>
       <c r="B1324" s="1" t="inlineStr">
         <is>
-          <t>...That was a mistake.</t>
+          <t>...That was a failure.</t>
         </is>
       </c>
       <c r="C1324" t="n">
@@ -20753,8 +20764,8 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is a bit curious, but she's shy, so she
-hates being poked at like that.</t>
+          <t>Rin-chan's a little curious, but she's shy, so she
+doesn't like being pressed on that subject.</t>
         </is>
       </c>
       <c r="C1325" t="n">
@@ -20769,8 +20780,8 @@
       </c>
       <c r="B1326" s="1" t="inlineStr">
         <is>
-          <t>Hmm, in that case, maybe it's best to pretend I heard
-nothing and act like usual？</t>
+          <t>Hmm, maybe it's best to pretend I didn't hear
+anything and just act as usual?</t>
         </is>
       </c>
       <c r="C1326" t="n">
@@ -20785,7 +20796,8 @@
       </c>
       <c r="B1327" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I composed my expression.</t>
+          <t>With that thought in mind, I put on a neutral
+expression.</t>
         </is>
       </c>
       <c r="C1327" t="n">
@@ -20830,7 +20842,7 @@
       </c>
       <c r="B1330" s="1" t="inlineStr">
         <is>
-          <t>And then, Rin-chan sneezes.</t>
+          <t>Then Rin-chan sneezed.</t>
         </is>
       </c>
       <c r="C1330" t="n">
@@ -20845,7 +20857,8 @@
       </c>
       <c r="B1331" s="1" t="inlineStr">
         <is>
-          <t>She got soaked solid in that water-gun fight, huh…….</t>
+          <t>Rin-chan got completely soaked in that water-gun
+fight, huh...</t>
         </is>
       </c>
       <c r="C1331" t="n">
@@ -20890,7 +20903,7 @@
       </c>
       <c r="B1334" s="1" t="inlineStr">
         <is>
-          <t>Seizing the chance, I said that and urged Rin-chan
+          <t>Seizing the opportunity, I said so and urged Rin-chan
 on.</t>
         </is>
       </c>
@@ -20936,7 +20949,7 @@
       </c>
       <c r="B1337" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan glares at me with a deadpan look.</t>
+          <t>Rin-chan gives me a sullen stare.</t>
         </is>
       </c>
       <c r="C1337" t="n">
@@ -20951,8 +20964,8 @@
       </c>
       <c r="B1338" s="1" t="inlineStr">
         <is>
-          <t>Huh？ Did I say something weird？ I thought I was only
-saying something totally harmless...</t>
+          <t>Huh? Did I say something strange? I thought I had
+only said something pretty harmless...</t>
         </is>
       </c>
       <c r="C1338" t="n">
@@ -20967,7 +20980,7 @@
       </c>
       <c r="B1339" s="1" t="inlineStr">
         <is>
-          <t>As I thought that, Rin-chan opened her mouth.</t>
+          <t>As I was thinking that, Rin-chan opened her mouth.</t>
         </is>
       </c>
       <c r="C1339" t="n">
@@ -21012,7 +21025,7 @@
       </c>
       <c r="B1342" s="1" t="inlineStr">
         <is>
-          <t>Then she dives into my chest.</t>
+          <t>Then Rin-chan throws herself into my arms.</t>
         </is>
       </c>
       <c r="C1342" t="n">
@@ -21027,8 +21040,7 @@
       </c>
       <c r="B1343" s="1" t="inlineStr">
         <is>
-          <t>Huh, isn’t this situation... actually really
-great...？</t>
+          <t>Wait, isn't this a really good situation...?</t>
         </is>
       </c>
       <c r="C1343" t="n">
@@ -21043,7 +21055,7 @@
       </c>
       <c r="B1344" s="1" t="inlineStr">
         <is>
-          <t>But if another girl saw us...！</t>
+          <t>But what if another girl saw us...!</t>
         </is>
       </c>
       <c r="C1344" t="n">
@@ -21058,7 +21070,7 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I turn my gaze toward the door.</t>
+          <t>I turned my gaze toward the door.</t>
         </is>
       </c>
       <c r="C1345" t="n">
@@ -21119,7 +21131,7 @@
       <c r="B1349" s="1" t="inlineStr">
         <is>
           <t>At that moment, I noticed that Rin-chan's gaze had
-drifted toward the door.</t>
+also drifted toward the door.</t>
         </is>
       </c>
       <c r="C1349" t="n">
@@ -21134,7 +21146,7 @@
       </c>
       <c r="B1350" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is conscious of it the same way I am...！？</t>
+          <t>Rin-chan is just as aware of it as I am...!?</t>
         </is>
       </c>
       <c r="C1350" t="n">
@@ -21239,8 +21251,8 @@
       </c>
       <c r="B1357" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan suddenly pulled away from me and turned her
-face away.</t>
+          <t>Rin-chan suddenly pulled away from me and looked
+away.</t>
         </is>
       </c>
       <c r="C1357" t="n">
@@ -21270,7 +21282,7 @@
       </c>
       <c r="B1359" s="1" t="inlineStr">
         <is>
-          <t>「E... eeeehhh...？!」</t>
+          <t>「Eh... eeeehhh...?!」</t>
         </is>
       </c>
       <c r="C1359" t="n">
@@ -21285,7 +21297,8 @@
       </c>
       <c r="B1360" s="1" t="inlineStr">
         <is>
-          <t>I get completely thrown off and obviously frustrated.</t>
+          <t>I'm left hanging and can't help but show how
+frustrated I am.</t>
         </is>
       </c>
       <c r="C1360" t="n">
@@ -21300,8 +21313,7 @@
       </c>
       <c r="B1361" s="1" t="inlineStr">
         <is>
-          <t>Because, just a little while ago it was going so
-well...</t>
+          <t>But it was going so well just a moment ago...</t>
         </is>
       </c>
       <c r="C1361" t="n">
@@ -21331,7 +21343,7 @@
       </c>
       <c r="B1363" s="1" t="inlineStr">
         <is>
-          <t>「Mufu... hey, Niini？ Did you want to kiss？」</t>
+          <t>Hehe... What is it, Niini? Did you want to kiss me?</t>
         </is>
       </c>
       <c r="C1363" t="n">
@@ -21376,8 +21388,8 @@
       </c>
       <c r="B1366" s="1" t="inlineStr">
         <is>
-          <t>She hits the nail on the head about my feelings and
-grins, and I have no words left.</t>
+          <t>Rin-chan nails what I'm feeling and grins, so I have
+nothing left to say.</t>
         </is>
       </c>
       <c r="C1366" t="n">
@@ -21392,7 +21404,7 @@
       </c>
       <c r="B1367" s="1" t="inlineStr">
         <is>
-          <t>...But when you flip it around, that means...</t>
+          <t>...But if you look at it the other way, that means...</t>
         </is>
       </c>
       <c r="C1367" t="n">
@@ -21422,7 +21434,7 @@
       </c>
       <c r="B1369" s="1" t="inlineStr">
         <is>
-          <t>「...Why did you think I meant 'kiss'？」</t>
+          <t>「'Kiss'? Why would you think that?」</t>
         </is>
       </c>
       <c r="C1369" t="n">
@@ -21452,7 +21464,7 @@
       </c>
       <c r="B1371" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！？ Nn, guuu...！」</t>
+          <t>「Nn...!? Nngh...!」</t>
         </is>
       </c>
       <c r="C1371" t="n">
@@ -21467,8 +21479,8 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>When I turn the question back on her, Rin-chan gets
-stuck for words too.</t>
+          <t>When I turn the question back on her, Rin-chan is at
+a loss for words too.</t>
         </is>
       </c>
       <c r="C1372" t="n">
@@ -21498,7 +21510,7 @@
       </c>
       <c r="B1374" s="1" t="inlineStr">
         <is>
-          <t>「Well, that's how it is in manga... right...?」</t>
+          <t>Well, that's how it goes in manga, right...?</t>
         </is>
       </c>
       <c r="C1374" t="n">
@@ -21528,7 +21540,7 @@
       </c>
       <c r="B1376" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah, that's it！ That's what I meant.」</t>
+          <t>「Y-yeah, that's it! That's what I wanted to say.」</t>
         </is>
       </c>
       <c r="C1376" t="n">
@@ -21559,8 +21571,8 @@
       </c>
       <c r="B1378" s="1" t="inlineStr">
         <is>
-          <t>But her cheeks are pink — is she actually thinking
-about a kiss...？</t>
+          <t>But Rin-chan's cheeks are flushed — could it be that
+she's thinking about a kiss...?</t>
         </is>
       </c>
       <c r="C1378" t="n">
@@ -21590,7 +21602,7 @@
       </c>
       <c r="B1380" s="1" t="inlineStr">
         <is>
-          <t>「S-so... want to try it like in the manga？」</t>
+          <t>"W-wanna try doing it like in the manga?"</t>
         </is>
       </c>
       <c r="C1380" t="n">
@@ -21650,8 +21662,8 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>「I mean, like, in the empty gym storeroom, secretly,
-a smooch.」</t>
+          <t>"So—secretly, a kiss in the deserted gym storage
+room."</t>
         </is>
       </c>
       <c r="C1384" t="n">
@@ -21681,7 +21693,7 @@
       </c>
       <c r="B1386" s="1" t="inlineStr">
         <is>
-          <t>「Nnng... nfuuh！」</t>
+          <t>「Nn... nfuuh!」</t>
         </is>
       </c>
       <c r="C1386" t="n">
@@ -21696,7 +21708,7 @@
       </c>
       <c r="B1387" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's tension quietly rises.</t>
+          <t>Rin-chan's excitement quietly rises.</t>
         </is>
       </c>
       <c r="C1387" t="n">
@@ -21711,7 +21723,8 @@
       </c>
       <c r="B1388" s="1" t="inlineStr">
         <is>
-          <t>She's pretending to be mad, but probably not...</t>
+          <t>Rin-chan's pretending to be angry, but probably
+not...</t>
         </is>
       </c>
       <c r="C1388" t="n">
@@ -21741,7 +21754,7 @@
       </c>
       <c r="B1390" s="1" t="inlineStr">
         <is>
-          <t>「Hey... wanna try it for a bit？」</t>
+          <t>「Hey... want to try it for a bit?」</t>
         </is>
       </c>
       <c r="C1390" t="n">
@@ -21771,7 +21784,7 @@
       </c>
       <c r="B1392" s="1" t="inlineStr">
         <is>
-          <t>「M-muu… do you want it that much？」</t>
+          <t>M-mmm... do you want to kiss that much?</t>
         </is>
       </c>
       <c r="C1392" t="n">
@@ -21831,7 +21844,7 @@
       </c>
       <c r="B1396" s="1" t="inlineStr">
         <is>
-          <t>「W-Well... okay...」</t>
+          <t>Th-then... okay...</t>
         </is>
       </c>
       <c r="C1396" t="n">
@@ -21876,7 +21889,8 @@
       </c>
       <c r="B1399" s="1" t="inlineStr">
         <is>
-          <t>…While clumsily persisting, Rin-chan finally gave in.</t>
+          <t>Though clumsy, I kept at it, and Rin-chan finally
+gave in.</t>
         </is>
       </c>
       <c r="C1399" t="n">
@@ -21906,7 +21920,7 @@
       </c>
       <c r="B1401" s="1" t="inlineStr">
         <is>
-          <t>「So... I’m going to do it, okay...？」</t>
+          <t>Then... I'll do it, okay...?</t>
         </is>
       </c>
       <c r="C1401" t="n">
@@ -21936,7 +21950,7 @@
       </c>
       <c r="B1403" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh...」</t>
+          <t>「Nn...」</t>
         </is>
       </c>
       <c r="C1403" t="n">
@@ -21951,7 +21965,7 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>I gently leaned in and pressed her lips to
+          <t>I gently leaned in and pressed my lips against
 Rin-chan's.</t>
         </is>
       </c>
@@ -21982,7 +21996,7 @@
       </c>
       <c r="B1406" s="1" t="inlineStr">
         <is>
-          <t>「Nn… h-huh, fu… fuu…」</t>
+          <t>「Nn... f-fu, fu... fuu...」</t>
         </is>
       </c>
       <c r="C1406" t="n">
@@ -22013,8 +22027,8 @@
       </c>
       <c r="B1408" s="1" t="inlineStr">
         <is>
-          <t>A hesitant sigh is basically saying, what should we
-do now?</t>
+          <t>Rin-chan's hesitant sigh seemed to be saying, 'What
+should we do now?'</t>
         </is>
       </c>
       <c r="C1408" t="n">
@@ -22029,7 +22043,7 @@
       </c>
       <c r="B1409" s="1" t="inlineStr">
         <is>
-          <t>...I guess I should show them by taking action！</t>
+          <t>Now's the time for me to show it through my actions!</t>
         </is>
       </c>
       <c r="C1409" t="n">
@@ -22059,7 +22073,7 @@
       </c>
       <c r="B1411" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaa...！？  Fu, uuh...？」</t>
+          <t>「Fwah...!? F-fuu...?」</t>
         </is>
       </c>
       <c r="C1411" t="n">
@@ -22074,8 +22088,8 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>When I licked her lips with my tongue, Rin-chan
-jumped and opened her eyes wide.</t>
+          <t>When I licked Rin-chan's lips with my tongue, she was
+startled and opened her eyes wide.</t>
         </is>
       </c>
       <c r="C1412" t="n">
@@ -22105,7 +22119,7 @@
       </c>
       <c r="B1414" s="1" t="inlineStr">
         <is>
-          <t>「Nng… nnng… ngg！ Nng, nnng~！」</t>
+          <t>Nn... nnng... nnng! Nn, nnng~!</t>
         </is>
       </c>
       <c r="C1414" t="n">
@@ -22120,8 +22134,8 @@
       </c>
       <c r="B1415" s="1" t="inlineStr">
         <is>
-          <t>But that only lasted a moment before she squeezed her
-eyes shut and clamped her lips tight.</t>
+          <t>But that only lasted a moment; Rin-chan squeezed her
+eyes shut and pressed her lips tightly together.</t>
         </is>
       </c>
       <c r="C1415" t="n">
@@ -22136,7 +22150,7 @@
       </c>
       <c r="B1416" s="1" t="inlineStr">
         <is>
-          <t>Man, that’s some serious shyness…</t>
+          <t>Hmmm... as expected, Rin-chan's really shy...</t>
         </is>
       </c>
       <c r="C1416" t="n">
@@ -22151,7 +22165,7 @@
       </c>
       <c r="B1417" s="1" t="inlineStr">
         <is>
-          <t>I shrugged inwardly and pulled my face back.</t>
+          <t>I gave a small, inward shrug and pulled back.</t>
         </is>
       </c>
       <c r="C1417" t="n">
@@ -22166,7 +22180,7 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C1418" t="n">
@@ -22181,7 +22195,7 @@
       </c>
       <c r="B1419" s="1" t="inlineStr">
         <is>
-          <t>「...！？ Nn, nngh...！」</t>
+          <t>「...!? Nn, nng...!」</t>
         </is>
       </c>
       <c r="C1419" t="n">
@@ -22196,7 +22210,7 @@
       </c>
       <c r="B1420" s="1" t="inlineStr">
         <is>
-          <t>Then, Rin-chan came chasing after me.</t>
+          <t>Then Rin-chan chased after me.</t>
         </is>
       </c>
       <c r="C1420" t="n">
@@ -22226,7 +22240,7 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>「Hah... nn... huh！ Huu... un...！」</t>
+          <t>「Hafu... nn... fuh! Huu... un...!」</t>
         </is>
       </c>
       <c r="C1422" t="n">
@@ -22271,8 +22285,8 @@
       </c>
       <c r="B1425" s="1" t="inlineStr">
         <is>
-          <t>This is kind of like the north wind and the sun, I
-guess.</t>
+          <t>Could this be something like the North Wind and the
+Sun?</t>
         </is>
       </c>
       <c r="C1425" t="n">
@@ -22287,8 +22301,8 @@
       </c>
       <c r="B1426" s="1" t="inlineStr">
         <is>
-          <t>If I come on too strong she'll pull away, but if I
-back off she moves toward me.</t>
+          <t>If I come on too strong, Rin-chan pulls away, but if
+I back off, Rin-chan comes closer.</t>
         </is>
       </c>
       <c r="C1426" t="n">
@@ -22348,7 +22362,7 @@
       </c>
       <c r="B1430" s="1" t="inlineStr">
         <is>
-          <t>「Ah！？ Amu！ Nn, nn！ Hah, huu！ Nn... fuu...！」</t>
+          <t>"Ah!? Amu! Nn... nn! Hah... huu! Nn... fuu...!"</t>
         </is>
       </c>
       <c r="C1430" t="n">
@@ -22364,7 +22378,7 @@
       <c r="B1431" s="1" t="inlineStr">
         <is>
           <t>When I pretended to be out of breath, Rin-chan seized
-the opportunity to press her attack.</t>
+the moment and pressed her advantage.</t>
         </is>
       </c>
       <c r="C1431" t="n">
@@ -22395,7 +22409,7 @@
       </c>
       <c r="B1433" s="1" t="inlineStr">
         <is>
-          <t>I kept pretending to pull back while opening my lips
+          <t>I continued to pretend to pull back, opened my lips,
 and stuck my tongue out a little.</t>
         </is>
       </c>
@@ -22411,7 +22425,7 @@
       </c>
       <c r="B1434" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C1434" t="n">
@@ -22426,7 +22440,7 @@
       </c>
       <c r="B1435" s="1" t="inlineStr">
         <is>
-          <t>「Nn... naa... nnah... ah, aaah...」</t>
+          <t>「Nn... n'ah... n'ah~... ah, ahh...」</t>
         </is>
       </c>
       <c r="C1435" t="n">
@@ -22441,7 +22455,7 @@
       </c>
       <c r="B1436" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan sticks her tongue out awkwardly.</t>
+          <t>Rin-chan also awkwardly stuck out her tongue.</t>
         </is>
       </c>
       <c r="C1436" t="n">
@@ -22486,7 +22500,7 @@
       </c>
       <c r="B1439" s="1" t="inlineStr">
         <is>
-          <t>「Nn, chu... fuu...」</t>
+          <t>「Mmm... smooch... phew...」</t>
         </is>
       </c>
       <c r="C1439" t="n">
@@ -22501,8 +22515,8 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>This time I press my tongue to hers, then pull away
-immediately.</t>
+          <t>This time I touch tongues with Rin-chan, then
+immediately pull back.</t>
         </is>
       </c>
       <c r="C1440" t="n">
@@ -22532,7 +22546,8 @@
       </c>
       <c r="B1442" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nngh！ Ahh, ahh... ah！ sck, smch, smooch...」</t>
+          <t>「Nn... nngh! Ahh, ahh... ah! smooch, smooch,
+smooch...」</t>
         </is>
       </c>
       <c r="C1442" t="n">
@@ -22563,7 +22578,7 @@
       </c>
       <c r="B1444" s="1" t="inlineStr">
         <is>
-          <t>It's surprisingly easy to understand...</t>
+          <t>Rin-chan's surprisingly easy to read...</t>
         </is>
       </c>
       <c r="C1444" t="n">
@@ -22593,7 +22608,7 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>「Chu, chuku...」</t>
+          <t>「Smooch... smuck...」</t>
         </is>
       </c>
       <c r="C1446" t="n">
@@ -22623,8 +22638,8 @@
       </c>
       <c r="B1448" s="1" t="inlineStr">
         <is>
-          <t>「chu, chuu...！ chuku, uuu, fuu...！ nha... ah, chu,
-chuk...！」</t>
+          <t>「Smooch, smooch...! Smooch, uuh, phew...! N'ah... ah,
+smooch, smooch...!」</t>
         </is>
       </c>
       <c r="C1448" t="n">
@@ -22639,8 +22654,8 @@
       </c>
       <c r="B1449" s="1" t="inlineStr">
         <is>
-          <t>……while teasing by darting her tongue in and out, our
-tongues started to properly entwine.</t>
+          <t>……while I teased by sticking my tongue out and
+pulling it back, our tongues began to entwine firmly.</t>
         </is>
       </c>
       <c r="C1449" t="n">
@@ -22701,7 +22716,7 @@
       </c>
       <c r="B1453" s="1" t="inlineStr">
         <is>
-          <t>「Smooch, smack！ Smooch smooch！」</t>
+          <t>「Smooch, smack! Smooch smooch!」</t>
         </is>
       </c>
       <c r="C1453" t="n">
@@ -22716,7 +22731,7 @@
       </c>
       <c r="B1454" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C1454" t="n">
@@ -22731,8 +22746,8 @@
       </c>
       <c r="B1455" s="1" t="inlineStr">
         <is>
-          <t>「Chuk！ Faa... ah！ Chu-chu！ Chu... haa... fa, nnn...
-chuk！」</t>
+          <t>「Smooch! Fah... ah! Smooch-smooch! Smooch... haa...
+fah, nngh... smooch!」</t>
         </is>
       </c>
       <c r="C1455" t="n">
@@ -22763,8 +22778,8 @@
       </c>
       <c r="B1457" s="1" t="inlineStr">
         <is>
-          <t>We both stick our tongues out and tangle them
-together... ending up like that.</t>
+          <t>We both stuck out our tongues and intertwined them...
+and ended up like that.</t>
         </is>
       </c>
       <c r="C1457" t="n">
@@ -22809,7 +22824,7 @@
       </c>
       <c r="B1460" s="1" t="inlineStr">
         <is>
-          <t>「Fu！ Nnn... nah！ Chuk！ Chuk！ Chuba, chu！ Nnn！ Nhaa！」</t>
+          <t>「Hah! Nn... nha! Chuk! Chuk! Chuba, chu! Nn! Nhaa!」</t>
         </is>
       </c>
       <c r="C1460" t="n">
@@ -22824,8 +22839,8 @@
       </c>
       <c r="B1461" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's tiny tongue wraps around mine over and
-over, as if refusing to let go.</t>
+          <t>Rin-chan's tiny tongue clings to mine, wrapping
+around it relentlessly.</t>
         </is>
       </c>
       <c r="C1461" t="n">
@@ -22856,7 +22871,7 @@
       </c>
       <c r="B1463" s="1" t="inlineStr">
         <is>
-          <t>Ahaha... you're totally lost in it...！</t>
+          <t>Ahaha... you're really getting into it...!</t>
         </is>
       </c>
       <c r="C1463" t="n">
@@ -22871,7 +22886,7 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>Smooch— I like you.</t>
+          <t>Kissing... I like it.</t>
         </is>
       </c>
       <c r="C1464" t="n">
@@ -22916,8 +22931,8 @@
       </c>
       <c r="B1467" s="1" t="inlineStr">
         <is>
-          <t>「Fuaah！ Ah, ahfuuh！ Chu, chuku！ Chu... chuu！ Faa...
-n'a, fuu...！」</t>
+          <t>Fwah! Ah, ahh...! Smooch, smack! Smooch... smooch!
+Fah... n'ah, phew...!</t>
         </is>
       </c>
       <c r="C1467" t="n">
@@ -22947,7 +22962,7 @@
       </c>
       <c r="B1469" s="1" t="inlineStr">
         <is>
-          <t>「Chu！　Chuchu！　Dju！」</t>
+          <t>Smooch! Smooch-smooch! Smooch!</t>
         </is>
       </c>
       <c r="C1469" t="n">
@@ -22977,8 +22992,8 @@
       </c>
       <c r="B1471" s="1" t="inlineStr">
         <is>
-          <t>I press my tongue firmly, suck in Rin-chan's breath,
-and hug her tiny body...</t>
+          <t>I press my tongue hard against hers, inhale
+Rin-chan's breath, and hold her tiny body close...</t>
         </is>
       </c>
       <c r="C1471" t="n">
@@ -22993,8 +23008,7 @@
       </c>
       <c r="B1472" s="1" t="inlineStr">
         <is>
-          <t>Ah... I'm getting completely absorbed in Rin-chan
-too...！</t>
+          <t>Ah... I'm getting carried away with Rin-chan too...!</t>
         </is>
       </c>
       <c r="C1472" t="n">
@@ -23024,7 +23038,7 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>「Huh~？ Rin~？ Onii-chan~？ You there~？」</t>
+          <t>「Hey~? Rin~? Onii-chan~? Are you there~?」</t>
         </is>
       </c>
       <c r="C1474" t="n">
@@ -23039,8 +23053,8 @@
       </c>
       <c r="B1475" s="1" t="inlineStr">
         <is>
-          <t>At Miru-chan's voice suddenly ringing out, the two of
-them snapped back to their senses.</t>
+          <t>Hearing Miru-chan's voice suddenly ring out, the two
+of them snapped back to their senses.</t>
         </is>
       </c>
       <c r="C1475" t="n">
@@ -23116,7 +23130,7 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>「............！」</t>
+          <t>「............っ！」</t>
         </is>
       </c>
       <c r="C1480" t="n">
@@ -23161,7 +23175,7 @@
       </c>
       <c r="B1483" s="1" t="inlineStr">
         <is>
-          <t>We nod at each other with our eyes.</t>
+          <t>We exchange a nod with our eyes.</t>
         </is>
       </c>
       <c r="C1483" t="n">
@@ -23191,7 +23205,7 @@
       </c>
       <c r="B1485" s="1" t="inlineStr">
         <is>
-          <t>「Huh？  …What are you doing？」</t>
+          <t>「Oh~? ... What are you doing?」</t>
         </is>
       </c>
       <c r="C1485" t="n">
@@ -23253,9 +23267,9 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>But I was holding down the water gun's turret part
-and Rin-chan was grabbing the tripod, making for a
-pretty mismatched, awkward scene.</t>
+          <t>But I was pressing down on the turret of the water
+gun while Rin-chan gripped the tripod — it made for
+an oddly mismatched scene.</t>
         </is>
       </c>
       <c r="C1489" t="n">
@@ -23332,8 +23346,8 @@
       </c>
       <c r="B1494" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan nodded vigorously, angled so she wouldn't
-meet Miru-chan's eyes.</t>
+          <t>Rin-chan nodded vigorously, tilting her head to avoid
+making eye contact with Miru-chan.</t>
         </is>
       </c>
       <c r="C1494" t="n">
@@ -23348,7 +23362,7 @@
       </c>
       <c r="B1495" s="1" t="inlineStr">
         <is>
-          <t>...This really isn't like the usual Rin-chan.</t>
+          <t>She's definitely not acting like the usual Rin-chan.</t>
         </is>
       </c>
       <c r="C1495" t="n">
@@ -23378,7 +23392,7 @@
       </c>
       <c r="B1497" s="1" t="inlineStr">
         <is>
-          <t>「Oh really？ Miru wanna help too？」</t>
+          <t>Oh? Shall Miru help too?</t>
         </is>
       </c>
       <c r="C1497" t="n">
@@ -23454,8 +23468,8 @@
       </c>
       <c r="B1502" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ahaha... it's okay, right？ I checked, but
-couldn't figure it out, so I was thinking we'd head
+          <t>「Ah... ahaha... it's okay. I looked into it, but
+couldn't figure it out, so I thought we'd just go
 back.」</t>
         </is>
       </c>
@@ -23516,8 +23530,8 @@
       </c>
       <c r="B1506" s="1" t="inlineStr">
         <is>
-          <t>「We'll head back right away too, so Miru-chan, you
-should go back too, okay？」</t>
+          <t>"We're heading back right away, so Miru-chan, you go
+back too, okay?"</t>
         </is>
       </c>
       <c r="C1506" t="n">
@@ -23547,7 +23561,7 @@
       </c>
       <c r="B1508" s="1" t="inlineStr">
         <is>
-          <t>「Really？ Then I'll go ahead...！」</t>
+          <t>「Is that so? I'll go on ahead then...！」</t>
         </is>
       </c>
       <c r="C1508" t="n">
@@ -23562,8 +23576,8 @@
       </c>
       <c r="B1509" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan said that, she obediently turned on
-her heel.</t>
+          <t>Hearing that, Miru-chan obediently turned on her
+heels.</t>
         </is>
       </c>
       <c r="C1509" t="n">
@@ -23593,7 +23607,7 @@
       </c>
       <c r="B1511" s="1" t="inlineStr">
         <is>
-          <t>「...huh, haaah！」</t>
+          <t>「…! Haaah!」</t>
         </is>
       </c>
       <c r="C1511" t="n">
@@ -23638,7 +23652,7 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>「Haa... phew... I'm glad MiruMiru is so simple...」</t>
+          <t>「Sigh... thank goodness MiruMiru is so simple...」</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -23653,7 +23667,7 @@
       </c>
       <c r="B1515" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan also sighs and drops her shoulders in
+          <t>Rin-chan sighed and slumped her shoulders in
 exhaustion.</t>
         </is>
       </c>
@@ -23699,8 +23713,8 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>「Well, that's one of Miru-chan's good points, though,
-right？」</t>
+          <t>「Well, that's one of Miru-chan's good points, isn't
+it？」</t>
         </is>
       </c>
       <c r="C1518" t="n">
@@ -23730,7 +23744,7 @@
       </c>
       <c r="B1520" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... well, huh...」</t>
+          <t>「Y-yeah... well, I guess...」</t>
         </is>
       </c>
       <c r="C1520" t="n">
@@ -23745,7 +23759,7 @@
       </c>
       <c r="B1521" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan scratches her cheek and nods.</t>
+          <t>Rin-chan rubs her cheek and nods.</t>
         </is>
       </c>
       <c r="C1521" t="n">
@@ -23760,9 +23774,9 @@
       </c>
       <c r="B1522" s="1" t="inlineStr">
         <is>
-          <t>Because we're close she blurts things out without
-embarrassment, but when she concedes something she
-can do it properly.</t>
+          <t>Because we're close, Miru-chan says things without
+embarrassment, but she properly admits things when
+necessary.</t>
         </is>
       </c>
       <c r="C1522" t="n">
@@ -23777,8 +23791,8 @@
       </c>
       <c r="B1523" s="1" t="inlineStr">
         <is>
-          <t>Anyway, from here we should probably go back to how
-things usually are, right？</t>
+          <t>Anyway, from now on, maybe we should stick to our
+usual routine?</t>
         </is>
       </c>
       <c r="C1523" t="n">
@@ -23793,9 +23807,9 @@
       </c>
       <c r="B1524" s="1" t="inlineStr">
         <is>
-          <t>I thought this before the kiss too, but Rin-chan is
-basically shy, so I shouldn't make her aware of
-things that would embarrass her.</t>
+          <t>I thought that before the kiss too, but Rin-chan is
+shy by nature, so I shouldn't make her self-conscious
+about anything that might embarrass her.</t>
         </is>
       </c>
       <c r="C1524" t="n">
@@ -23825,7 +23839,7 @@
       </c>
       <c r="B1526" s="1" t="inlineStr">
         <is>
-          <t>「...So, shall we head back？」</t>
+          <t>「...Well then, shall we head back too?」</t>
         </is>
       </c>
       <c r="C1526" t="n">
@@ -23870,8 +23884,8 @@
       </c>
       <c r="B1529" s="1" t="inlineStr">
         <is>
-          <t>I force my usual tone, and Rin-chan nods in her usual
-way.</t>
+          <t>I deliberately adopted my usual tone, and Rin-chan
+nodded in hers.</t>
         </is>
       </c>
       <c r="C1529" t="n">
@@ -23886,8 +23900,8 @@
       </c>
       <c r="B1530" s="1" t="inlineStr">
         <is>
-          <t>Maybe because she panicked she returned to her normal
-self quicker.</t>
+          <t>Maybe because she was flustered, Rin-chan returned to
+her usual self sooner.</t>
         </is>
       </c>
       <c r="C1530" t="n">
@@ -23932,8 +23946,8 @@
       </c>
       <c r="B1533" s="1" t="inlineStr">
         <is>
-          <t>We step out of the storage room and close the door;
-Rin-chan stares at me intently.</t>
+          <t>I step out of the storage room and close the door,
+and Rin-chan stares at me intently.</t>
         </is>
       </c>
       <c r="C1533" t="n">
@@ -24008,8 +24022,8 @@
       </c>
       <c r="B1538" s="1" t="inlineStr">
         <is>
-          <t>She looked like she wanted to say something, but
-Rin-chan turns away with a little huff.</t>
+          <t>Rin-chan seems like she wants to say something, but
+she pouts and looks away.</t>
         </is>
       </c>
       <c r="C1538" t="n">
@@ -24024,7 +24038,7 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>Still, I can see her bashful profile...</t>
+          <t>I still caught sight of her bashful profile...</t>
         </is>
       </c>
       <c r="C1539" t="n">
@@ -24054,7 +24068,7 @@
       </c>
       <c r="B1541" s="1" t="inlineStr">
         <is>
-          <t>「...Shall we... go？」</t>
+          <t>「...Shall we go?」</t>
         </is>
       </c>
       <c r="C1541" t="n">
@@ -24114,8 +24128,8 @@
       </c>
       <c r="B1545" s="1" t="inlineStr">
         <is>
-          <t>And so we walk the short distance to the classroom a
-little closer than usual.</t>
+          <t>And so we walked the short distance to the classroom,
+a little closer than usual.</t>
         </is>
       </c>
       <c r="C1545" t="n">
@@ -24145,7 +24159,7 @@
       </c>
       <c r="B1547" s="1" t="inlineStr">
         <is>
-          <t>「Alright then, let's ask Rurichiyo-chan for help.」</t>
+          <t>「Well then, maybe I'll ask Rurichiyo-chan.」</t>
         </is>
       </c>
       <c r="C1547" t="n">
@@ -24190,7 +24204,7 @@
       </c>
       <c r="B1550" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nods happily.</t>
+          <t>Rurichiyo-chan nodded happily.</t>
         </is>
       </c>
       <c r="C1550" t="n">
@@ -24236,7 +24250,7 @@
       </c>
       <c r="B1553" s="1" t="inlineStr">
         <is>
-          <t>「Alright, everyone else change first, okay?」</t>
+          <t>Alright, everyone else, go change first, okay?</t>
         </is>
       </c>
       <c r="C1553" t="n">
@@ -24251,7 +24265,8 @@
       </c>
       <c r="B1554" s="1" t="inlineStr">
         <is>
-          <t>I say that, hug the water gun, and start walking.</t>
+          <t>Having said that, I pick up the water gun and start
+walking.</t>
         </is>
       </c>
       <c r="C1554" t="n">
@@ -24296,7 +24311,7 @@
       </c>
       <c r="B1557" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan followed a step behind.</t>
+          <t>Rurichiyo-chan trailed one step behind us.</t>
         </is>
       </c>
       <c r="C1557" t="n">
@@ -24326,7 +24341,7 @@
       </c>
       <c r="B1559" s="1" t="inlineStr">
         <is>
-          <t>「Now then, where should I put this...?」</t>
+          <t>Now then, where should I put this...?</t>
         </is>
       </c>
       <c r="C1559" t="n">
@@ -24387,7 +24402,8 @@
       </c>
       <c r="B1563" s="1" t="inlineStr">
         <is>
-          <t>「...Do we have to move some things first？」</t>
+          <t>「...Will we need to move some other things out of the
+way first?」</t>
         </is>
       </c>
       <c r="C1563" t="n">
@@ -24432,8 +24448,8 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>As Rurichiyo-chan says, we'll need to tidy up a bit
-to fit everything neatly.</t>
+          <t>As Rurichiyo-chan said, it looks like we'll need to
+tidy up a bit to fit it all properly.</t>
         </is>
       </c>
       <c r="C1566" t="n">
@@ -24495,8 +24511,8 @@
       </c>
       <c r="B1570" s="1" t="inlineStr">
         <is>
-          <t>「Ah… if that's the case, I'll have to move the mat
-and the ball holder first, what a hassle…」</t>
+          <t>Ah... in that case I'd have to move the mats and the
+ball bin first; what a hassle...</t>
         </is>
       </c>
       <c r="C1570" t="n">
@@ -24526,8 +24542,7 @@
       </c>
       <c r="B1572" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, calling it a hassle? You must do it
-properly！」</t>
+          <t>Oh? Calling it a hassle? You must do it properly!</t>
         </is>
       </c>
       <c r="C1572" t="n">
@@ -24574,8 +24589,8 @@
       </c>
       <c r="B1575" s="1" t="inlineStr">
         <is>
-          <t>「Nah, it's a hassle, so I figured there must be a
-more efficient way...」</t>
+          <t>No, it's a hassle, so I thought there might be a more
+efficient way...</t>
         </is>
       </c>
       <c r="C1575" t="n">
@@ -24605,8 +24620,8 @@
       </c>
       <c r="B1577" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama, trying to get everything over with too
-easily isn’t right, you know？」</t>
+          <t>"Oji-sama, you mustn't try to do everything too
+easily, you know?"</t>
         </is>
       </c>
       <c r="C1577" t="n">
@@ -24651,9 +24666,8 @@
       </c>
       <c r="B1580" s="1" t="inlineStr">
         <is>
-          <t>「But thinking up efficient ways of doing things is
-something you should do if you’re thinking about the
-long run, right？」</t>
+          <t>But coming up with efficient methods is a good idea
+if you think ahead, isn't it?</t>
         </is>
       </c>
       <c r="C1580" t="n">
@@ -24698,8 +24712,8 @@
       </c>
       <c r="B1583" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who was about to argue further, gave
-a small sneeze.</t>
+          <t>Rurichiyo-chan, who was about to argue her point
+further, sneezed softly.</t>
         </is>
       </c>
       <c r="C1583" t="n">
@@ -24789,8 +24803,8 @@
       </c>
       <c r="B1589" s="1" t="inlineStr">
         <is>
-          <t>「I'll take care of it later, so for now just put it
-somewhere easy to stow and go change, okay？」</t>
+          <t>"I'll take care of it later, so for now just put it
+somewhere convenient and go get changed, okay?"</t>
         </is>
       </c>
       <c r="C1589" t="n">
@@ -24850,9 +24864,9 @@
       </c>
       <c r="B1593" s="1" t="inlineStr">
         <is>
-          <t>She seems willing to accept my help, but feels bad
-that my assistance is only half-done... something
-like that.</t>
+          <t>She's trying to accept my kindness, but feels bad
+that her help ended up being unfinished... I guess
+that's about it.</t>
         </is>
       </c>
       <c r="C1593" t="n">
@@ -24882,7 +24896,7 @@
       </c>
       <c r="B1595" s="1" t="inlineStr">
         <is>
-          <t>「Then... for now, put it here...」</t>
+          <t>"Then... I'll put it here for now..."</t>
         </is>
       </c>
       <c r="C1595" t="n">
@@ -24897,8 +24911,8 @@
       </c>
       <c r="B1596" s="1" t="inlineStr">
         <is>
-          <t>I find a spot just big enough to barely fit in front
-of the storeroom door and set the water gun there.</t>
+          <t>I find a space just big enough to fit in front of the
+storeroom door and place the water gun there.</t>
         </is>
       </c>
       <c r="C1596" t="n">
@@ -24975,8 +24989,8 @@
       </c>
       <c r="B1601" s="1" t="inlineStr">
         <is>
-          <t>Hearing Rurichiyo-chan's words, I tried closing the
-door to see.</t>
+          <t>Hearing Rurichiyo-chan's words, I try closing the
+door.</t>
         </is>
       </c>
       <c r="C1601" t="n">
@@ -25037,7 +25051,7 @@
       <c r="B1605" s="1" t="inlineStr">
         <is>
           <t>I mumbled to myself after checking it wouldn't be in
-the way the next time we opened it.</t>
+the way the next time I open it.</t>
         </is>
       </c>
       <c r="C1605" t="n">
@@ -25082,7 +25096,7 @@
       </c>
       <c r="B1608" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nodded as she watched.</t>
+          <t>Rurichiyo-chan also nodded as she watched.</t>
         </is>
       </c>
       <c r="C1608" t="n">
@@ -25127,8 +25141,8 @@
       </c>
       <c r="B1611" s="1" t="inlineStr">
         <is>
-          <t>Shall we go change？ I hesitated for a moment before
-saying that.</t>
+          <t>Shall we go change? I hesitated for a moment before
+saying it.</t>
         </is>
       </c>
       <c r="C1611" t="n">
@@ -25159,7 +25173,7 @@
       </c>
       <c r="B1613" s="1" t="inlineStr">
         <is>
-          <t>I'm kind of secretly longing for this situation...</t>
+          <t>I kind of find myself longing for this situation...</t>
         </is>
       </c>
       <c r="C1613" t="n">
@@ -25189,7 +25203,7 @@
       </c>
       <c r="B1615" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama？ Is something the matter？」</t>
+          <t>Oji-sama? Is something the matter?</t>
         </is>
       </c>
       <c r="C1615" t="n">
@@ -25204,7 +25218,7 @@
       </c>
       <c r="B1616" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan moves closer to me, who have stopped
+          <t>Rurichiyo-chan moves closer to me; I've stopped
 moving.</t>
         </is>
       </c>
@@ -25250,8 +25264,8 @@
       </c>
       <c r="B1619" s="1" t="inlineStr">
         <is>
-          <t>When Rurichiyo-chan came close, I felt a faintly warm
-air.</t>
+          <t>When Rurichiyo-chan came close, I felt a faint
+warmth.</t>
         </is>
       </c>
       <c r="C1619" t="n">
@@ -25266,9 +25280,9 @@
       </c>
       <c r="B1620" s="1" t="inlineStr">
         <is>
-          <t>Because she'd been happily playing, her body
-temperature had gone up, and the moisture in her body
-was radiating outward.</t>
+          <t>She'd been happily playing, so her body temperature
+had risen, and moisture from her skin radiated
+outward.</t>
         </is>
       </c>
       <c r="C1620" t="n">
@@ -25298,8 +25312,8 @@
       </c>
       <c r="B1622" s="1" t="inlineStr">
         <is>
-          <t>That aura was warm, sweet, and had the power to make
-me bow my head.</t>
+          <t>That aura was warm and sweet, and it had the power to
+make me prostrate myself.</t>
         </is>
       </c>
       <c r="C1622" t="n">
@@ -25329,7 +25343,7 @@
       </c>
       <c r="B1624" s="1" t="inlineStr">
         <is>
-          <t>「O...oji-sama...？」</t>
+          <t>「O... Oji-sama...？」</t>
         </is>
       </c>
       <c r="C1624" t="n">
@@ -25405,7 +25419,7 @@
       </c>
       <c r="B1629" s="1" t="inlineStr">
         <is>
-          <t>「Huh...！？」</t>
+          <t>「Whew...!?」</t>
         </is>
       </c>
       <c r="C1629" t="n">
@@ -25481,8 +25495,7 @@
       </c>
       <c r="B1634" s="1" t="inlineStr">
         <is>
-          <t>She continues, as if trying to hide her
-embarrassment.</t>
+          <t>Rurichiyo-chan adds, as if to hide her embarrassment.</t>
         </is>
       </c>
       <c r="C1634" t="n">
@@ -25497,7 +25510,7 @@
       </c>
       <c r="B1635" s="1" t="inlineStr">
         <is>
-          <t>Then she stretches up and smooths my bangs.</t>
+          <t>Then Rurichiyo-chan reaches up and strokes my bangs.</t>
         </is>
       </c>
       <c r="C1635" t="n">
@@ -25527,8 +25540,8 @@
       </c>
       <c r="B1637" s="1" t="inlineStr">
         <is>
-          <t>「Oh my... your hair's a bit mussed, isn't it？
-Tee-hee...！」</t>
+          <t>Oh my... your hair's a bit disheveled, isn't it?
+Fufu...!</t>
         </is>
       </c>
       <c r="C1637" t="n">
@@ -25573,7 +25586,7 @@
       </c>
       <c r="B1640" s="1" t="inlineStr">
         <is>
-          <t>I'm probably just hiding my embarrassment, but I'm
+          <t>She's probably just pretending to be shy, but she's
 surprisingly close...</t>
         </is>
       </c>
@@ -25649,7 +25662,7 @@
       </c>
       <c r="B1645" s="1" t="inlineStr">
         <is>
-          <t>I want to nibble on her lips and smooch them...！</t>
+          <t>I want to nibble at her lips and smooch them...!</t>
         </is>
       </c>
       <c r="C1645" t="n">
@@ -25709,9 +25722,9 @@
       </c>
       <c r="B1649" s="1" t="inlineStr">
         <is>
-          <t>After saying it she snapped back to herself and was
-surprised, but Rurichiyo-chan squinted her eyes and
-smiled gently.</t>
+          <t>After saying that, she came to her senses and looked
+surprised, but Rurichiyo-chan narrowed her eyes and
+smiled softly.</t>
         </is>
       </c>
       <c r="C1649" t="n">
@@ -25741,7 +25754,8 @@
       </c>
       <c r="B1651" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ No, it's pretend！ Pretend is fine, though！？」</t>
+          <t>「Ah! No—it's just pretend! It's okay if we're just
+pretending, right?!」</t>
         </is>
       </c>
       <c r="C1651" t="n">
@@ -25832,7 +25846,7 @@
       </c>
       <c r="B1657" s="1" t="inlineStr">
         <is>
-          <t>「…Yes, let's do it.」</t>
+          <t>…Yes, let's do it.</t>
         </is>
       </c>
       <c r="C1657" t="n">
@@ -25847,8 +25861,8 @@
       </c>
       <c r="B1658" s="1" t="inlineStr">
         <is>
-          <t>…Feeling all fuzzy and unsettled, Rurichiyo-chan
-smiles and says that to me.</t>
+          <t>…When I'm feeling unsettled, Rurichiyo-chan smiles
+and says that to me.</t>
         </is>
       </c>
       <c r="C1658" t="n">
@@ -25893,8 +25907,8 @@
       </c>
       <c r="B1661" s="1" t="inlineStr">
         <is>
-          <t>It was just when I thought I'd messed up, so I
-couldn't help but honestly feel happy.</t>
+          <t>It was just when I thought I'd blown it, so I
+couldn't help but feel genuinely happy.</t>
         </is>
       </c>
       <c r="C1661" t="n">
@@ -25924,7 +25938,7 @@
       </c>
       <c r="B1663" s="1" t="inlineStr">
         <is>
-          <t>「Heh... Oji-sama, you...」</t>
+          <t>「Teehee... Oji-sama...!」</t>
         </is>
       </c>
       <c r="C1663" t="n">
@@ -25939,8 +25953,8 @@
       </c>
       <c r="B1664" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan watches me and smiles as if she finds
-it funny.</t>
+          <t>Rurichiyo-chan looks at me and smiles, seeming
+amused.</t>
         </is>
       </c>
       <c r="C1664" t="n">
@@ -25955,7 +25969,7 @@
       </c>
       <c r="B1665" s="1" t="inlineStr">
         <is>
-          <t>Was I really that happy-looking？</t>
+          <t>Did I really look that happy?</t>
         </is>
       </c>
       <c r="C1665" t="n">
@@ -25970,8 +25984,9 @@
       </c>
       <c r="B1666" s="1" t="inlineStr">
         <is>
-          <t>……But when you smile at me like that, like you’re
-looking at a child, it makes things a little awkward.</t>
+          <t>…But when she smiles at me like that, as if she were
+looking at a child, it makes me a little
+uncomfortable.</t>
         </is>
       </c>
       <c r="C1666" t="n">
@@ -25986,7 +26001,7 @@
       </c>
       <c r="B1667" s="1" t="inlineStr">
         <is>
-          <t>So I put on an intentionally serious face.</t>
+          <t>So I made an effort to put on a serious expression.</t>
         </is>
       </c>
       <c r="C1667" t="n">
@@ -26076,7 +26091,7 @@
       </c>
       <c r="B1673" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ah...」</t>
+          <t>「Nn... fah...」</t>
         </is>
       </c>
       <c r="C1673" t="n">
@@ -26091,8 +26106,8 @@
       </c>
       <c r="B1674" s="1" t="inlineStr">
         <is>
-          <t>We lean in gently and press our lips together
-quietly...</t>
+          <t>Rurichiyo-chan leans in gently and quietly presses
+her lips to mine...</t>
         </is>
       </c>
       <c r="C1674" t="n">
@@ -26107,7 +26122,7 @@
       </c>
       <c r="B1675" s="1" t="inlineStr">
         <is>
-          <t>Then, Rurichiyo-chan let out a warm breath.</t>
+          <t>Then Rurichiyo-chan exhaled, her breath hot.</t>
         </is>
       </c>
       <c r="C1675" t="n">
@@ -26137,7 +26152,7 @@
       </c>
       <c r="B1677" s="1" t="inlineStr">
         <is>
-          <t>「Puaa... ah... Oji-sama...」</t>
+          <t>「Puh... ah... Oji-sama...」</t>
         </is>
       </c>
       <c r="C1677" t="n">
@@ -26152,7 +26167,7 @@
       </c>
       <c r="B1678" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan slightly parted her lips and exhaled.</t>
+          <t>Rurichiyo-chan slightly shifted her lips and exhaled.</t>
         </is>
       </c>
       <c r="C1678" t="n">
@@ -26182,7 +26197,7 @@
       </c>
       <c r="B1680" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！？ Nn—, nn... fuh...！」</t>
+          <t>「Nn...!? Nnngh... nn... fuh...!」</t>
         </is>
       </c>
       <c r="C1680" t="n">
@@ -26244,8 +26259,8 @@
       </c>
       <c r="B1684" s="1" t="inlineStr">
         <is>
-          <t>Thinking that makes me hesitate, but now there's no
-turning back.</t>
+          <t>That thought makes me hesitate, but I can't back out
+now.</t>
         </is>
       </c>
       <c r="C1684" t="n">
@@ -26275,7 +26290,8 @@
       </c>
       <c r="B1686" s="1" t="inlineStr">
         <is>
-          <t>Instead of words, I pressed my lips harder.</t>
+          <t>Instead of words, I pressed my lips to hers more
+firmly.</t>
         </is>
       </c>
       <c r="C1686" t="n">
@@ -26305,8 +26321,8 @@
       </c>
       <c r="B1688" s="1" t="inlineStr">
         <is>
-          <t>「Nn... mmm. Ahh... nmm... ffu... fuu... fuu...
-nnn...！」</t>
+          <t>「Nn... mwaah. Ahh... nmph... fuh... fuu... fuu—...
+nngh...！」</t>
         </is>
       </c>
       <c r="C1688" t="n">
@@ -26352,8 +26368,8 @@
       </c>
       <c r="B1691" s="1" t="inlineStr">
         <is>
-          <t>But her movements were still childishly innocent, and
-that contrast made my heart race...！</t>
+          <t>Still, her gestures remained utterly innocent, and
+that contrast made my heart race...!</t>
         </is>
       </c>
       <c r="C1691" t="n">
@@ -26383,7 +26399,7 @@
       </c>
       <c r="B1693" s="1" t="inlineStr">
         <is>
-          <t>「U... haa... o-ji-sama...」</t>
+          <t>"U... haa... Oji-sama..."</t>
         </is>
       </c>
       <c r="C1693" t="n">
@@ -26398,9 +26414,9 @@
       </c>
       <c r="B1694" s="1" t="inlineStr">
         <is>
-          <t>She called me while our lips were still touching, and
-even her voice sounded softer than usual — it was
-amazing.</t>
+          <t>Rurichiyo-chan called me while our lips were still
+touching; even her voice sounded softer and more
+refined than usual — it felt really nice.</t>
         </is>
       </c>
       <c r="C1694" t="n">
@@ -26430,7 +26446,7 @@
       </c>
       <c r="B1696" s="1" t="inlineStr">
         <is>
-          <t>「Nfu...！？ nng, nfuuh... fa, ah...」</t>
+          <t>「Nnfu...!? Nn, nfuuh... fa, ah...」</t>
         </is>
       </c>
       <c r="C1696" t="n">
@@ -26445,7 +26461,7 @@
       </c>
       <c r="B1697" s="1" t="inlineStr">
         <is>
-          <t>I slid my tongue into the wide-open mouth.</t>
+          <t>I slid my tongue into her gaping mouth.</t>
         </is>
       </c>
       <c r="C1697" t="n">
@@ -26460,9 +26476,9 @@
       </c>
       <c r="B1698" s="1" t="inlineStr">
         <is>
-          <t>I felt like I was being guided by the sound of
-Rurichiyo-chan calling me, and I couldn't help but do
-it.</t>
+          <t>It felt as though I was being guided by
+Rurichiyo-chan's voice calling me, and I couldn't
+help myself.</t>
         </is>
       </c>
       <c r="C1698" t="n">
@@ -26492,7 +26508,7 @@
       </c>
       <c r="B1700" s="1" t="inlineStr">
         <is>
-          <t>「Fa... n'aa...！？ huff, huff...！」</t>
+          <t>「Faa... naaah...!? Huff, huff...！」</t>
         </is>
       </c>
       <c r="C1700" t="n">
@@ -26507,7 +26523,7 @@
       </c>
       <c r="B1701" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan exhaled awkwardly through her
+          <t>Rurichiyo-chan awkwardly exhales through her
 half-open mouth.</t>
         </is>
       </c>
@@ -26523,7 +26539,7 @@
       </c>
       <c r="B1702" s="1" t="inlineStr">
         <is>
-          <t>...Had I done it again？</t>
+          <t>...Had I done it again?</t>
         </is>
       </c>
       <c r="C1702" t="n">
@@ -26555,7 +26571,7 @@
       </c>
       <c r="B1704" s="1" t="inlineStr">
         <is>
-          <t>Did you just feel that way about me...？</t>
+          <t>Did she just think that about me...?</t>
         </is>
       </c>
       <c r="C1704" t="n">
@@ -26585,7 +26601,7 @@
       </c>
       <c r="B1706" s="1" t="inlineStr">
         <is>
-          <t>「Nn, ah, haa...！ Fuu... nn！」</t>
+          <t>「Nn... ahh... haa...! Fuu... nn!」</t>
         </is>
       </c>
       <c r="C1706" t="n">
@@ -26615,7 +26631,7 @@
       </c>
       <c r="B1708" s="1" t="inlineStr">
         <is>
-          <t>「Nnn...！？」</t>
+          <t>「Nn...！？」</t>
         </is>
       </c>
       <c r="C1708" t="n">
@@ -26661,7 +26677,8 @@
       </c>
       <c r="B1711" s="1" t="inlineStr">
         <is>
-          <t>「Pua...huh, fwah...！ Rero, rero...kuchu, puu, fuu…」</t>
+          <t>"Pua... fuu, fwah...! Rero, rero... kuchu, puu,
+fuu..."</t>
         </is>
       </c>
       <c r="C1711" t="n">
@@ -26676,8 +26693,8 @@
       </c>
       <c r="B1712" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's tongue flicked at mine, licking it
-lightly.</t>
+          <t>Rurichiyo-chan's tongue darted across mine, lightly
+licking it.</t>
         </is>
       </c>
       <c r="C1712" t="n">
@@ -26692,8 +26709,8 @@
       </c>
       <c r="B1713" s="1" t="inlineStr">
         <is>
-          <t>She was clumsy, but I felt like she was doing her
-best to respond to me.</t>
+          <t>Rurichiyo-chan is awkward, but I think she's doing
+her best to respond to me.</t>
         </is>
       </c>
       <c r="C1713" t="n">
@@ -26723,8 +26740,8 @@
       </c>
       <c r="B1715" s="1" t="inlineStr">
         <is>
-          <t>「Kuchu, chuu...chuku, amu, rero, rero...fu,
-fuu...nnu...」</t>
+          <t>"Squelch, smooch... smooch, nibble, lick, lick...
+ahh, fuu... mmm..."</t>
         </is>
       </c>
       <c r="C1715" t="n">
@@ -26739,8 +26756,8 @@
       </c>
       <c r="B1716" s="1" t="inlineStr">
         <is>
-          <t>Ah… but why does making out with Rurichiyo feel so
-good…?</t>
+          <t>Ah… but why does a tongue kiss with Rurichiyo-chan
+feel so good…?</t>
         </is>
       </c>
       <c r="C1716" t="n">
@@ -26755,7 +26772,8 @@
       </c>
       <c r="B1717" s="1" t="inlineStr">
         <is>
-          <t>It's a kiss that makes me feel very gentle inside.</t>
+          <t>It's a tongue-kiss that makes me feel very warm
+inside.</t>
         </is>
       </c>
       <c r="C1717" t="n">
@@ -26770,7 +26788,7 @@
       </c>
       <c r="B1718" s="1" t="inlineStr">
         <is>
-          <t>That's probably because it's Rurichiyo.</t>
+          <t>That's probably because it's Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C1718" t="n">
@@ -26800,7 +26818,7 @@
       </c>
       <c r="B1720" s="1" t="inlineStr">
         <is>
-          <t>「Nfufu...Oji-sama...nmu！ Chu, chuku...chuba, chu...」</t>
+          <t>Nfufu... Oji-sama... nmu! Chu, chuku... chuba, chu...</t>
         </is>
       </c>
       <c r="C1720" t="n">
@@ -26830,8 +26848,9 @@
       </c>
       <c r="B1722" s="1" t="inlineStr">
         <is>
-          <t>...Or so I thought, but she called to me sweetly, and
-this time she kissed me herself.</t>
+          <t>Just when I thought so, Rurichiyo-chan called to me
+in a sweet, affectionate way—and this time it was her
+who kissed me.</t>
         </is>
       </c>
       <c r="C1722" t="n">
@@ -26861,8 +26880,8 @@
       </c>
       <c r="B1724" s="1" t="inlineStr">
         <is>
-          <t>「Chuba！ Kuchu...chuchu！ N'ff...chuba, kuchu,
-chuu...！」</t>
+          <t>"Smack! Slurp... smooch! Mmmf... smack, slurp,
+kiss...!"</t>
         </is>
       </c>
       <c r="C1724" t="n">
@@ -26877,7 +26896,7 @@
       </c>
       <c r="B1725" s="1" t="inlineStr">
         <is>
-          <t>...Rurichiyo-chan was being proactive.</t>
+          <t>...Rurichiyo-chan is taking the initiative.</t>
         </is>
       </c>
       <c r="C1725" t="n">
@@ -26892,8 +26911,8 @@
       </c>
       <c r="B1726" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, I had been going on with just the mood, my
-feelings lagging behind.</t>
+          <t>Meanwhile, I was acting only on the mood — my
+feelings hadn't caught up.</t>
         </is>
       </c>
       <c r="C1726" t="n">
@@ -26938,7 +26957,7 @@
       </c>
       <c r="B1729" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-cha...n, rero, rerer！」</t>
+          <t>「Rurichiyo-chan...n, rero, reru!」</t>
         </is>
       </c>
       <c r="C1729" t="n">
@@ -26968,7 +26987,7 @@
       </c>
       <c r="B1731" s="1" t="inlineStr">
         <is>
-          <t>「Fwah...ah, ah...Oji-sama...fuu, nnn...naah, nfu！
+          <t>「Fwah... ah, ah... Oji-sama... fuu, nn... naa, nfu!
 Fuu, fuuu...！」</t>
         </is>
       </c>
@@ -26985,8 +27004,8 @@
       <c r="B1732" s="1" t="inlineStr">
         <is>
           <t>Sticking my tongue out in return, Rurichiyo-chan did
-the same, and our tongues slid together, wetly
-tangled around each other.</t>
+the same, and our tongues stuck together, entwined in
+a sticky, wet tangle.</t>
         </is>
       </c>
       <c r="C1732" t="n">
@@ -27001,7 +27020,7 @@
       </c>
       <c r="B1733" s="1" t="inlineStr">
         <is>
-          <t>Ah… it's getting more and more unbearable…！</t>
+          <t>Ah... it's getting harder and harder to resist...!</t>
         </is>
       </c>
       <c r="C1733" t="n">
@@ -27016,9 +27035,9 @@
       </c>
       <c r="B1734" s="1" t="inlineStr">
         <is>
-          <t>The hesitation I felt just moments ago has vanished
-somewhere, and in its place a pure happiness wells
-up.</t>
+          <t>The hesitation I felt just moments ago has
+disappeared, replaced by a pure happiness welling up
+inside me.</t>
         </is>
       </c>
       <c r="C1734" t="n">
@@ -27048,7 +27067,7 @@
       </c>
       <c r="B1736" s="1" t="inlineStr">
         <is>
-          <t>「Chu, chu, rello-rello！」</t>
+          <t>「Chu, chu, rero-rero！」</t>
         </is>
       </c>
       <c r="C1736" t="n">
@@ -27078,8 +27097,8 @@
       </c>
       <c r="B1738" s="1" t="inlineStr">
         <is>
-          <t>「Smack！ Ssmack...~...slrrp！ Nnngh... nhaa！ Fuh,
-faa... nn！」</t>
+          <t>Smooch! Slurp... ~...lick-lick! Mmm... ahh! Fuh,
+faa... nn!</t>
         </is>
       </c>
       <c r="C1738" t="n">
@@ -27109,8 +27128,8 @@
       </c>
       <c r="B1740" s="1" t="inlineStr">
         <is>
-          <t>It felt like she was asking for more, and yet somehow
-like she was saying it's over.</t>
+          <t>It seemed like Rurichiyo-chan was saying "do more,"
+and at the same time like she was saying "it's over."</t>
         </is>
       </c>
       <c r="C1740" t="n">
@@ -27140,8 +27159,8 @@
       </c>
       <c r="B1742" s="1" t="inlineStr">
         <is>
-          <t>But wanting to make sure of Rurichiyo-chan's feelings
-came first, so I pulled my face back for a moment.</t>
+          <t>But my desire to make sure of Rurichiyo-chan's
+feelings came first, so I pulled back for a moment.</t>
         </is>
       </c>
       <c r="C1742" t="n">
@@ -27202,8 +27221,7 @@
       </c>
       <c r="B1746" s="1" t="inlineStr">
         <is>
-          <t>It felt like her mind wasn't here... that's the gist
-of it.</t>
+          <t>Her mind wasn't really there... that's how it felt.</t>
         </is>
       </c>
       <c r="C1746" t="n">
@@ -27233,7 +27251,7 @@
       </c>
       <c r="B1748" s="1" t="inlineStr">
         <is>
-          <t>「............Rurichiyo-chan？」</t>
+          <t>「...Rurichiyo-chan?」</t>
         </is>
       </c>
       <c r="C1748" t="n">
@@ -27263,7 +27281,7 @@
       </c>
       <c r="B1750" s="1" t="inlineStr">
         <is>
-          <t>「............Huh！？」</t>
+          <t>「...Huh!?」</t>
         </is>
       </c>
       <c r="C1750" t="n">
@@ -27278,8 +27296,8 @@
       </c>
       <c r="B1751" s="1" t="inlineStr">
         <is>
-          <t>When I called out, Rurichiyo-chan snapped back to
-herself in an instant and gave a startled look.</t>
+          <t>When I called out, Rurichiyo-chan instantly came to
+her senses and looked startled.</t>
         </is>
       </c>
       <c r="C1751" t="n">
@@ -27309,7 +27327,7 @@
       </c>
       <c r="B1753" s="1" t="inlineStr">
         <is>
-          <t>「Ugh............uu...」</t>
+          <t>「Ugh... uuu...」</t>
         </is>
       </c>
       <c r="C1753" t="n">
@@ -27324,7 +27342,8 @@
       </c>
       <c r="B1754" s="1" t="inlineStr">
         <is>
-          <t>Then she covered her mouth and let her eyes wander.</t>
+          <t>Then Rurichiyo-chan pressed a hand to her mouth and
+her gaze drifted.</t>
         </is>
       </c>
       <c r="C1754" t="n">
@@ -27369,7 +27388,7 @@
       </c>
       <c r="B1757" s="1" t="inlineStr">
         <is>
-          <t>...You don't hate this reaction, right...？</t>
+          <t>She doesn't dislike this reaction, does she...?</t>
         </is>
       </c>
       <c r="C1757" t="n">
@@ -27384,7 +27403,7 @@
       </c>
       <c r="B1758" s="1" t="inlineStr">
         <is>
-          <t>Maybe I can be a little more greedy…？</t>
+          <t>Would it be okay if I got a little greedy...?</t>
         </is>
       </c>
       <c r="C1758" t="n">
@@ -27399,8 +27418,7 @@
       </c>
       <c r="B1759" s="1" t="inlineStr">
         <is>
-          <t>Feeling that way, my heart suddenly started pounding
-harder than ever.</t>
+          <t>When I felt that, my heart belatedly began to race.</t>
         </is>
       </c>
       <c r="C1759" t="n">
@@ -27445,7 +27463,7 @@
       </c>
       <c r="B1762" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-cha……」</t>
+          <t>「Rurichiyo-chan……」</t>
         </is>
       </c>
       <c r="C1762" t="n">
@@ -27475,7 +27493,7 @@
       </c>
       <c r="B1764" s="1" t="inlineStr">
         <is>
-          <t>「That was... an adult kiss, wasn't it...?」</t>
+          <t>That was... an adult kiss, wasn't it...?</t>
         </is>
       </c>
       <c r="C1764" t="n">
@@ -27491,7 +27509,7 @@
       <c r="B1765" s="1" t="inlineStr">
         <is>
           <t>Almost at the same time I called out, Rurichiyo-chan
-spoke.</t>
+also spoke.</t>
         </is>
       </c>
       <c r="C1765" t="n">
@@ -27521,7 +27539,7 @@
       </c>
       <c r="B1767" s="1" t="inlineStr">
         <is>
-          <t>「U-uh...」</t>
+          <t>「Y-yeah...」</t>
         </is>
       </c>
       <c r="C1767" t="n">
@@ -27597,8 +27615,8 @@
       </c>
       <c r="B1772" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan gets excited in a way that's both
-happy and embarrassed.</t>
+          <t>Rurichiyo-chan brightened, looking both pleased and
+embarrassed.</t>
         </is>
       </c>
       <c r="C1772" t="n">
@@ -27644,7 +27662,7 @@
       </c>
       <c r="B1775" s="1" t="inlineStr">
         <is>
-          <t>「Now then...! Shall we go back to everyone?」</t>
+          <t>"Now then...! Shall we head back to the others?"</t>
         </is>
       </c>
       <c r="C1775" t="n">
@@ -27659,8 +27677,7 @@
       </c>
       <c r="B1776" s="1" t="inlineStr">
         <is>
-          <t>While my momentum was dying down, Rurichiyo-chan said
-that to me.</t>
+          <t>While I hesitated, Rurichiyo-chan said that to me.</t>
         </is>
       </c>
       <c r="C1776" t="n">
@@ -27675,9 +27692,9 @@
       </c>
       <c r="B1777" s="1" t="inlineStr">
         <is>
-          <t>Damn... if I'd just kept going quietly a little
-longer, I might've been able to savor that sweet time
-even more...！</t>
+          <t>Ugh... If I'd just stayed quiet and kept going a
+little longer, I might've been able to savor that
+sweet time much, much more...!</t>
         </is>
       </c>
       <c r="C1777" t="n">
@@ -27738,8 +27755,8 @@
       </c>
       <c r="B1781" s="1" t="inlineStr">
         <is>
-          <t>But her right hand and right foot moved forward
-together….</t>
+          <t>But she moved her right hand and right foot forward
+at the same time...</t>
         </is>
       </c>
       <c r="C1781" t="n">
@@ -27799,7 +27816,7 @@
       </c>
       <c r="B1785" s="1" t="inlineStr">
         <is>
-          <t>「Ha… auu！？」</t>
+          <t>「Hah... ah!?」</t>
         </is>
       </c>
       <c r="C1785" t="n">
@@ -27876,8 +27893,8 @@
       </c>
       <c r="B1790" s="1" t="inlineStr">
         <is>
-          <t>「Ah ha, ahaha... I showed you something
-embarrassing... ahaha...」</t>
+          <t>「Aha... ahaha... How embarrassing to have shown you
+that... ahaha...」</t>
         </is>
       </c>
       <c r="C1790" t="n">
@@ -27892,8 +27909,8 @@
       </c>
       <c r="B1791" s="1" t="inlineStr">
         <is>
-          <t>…Rurichiyo-chan says that with a laugh, but her laugh
-plainly gives away how totally flustered she is.</t>
+          <t>…Rurichiyo-chan says so with a laugh, but her
+laughter clearly betrays how flustered she is.</t>
         </is>
       </c>
       <c r="C1791" t="n">
@@ -27908,9 +27925,9 @@
       </c>
       <c r="B1792" s="1" t="inlineStr">
         <is>
-          <t>It's rare for Rurichiyo-chan to get flustered like
-this, but honestly, I'd much rather it than her not
-being flustered at all.</t>
+          <t>It's rare to see Rurichiyo-chan get flustered like
+this, but I'm much happier to see her flustered than
+not.</t>
         </is>
       </c>
       <c r="C1792" t="n">
@@ -27925,8 +27942,8 @@
       </c>
       <c r="B1793" s="1" t="inlineStr">
         <is>
-          <t>Because that 'adult' kiss means she noticed me as a
-guy... right？</t>
+          <t>I mean, that 'adult' kiss meant she saw me as a
+guy... right?</t>
         </is>
       </c>
       <c r="C1793" t="n">
@@ -27987,7 +28004,7 @@
       </c>
       <c r="B1797" s="1" t="inlineStr">
         <is>
-          <t>「So, shall we go？」</t>
+          <t>「Well then, shall we go?」</t>
         </is>
       </c>
       <c r="C1797" t="n">
@@ -28095,8 +28112,8 @@
       </c>
       <c r="B1804" s="1" t="inlineStr">
         <is>
-          <t>...We began to walk, each of us carrying a mutual,
-awkward embarrassment.</t>
+          <t>We started walking, both of us still feeling
+embarrassed.</t>
         </is>
       </c>
       <c r="C1804" t="n">
@@ -28187,8 +28204,8 @@
       </c>
       <c r="B1810" s="1" t="inlineStr">
         <is>
-          <t>Maybe because she's a teacher, she likes being relied
-on.</t>
+          <t>Maybe because she's a sensei, she's happy to be
+relied on.</t>
         </is>
       </c>
       <c r="C1810" t="n">
@@ -28218,7 +28235,7 @@
       </c>
       <c r="B1812" s="1" t="inlineStr">
         <is>
-          <t>「All right, everyone, go ahead and change first.」</t>
+          <t>「All right, everyone, please change first.」</t>
         </is>
       </c>
       <c r="C1812" t="n">
@@ -28248,7 +28265,7 @@
       </c>
       <c r="B1814" s="1" t="inlineStr">
         <is>
-          <t>「Come on, let's go！ Janitor-sensei！」</t>
+          <t>All right, let's go, Janitor-sensei!</t>
         </is>
       </c>
       <c r="C1814" t="n">
@@ -28293,7 +28310,7 @@
       </c>
       <c r="B1817" s="1" t="inlineStr">
         <is>
-          <t>「...Y-yes.」</t>
+          <t>「...Y-yes!」</t>
         </is>
       </c>
       <c r="C1817" t="n">
@@ -28308,8 +28325,8 @@
       </c>
       <c r="B1818" s="1" t="inlineStr">
         <is>
-          <t>Pressed by Nono-chan's enthusiasm, I followed behind
-her, clutching a water gun.</t>
+          <t>Spurred on by Nono-chan's enthusiasm, I followed
+after her, clutching a water gun.</t>
         </is>
       </c>
       <c r="C1818" t="n">
@@ -28339,7 +28356,7 @@
       </c>
       <c r="B1820" s="1" t="inlineStr">
         <is>
-          <t>「Wow, there sure are a lot of things...！」</t>
+          <t>Wow, there sure are a lot of things...！</t>
         </is>
       </c>
       <c r="C1820" t="n">
@@ -28385,8 +28402,8 @@
       </c>
       <c r="B1823" s="1" t="inlineStr">
         <is>
-          <t>「That is... a balance beam, right? I know that！ Ah！
-There are vaulting boxes and hurdles too！」</t>
+          <t>That's... a balance beam, isn't it? I know it! Oh!
+There are vaulting boxes and hurdles, too!</t>
         </is>
       </c>
       <c r="C1823" t="n">
@@ -28401,8 +28418,8 @@
       </c>
       <c r="B1824" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan is a teacher, but she's only just been
-posted here.</t>
+          <t>Nono-chan is a teacher, but she's only been assigned
+here recently.</t>
         </is>
       </c>
       <c r="C1824" t="n">
@@ -28417,8 +28434,8 @@
       </c>
       <c r="B1825" s="1" t="inlineStr">
         <is>
-          <t>It's her first time going into the storage, and it's
-probably the first time she's actually seen the
+          <t>She's never been inside the storage room before, and
+it's probably also her first time actually seeing the
 equipment used in PE.</t>
         </is>
       </c>
@@ -28449,8 +28466,8 @@
       </c>
       <c r="B1827" s="1" t="inlineStr">
         <is>
-          <t>「Hmm-hmm... maybe next time we could do an obstacle
-course race？」</t>
+          <t>“Hmm... maybe next time we could have an obstacle
+race?”</t>
         </is>
       </c>
       <c r="C1827" t="n">
@@ -28495,7 +28512,7 @@
       </c>
       <c r="B1830" s="1" t="inlineStr">
         <is>
-          <t>I hugged the water gun and watched warmly.</t>
+          <t>Still clutching the water gun, I watched warmly.</t>
         </is>
       </c>
       <c r="C1830" t="n">
@@ -28510,7 +28527,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>Then Nono-chan looked back at me and panicked.</t>
+          <t>Then Nono-chan looked back at me, flustered.</t>
         </is>
       </c>
       <c r="C1831" t="n">
@@ -28540,8 +28557,8 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah！ I'm sorry！ My eyes just wandered to
-something else…」</t>
+          <t>「Ah—! I'm sorry! I just got distracted by all the
+other things...」</t>
         </is>
       </c>
       <c r="C1833" t="n">
@@ -28603,9 +28620,9 @@
       </c>
       <c r="B1837" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it she didn't know the Noboribō
-either, so there still seems to be a lot she doesn't
-know in that sense.</t>
+          <t>Come to think of it, Nono-chan didn't know what a
+Noboribō was either, so in that respect there still
+seems to be a lot she doesn't know.</t>
         </is>
       </c>
       <c r="C1837" t="n">
@@ -28697,8 +28714,8 @@
       </c>
       <c r="B1843" s="1" t="inlineStr">
         <is>
-          <t>「Hmm… that water gun is big, so there's no space
-where it fits neatly…」</t>
+          <t>“Hmm... that water gun is big, so there's nowhere for
+it to fit properly...”</t>
         </is>
       </c>
       <c r="C1843" t="n">
@@ -28790,7 +28807,7 @@
       </c>
       <c r="B1849" s="1" t="inlineStr">
         <is>
-          <t>「What should we do？」</t>
+          <t>"What should we do?"</t>
         </is>
       </c>
       <c r="C1849" t="n">
@@ -28805,7 +28822,7 @@
       </c>
       <c r="B1850" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1850" t="n">
@@ -28852,7 +28869,7 @@
       </c>
       <c r="B1853" s="1" t="inlineStr">
         <is>
-          <t>「Oh….」</t>
+          <t>「Oh...」</t>
         </is>
       </c>
       <c r="C1853" t="n">
@@ -28928,7 +28945,7 @@
       </c>
       <c r="B1858" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1858" t="n">
@@ -28943,7 +28960,7 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>「…Heave！」</t>
+          <t>「…Heave!」</t>
         </is>
       </c>
       <c r="C1859" t="n">
@@ -28958,7 +28975,7 @@
       </c>
       <c r="B1860" s="1" t="inlineStr">
         <is>
-          <t>Then, suddenly, she did a somersault on the mat.</t>
+          <t>Then Nono-chan suddenly did a somersault on the mat.</t>
         </is>
       </c>
       <c r="C1860" t="n">
@@ -28988,7 +29005,8 @@
       </c>
       <c r="B1862" s="1" t="inlineStr">
         <is>
-          <t>「Haha, you wanted to try mat exercises？」</t>
+          <t>"Haha, so you wanted to try tumbling on the mat,
+Nono-chan?"</t>
         </is>
       </c>
       <c r="C1862" t="n">
@@ -29018,7 +29036,7 @@
       </c>
       <c r="B1864" s="1" t="inlineStr">
         <is>
-          <t>「S-sorry... I just...」</t>
+          <t>「I-I'm sorry... I couldn't help it...」</t>
         </is>
       </c>
       <c r="C1864" t="n">
@@ -29033,8 +29051,8 @@
       </c>
       <c r="B1865" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan hurriedly stands up and returns an
-embarrassed laugh.</t>
+          <t>Nono-chan hurriedly stood up and gave an embarrassed
+laugh.</t>
         </is>
       </c>
       <c r="C1865" t="n">
@@ -29049,8 +29067,8 @@
       </c>
       <c r="B1866" s="1" t="inlineStr">
         <is>
-          <t>Even though I'm the teacher, that childlike innocence
-is so cute...！</t>
+          <t>She's a sensei, but that childlike innocence is so
+cute...!</t>
         </is>
       </c>
       <c r="C1866" t="n">
@@ -29080,7 +29098,7 @@
       </c>
       <c r="B1868" s="1" t="inlineStr">
         <is>
-          <t>「Wanna do mat exercises together？」</t>
+          <t>"Want to do some mat exercises together?"</t>
         </is>
       </c>
       <c r="C1868" t="n">
@@ -29110,7 +29128,7 @@
       </c>
       <c r="B1870" s="1" t="inlineStr">
         <is>
-          <t>「Oh...！ There's a mat exercise for two people？」</t>
+          <t>「Ooh...! Is there a mat exercise for two people?」</t>
         </is>
       </c>
       <c r="C1870" t="n">
@@ -29140,7 +29158,7 @@
       </c>
       <c r="B1872" s="1" t="inlineStr">
         <is>
-          <t>「No... I was joking...」</t>
+          <t>「No... I'm just joking...」</t>
         </is>
       </c>
       <c r="C1872" t="n">
@@ -29155,8 +29173,9 @@
       </c>
       <c r="B1873" s="1" t="inlineStr">
         <is>
-          <t>Even if I accidentally make a dirty joke, she doesn't
-get it and asks back—it's just even cuter！</t>
+          <t>Even if I accidentally say something dirty, Nono-chan
+doesn't get it and asks about it — it's all the more
+adorable!</t>
         </is>
       </c>
       <c r="C1873" t="n">
@@ -29201,8 +29220,8 @@
       </c>
       <c r="B1876" s="1" t="inlineStr">
         <is>
-          <t>...I move the equipment where Nono-chan said, and in
-the cleared space I place a huge water gun.</t>
+          <t>I rearrange the equipment the way Nono-chan said,
+then place a huge water gun in the space we made.</t>
         </is>
       </c>
       <c r="C1876" t="n">
@@ -29217,7 +29236,7 @@
       </c>
       <c r="B1877" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1877" t="n">
@@ -29232,8 +29251,8 @@
       </c>
       <c r="B1878" s="1" t="inlineStr">
         <is>
-          <t>「Is this okay for now？ We'll arrange things later so
-it fits properly！」</t>
+          <t>Will this do for now? We'll adjust the placement
+later so it fits properly!</t>
         </is>
       </c>
       <c r="C1878" t="n">
@@ -29278,7 +29297,7 @@
       </c>
       <c r="B1881" s="1" t="inlineStr">
         <is>
-          <t>Under Nono-chan's direction, the tidying is finished.</t>
+          <t>With Nono-chan in charge, the cleanup was finished.</t>
         </is>
       </c>
       <c r="C1881" t="n">
@@ -29293,9 +29312,9 @@
       </c>
       <c r="B1882" s="1" t="inlineStr">
         <is>
-          <t>Usually things go sideways or people tease her, but
-when it comes to this kind of coordination, she's
-truly teacher-like.</t>
+          <t>She may fumble and get teased by everyone, but when
+it comes to arranging things like this, she's truly a
+sensei.</t>
         </is>
       </c>
       <c r="C1882" t="n">
@@ -29341,7 +29360,7 @@
       </c>
       <c r="B1885" s="1" t="inlineStr">
         <is>
-          <t>Then, looking over the gear, she gets excited.</t>
+          <t>Then she looks over the equipment and gets excited.</t>
         </is>
       </c>
       <c r="C1885" t="n">
@@ -29356,8 +29375,8 @@
       </c>
       <c r="B1886" s="1" t="inlineStr">
         <is>
-          <t>Well, even at a sports festival, we probably won't
-use half of the stuff here, though.</t>
+          <t>Well, even for a sports festival, we probably won't
+even use half of what's here.</t>
         </is>
       </c>
       <c r="C1886" t="n">
@@ -29372,9 +29391,9 @@
       </c>
       <c r="B1887" s="1" t="inlineStr">
         <is>
-          <t>...But she said she wanted an obstacle race, and
-Nono-chan would probably design a course that uses
-absolutely everything available.</t>
+          <t>...But she said she wanted an obstacle course, and
+Nono-chan would probably come up with a course that
+uses every single piece of equipment here.</t>
         </is>
       </c>
       <c r="C1887" t="n">
@@ -29435,7 +29454,7 @@
       </c>
       <c r="B1891" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ I only said it as a joke...」</t>
+          <t>Huh? I was just joking...</t>
         </is>
       </c>
       <c r="C1891" t="n">
@@ -29482,7 +29501,7 @@
       <c r="B1894" s="1" t="inlineStr">
         <is>
           <t>...Even though I said it was a joke, Nono-chan really
-bit on it, huh.</t>
+took the bait, huh.</t>
         </is>
       </c>
       <c r="C1894" t="n">
@@ -29497,7 +29516,7 @@
       </c>
       <c r="B1895" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C1895" t="n">
@@ -29512,9 +29531,9 @@
       </c>
       <c r="B1896" s="1" t="inlineStr">
         <is>
-          <t>「Actually... I can only do forward rolls and straddle
-forward rolls, so if there's anything I should know,
-I'd like you to tell me！」</t>
+          <t>"Actually... I can only do forward rolls and straddle
+forward rolls, so if there's anything else I should
+be able to do, please teach me!"</t>
         </is>
       </c>
       <c r="C1896" t="n">
@@ -29575,9 +29594,8 @@
       </c>
       <c r="B1900" s="1" t="inlineStr">
         <is>
-          <t>I accidentally blurted it out even though it was
-about nighttime mat exercises... What do I do, how do
-I follow this up?</t>
+          <t>I accidentally blurted it out about the nighttime mat
+exercise... What should I do to cover this?</t>
         </is>
       </c>
       <c r="C1900" t="n">
@@ -29622,7 +29640,7 @@
       </c>
       <c r="B1903" s="1" t="inlineStr">
         <is>
-          <t>You know what — maybe I should tease you a little？</t>
+          <t>That's it — maybe I'll tease her a little?</t>
         </is>
       </c>
       <c r="C1903" t="n">
@@ -29652,8 +29670,7 @@
       </c>
       <c r="B1905" s="1" t="inlineStr">
         <is>
-          <t>「Well then, I'll tell you—just a little, and only to
-you, Sensei.」</t>
+          <t>All right then, Sensei will teach you just a little.</t>
         </is>
       </c>
       <c r="C1905" t="n">
@@ -29683,7 +29700,7 @@
       </c>
       <c r="B1907" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ Nice to meet you！」</t>
+          <t>Yes! Please teach me!</t>
         </is>
       </c>
       <c r="C1907" t="n">
@@ -29698,7 +29715,8 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>When Nono-chan got on, I closed the warehouse door.</t>
+          <t>Once Nono-chan went along with it, I closed the
+warehouse door.</t>
         </is>
       </c>
       <c r="C1908" t="n">
@@ -29728,7 +29746,7 @@
       </c>
       <c r="B1910" s="1" t="inlineStr">
         <is>
-          <t>「J- Janitor-sensei？ Why are you closing the door？」</t>
+          <t>J-Janitor-sensei? Why are you closing the door?</t>
         </is>
       </c>
       <c r="C1910" t="n">
@@ -29818,8 +29836,8 @@
       </c>
       <c r="B1916" s="1" t="inlineStr">
         <is>
-          <t>I say it in as deep a voice as I can manage and bang
-on the mat.</t>
+          <t>I say it in as deep a voice as I can, pounding the
+mat.</t>
         </is>
       </c>
       <c r="C1916" t="n">
@@ -29849,8 +29867,7 @@
       </c>
       <c r="B1918" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei！？ I feel like that's kind of wrong,
-though！？」</t>
+          <t>Janitor-sensei!? That doesn't seem quite right!?</t>
         </is>
       </c>
       <c r="C1918" t="n">
@@ -29880,8 +29897,8 @@
       </c>
       <c r="B1920" s="1" t="inlineStr">
         <is>
-          <t>「No, don't you think if you do a straddle forward
-roll over me you'll understand somehow？」</t>
+          <t>Well... don't you think that if you did a straddle
+forward roll over me, you'd get the idea?</t>
         </is>
       </c>
       <c r="C1920" t="n">
@@ -29926,7 +29943,7 @@
       </c>
       <c r="B1923" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan yells, her face beet-red.</t>
+          <t>Nono-chan yells, her face flushed bright red.</t>
         </is>
       </c>
       <c r="C1923" t="n">
@@ -29971,7 +29988,7 @@
       </c>
       <c r="B1926" s="1" t="inlineStr">
         <is>
-          <t>「Hey, I told you it was a joke, didn't I？」</t>
+          <t>Well, I did say it was a joke, didn't I?</t>
         </is>
       </c>
       <c r="C1926" t="n">
@@ -30001,7 +30018,7 @@
       </c>
       <c r="B1928" s="1" t="inlineStr">
         <is>
-          <t>「Muu, muuuuuuu！」</t>
+          <t>「Mmm... muuuuuuu!」</t>
         </is>
       </c>
       <c r="C1928" t="n">
@@ -30016,8 +30033,9 @@
       </c>
       <c r="B1929" s="1" t="inlineStr">
         <is>
-          <t>Returning to her normal tone and saying it plainly,
-Nono-chan puffed out her cheeks and let out a growl.</t>
+          <t>When I reverted to my usual tone and said it
+offhandedly, Nono-chan puffed out her cheeks and gave
+a disgruntled growl.</t>
         </is>
       </c>
       <c r="C1929" t="n">
@@ -30047,8 +30065,8 @@
       </c>
       <c r="B1931" s="1" t="inlineStr">
         <is>
-          <t>「Y- I think Janitor-sensei is pervy！ That's not
-okay！」</t>
+          <t>「I-I think Janitor-sensei is perverted! That's not
+okay!」</t>
         </is>
       </c>
       <c r="C1931" t="n">
@@ -30123,8 +30141,8 @@
       </c>
       <c r="B1936" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, her puffed-up cheeks flushed red,
-continued to let out muffled groans.</t>
+          <t>Nono-chan, her puffed-out cheeks flushed red,
+continued to let out a muffled groan.</t>
         </is>
       </c>
       <c r="C1936" t="n">
@@ -30262,7 +30280,7 @@
       </c>
       <c r="B1945" s="1" t="inlineStr">
         <is>
-          <t>She was exactly in the position you'd be in right
+          <t>Nono-chan was exactly in the position one takes right
 after finishing a straddle forward roll…</t>
         </is>
       </c>
@@ -30293,7 +30311,7 @@
       </c>
       <c r="B1947" s="1" t="inlineStr">
         <is>
-          <t>「Th-that’s, um, rude to a lady, isn't it！？」</t>
+          <t>「Th-that's rude to a lady, isn't it!?」</t>
         </is>
       </c>
       <c r="C1947" t="n">
@@ -30308,8 +30326,8 @@
       </c>
       <c r="B1948" s="1" t="inlineStr">
         <is>
-          <t>They keep arguing about it like they know what
-they're talking about, but I'm getting dizzy….</t>
+          <t>Nono-chan keeps insisting like that, but I'm getting
+dizzy…</t>
         </is>
       </c>
       <c r="C1948" t="n">
@@ -30324,7 +30342,7 @@
       </c>
       <c r="B1949" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan... I wonder how far she imagined it？</t>
+          <t>Nono-chan... I wonder how far her imagination went.</t>
         </is>
       </c>
       <c r="C1949" t="n">
@@ -30339,8 +30357,8 @@
       </c>
       <c r="B1950" s="1" t="inlineStr">
         <is>
-          <t>...Or rather, Nono-chan's wet, slightly damp body
-feels gently warm.</t>
+          <t>...Actually, Nono-chan's body, damp with moisture, is
+faintly warm.</t>
         </is>
       </c>
       <c r="C1950" t="n">
@@ -30355,7 +30373,8 @@
       </c>
       <c r="B1951" s="1" t="inlineStr">
         <is>
-          <t>I'm getting excited, my body temperature's going up…</t>
+          <t>Nono-chan's getting aroused... her body temperature
+is rising.</t>
         </is>
       </c>
       <c r="C1951" t="n">
@@ -30430,8 +30449,8 @@
       </c>
       <c r="B1956" s="1" t="inlineStr">
         <is>
-          <t>I felt like I was being blamed for getting turned on
-by the little kid's body heat, so I panicked and
+          <t>I felt like I was being blamed for getting aroused by
+Nono-chan's small body heat, so I panicked and
 apologized.</t>
         </is>
       </c>
@@ -30462,7 +30481,7 @@
       </c>
       <c r="B1958" s="1" t="inlineStr">
         <is>
-          <t>「Ah... if you apologized, then that's fine...」</t>
+          <t>「Ah... if you've apologized, then that's fine...」</t>
         </is>
       </c>
       <c r="C1958" t="n">
@@ -30477,7 +30496,7 @@
       </c>
       <c r="B1959" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan suddenly lost her momentum.</t>
+          <t>Nono-chan suddenly deflated.</t>
         </is>
       </c>
       <c r="C1959" t="n">
@@ -30508,9 +30527,9 @@
       </c>
       <c r="B1961" s="1" t="inlineStr">
         <is>
-          <t>Really, I wasn't apologizing for teasing her so much
-as for my own feelings... but I decided not to say
-that.</t>
+          <t>Actually, I wasn't apologizing for teasing her; I was
+apologizing because of my own state of mind... I'll
+keep that to myself.</t>
         </is>
       </c>
       <c r="C1961" t="n">
@@ -30525,7 +30544,7 @@
       </c>
       <c r="B1962" s="1" t="inlineStr">
         <is>
-          <t>More than that, Nono-chan's posture right now is the
+          <t>More importantly, Nono-chan's current position is the
 problem.</t>
         </is>
       </c>
@@ -30541,8 +30560,8 @@
       </c>
       <c r="B1963" s="1" t="inlineStr">
         <is>
-          <t>She's straddling me, legs spread, and her face is
-surprisingly close！</t>
+          <t>Nono-chan straddled me, legs spread, and her face was
+unexpectedly close!</t>
         </is>
       </c>
       <c r="C1963" t="n">
@@ -30557,8 +30576,8 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>I can feel her warmth perfectly... and there's a
-scent too...！</t>
+          <t>I can feel her warmth perfectly... and her scent
+too...!</t>
         </is>
       </c>
       <c r="C1964" t="n">
@@ -30588,8 +30607,7 @@
       </c>
       <c r="B1966" s="1" t="inlineStr">
         <is>
-          <t>「Um... Janitor-sensei？ A-are you reflecting on
-it...？」</t>
+          <t>Um... Janitor-sensei? A-are you reflecting on it...?</t>
         </is>
       </c>
       <c r="C1966" t="n">
@@ -30636,7 +30654,7 @@
       </c>
       <c r="B1969" s="1" t="inlineStr">
         <is>
-          <t>Even though I'm not really mad anymore, I end up
+          <t>Even though she's not really mad anymore, she ends up
 keeping up the angry act — it's hopelessly clumsy.</t>
         </is>
       </c>
@@ -30697,7 +30715,7 @@
       </c>
       <c r="B1973" s="1" t="inlineStr">
         <is>
-          <t>「You're not reflecting at all, are you!？!」</t>
+          <t>「You're not reflecting at all, are you?!」</t>
         </is>
       </c>
       <c r="C1973" t="n">
@@ -30712,8 +30730,8 @@
       </c>
       <c r="B1974" s="1" t="inlineStr">
         <is>
-          <t>I said it in a polite tone, keeping up the teacher
-act, but I guess I couldn't help laughing.</t>
+          <t>I spoke in a polite tone, trying to behave properly
+toward Sensei, but apparently a laugh slipped out.</t>
         </is>
       </c>
       <c r="C1974" t="n">
@@ -30773,7 +30791,7 @@
       </c>
       <c r="B1978" s="1" t="inlineStr">
         <is>
-          <t>「No way！ Janitor-sensei is still teasing me！」</t>
+          <t>That's a lie! Janitor-sensei is still teasing me!</t>
         </is>
       </c>
       <c r="C1978" t="n">
@@ -30788,8 +30806,7 @@
       </c>
       <c r="B1979" s="1" t="inlineStr">
         <is>
-          <t>Maybe my tone was off, because Nono-chan presses the
-point.</t>
+          <t>I must have used the wrong tone — Nono-chan dug in.</t>
         </is>
       </c>
       <c r="C1979" t="n">
@@ -30865,7 +30882,7 @@
       </c>
       <c r="B1984" s="1" t="inlineStr">
         <is>
-          <t>「W-well...」</t>
+          <t>「Th-that's...」</t>
         </is>
       </c>
       <c r="C1984" t="n">
@@ -30880,8 +30897,8 @@
       </c>
       <c r="B1985" s="1" t="inlineStr">
         <is>
-          <t>I deliberately tossed the question at her, and she
-faltered.</t>
+          <t>I deliberately brought it up, and Nono-chan
+hesitated.</t>
         </is>
       </c>
       <c r="C1985" t="n">
@@ -30911,7 +30928,7 @@
       </c>
       <c r="B1987" s="1" t="inlineStr">
         <is>
-          <t>「...Hm？」</t>
+          <t>「...Huh?」</t>
         </is>
       </c>
       <c r="C1987" t="n">
@@ -30926,7 +30943,7 @@
       </c>
       <c r="B1988" s="1" t="inlineStr">
         <is>
-          <t>I tilted my head at her hesitation, watching.</t>
+          <t>I tilted my head at Nono-chan's hesitation.</t>
         </is>
       </c>
       <c r="C1988" t="n">
@@ -30956,7 +30973,7 @@
       </c>
       <c r="B1990" s="1" t="inlineStr">
         <is>
-          <t>「Um, please... look at me properly, as a lady.」</t>
+          <t>「Um... please see me as a proper lady.」</t>
         </is>
       </c>
       <c r="C1990" t="n">
@@ -31016,7 +31033,7 @@
       </c>
       <c r="B1994" s="1" t="inlineStr">
         <is>
-          <t>So that means...？</t>
+          <t>So you're saying...?</t>
         </is>
       </c>
       <c r="C1994" t="n">
@@ -31031,7 +31048,7 @@
       </c>
       <c r="B1995" s="1" t="inlineStr">
         <is>
-          <t>You mean... like this！？</t>
+          <t>So... is it like this!?</t>
         </is>
       </c>
       <c r="C1995" t="n">
@@ -31092,7 +31109,7 @@
       </c>
       <c r="B1999" s="1" t="inlineStr">
         <is>
-          <t>So... is this what you meant！？</t>
+          <t>So... is this okay like this!?</t>
         </is>
       </c>
       <c r="C1999" t="n">
@@ -31152,7 +31169,7 @@
       </c>
       <c r="B2003" s="1" t="inlineStr">
         <is>
-          <t>「...phew...！」</t>
+          <t>「...haa...！」</t>
         </is>
       </c>
       <c r="C2003" t="n">
@@ -31167,7 +31184,7 @@
       </c>
       <c r="B2004" s="1" t="inlineStr">
         <is>
-          <t>I leaned in and stole Nono-chan’s lips.</t>
+          <t>I leaned in and stole a kiss from Nono-chan.</t>
         </is>
       </c>
       <c r="C2004" t="n">
@@ -31182,8 +31199,8 @@
       </c>
       <c r="B2005" s="1" t="inlineStr">
         <is>
-          <t>She seemed flustered just before, but by the time I
-noticed I couldn't hold back.</t>
+          <t>Nono-chan seemed flustered just before, but by the
+time I noticed, I couldn't hold back.</t>
         </is>
       </c>
       <c r="C2005" t="n">
@@ -31213,7 +31230,7 @@
       </c>
       <c r="B2007" s="1" t="inlineStr">
         <is>
-          <t>「Nmp! Nmm, nnh...」</t>
+          <t>「Mmph! Mmm, mmm...」</t>
         </is>
       </c>
       <c r="C2007" t="n">
@@ -31228,7 +31245,8 @@
       </c>
       <c r="B2008" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan presses her lips tight with nerves.</t>
+          <t>Nono-chan nervously presses her lips tightly
+together.</t>
         </is>
       </c>
       <c r="C2008" t="n">
@@ -31259,7 +31277,7 @@
       </c>
       <c r="B2010" s="1" t="inlineStr">
         <is>
-          <t>So this is okay... right？</t>
+          <t>So this was okay...?</t>
         </is>
       </c>
       <c r="C2010" t="n">
@@ -31289,7 +31307,7 @@
       </c>
       <c r="B2012" s="1" t="inlineStr">
         <is>
-          <t>「Mwa... ugh... ah... up！ Puaah！」</t>
+          <t>「Mwa... uuh... ah... up! Puaaah!」</t>
         </is>
       </c>
       <c r="C2012" t="n">
@@ -31320,8 +31338,8 @@
       </c>
       <c r="B2014" s="1" t="inlineStr">
         <is>
-          <t>Since she's in the middle of a kiss, she must be
-mortified.</t>
+          <t>We're in the middle of a kiss, so Nono-chan must be
+embarrassed.</t>
         </is>
       </c>
       <c r="C2014" t="n">
@@ -31382,7 +31400,7 @@
       </c>
       <c r="B2018" s="1" t="inlineStr">
         <is>
-          <t>「Nn, n-ah... ah, huff, fuu... uh, ah... hau... uah,
+          <t>「Nn... n-ah... ah, fuh, fuu... uh, ah... hau... uah,
 aa...」</t>
         </is>
       </c>
@@ -31413,8 +31431,9 @@
       </c>
       <c r="B2020" s="1" t="inlineStr">
         <is>
-          <t>She must be embarrassed and nervous, but she still
-seems to be trying to find a way to breathe.</t>
+          <t>Nono-chan must be embarrassed and nervous, but she
+still seems to be trying to figure out how to breathe
+properly.</t>
         </is>
       </c>
       <c r="C2020" t="n">
@@ -31429,7 +31448,7 @@
       </c>
       <c r="B2021" s="1" t="inlineStr">
         <is>
-          <t>Hmm... just lick her lips.</t>
+          <t>Hmm... go ahead and lick Nono-chan's lips.</t>
         </is>
       </c>
       <c r="C2021" t="n">
@@ -31459,7 +31478,7 @@
       </c>
       <c r="B2023" s="1" t="inlineStr">
         <is>
-          <t>「Fua！？ A-fu, faa... hau, uu...」</t>
+          <t>"Fwah!? Ahh, faa... hau, uuh..."</t>
         </is>
       </c>
       <c r="C2023" t="n">
@@ -31474,8 +31493,8 @@
       </c>
       <c r="B2024" s="1" t="inlineStr">
         <is>
-          <t>When I licked her lips, I could tell Nono-chan got
-even more tense.</t>
+          <t>When I licked her lips, I could tell Nono-chan was
+getting even more nervous.</t>
         </is>
       </c>
       <c r="C2024" t="n">
@@ -31520,7 +31539,7 @@
       </c>
       <c r="B2027" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C2027" t="n">
@@ -31535,7 +31554,7 @@
       </c>
       <c r="B2028" s="1" t="inlineStr">
         <is>
-          <t>「Fah... fai！ Mm, uuu...」</t>
+          <t>「Fah... fai! Mm... uuu...」</t>
         </is>
       </c>
       <c r="C2028" t="n">
@@ -31550,9 +31569,9 @@
       </c>
       <c r="B2029" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan answers dutifully, but thinking about
-something in her head and acting on feeling are two
-different things.</t>
+          <t>Nono-chan answers dutifully, but thinking with her
+head and acting on her feelings are two different
+things.</t>
         </is>
       </c>
       <c r="C2029" t="n">
@@ -31567,8 +31586,8 @@
       </c>
       <c r="B2030" s="1" t="inlineStr">
         <is>
-          <t>Maybe it's better if I say more things to her from my
-side.</t>
+          <t>Then maybe I should just say a few things to
+Nono-chan myself.</t>
         </is>
       </c>
       <c r="C2030" t="n">
@@ -31598,7 +31617,7 @@
       </c>
       <c r="B2032" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan... shall we do a lover's kiss？」</t>
+          <t>「Nono-chan... shall we kiss like lovers?」</t>
         </is>
       </c>
       <c r="C2032" t="n">
@@ -31628,7 +31647,7 @@
       </c>
       <c r="B2034" s="1" t="inlineStr">
         <is>
-          <t>「K-Koi... lover's kiss!？」</t>
+          <t>L-Like a kiss between lovers!?</t>
         </is>
       </c>
       <c r="C2034" t="n">
@@ -31658,7 +31677,7 @@
       </c>
       <c r="B2036" s="1" t="inlineStr">
         <is>
-          <t>「Yes... open your mouth...」</t>
+          <t>「That's it... open your mouth...」</t>
         </is>
       </c>
       <c r="C2036" t="n">
@@ -31688,7 +31707,7 @@
       </c>
       <c r="B2038" s="1" t="inlineStr">
         <is>
-          <t>「Ha, haaaa... amu！？  Ugh, nfu...！」</t>
+          <t>「Ha, haaa... amu!? Uh, nfu...」</t>
         </is>
       </c>
       <c r="C2038" t="n">
@@ -31703,8 +31722,8 @@
       </c>
       <c r="B2039" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, earnest or whatever you want to call it,
-obediently opens her mouth for me.</t>
+          <t>Nono-chan—earnest, or how should I put it—obediently
+opens her mouth for me.</t>
         </is>
       </c>
       <c r="C2039" t="n">
@@ -31750,7 +31769,8 @@
       </c>
       <c r="B2042" s="1" t="inlineStr">
         <is>
-          <t>「Lovers' kisses are, you know, tongues entwining...」</t>
+          <t>A lover's kiss is, you know, when tongues
+intertwine...</t>
         </is>
       </c>
       <c r="C2042" t="n">
@@ -31765,7 +31785,7 @@
       </c>
       <c r="B2043" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C2043" t="n">
@@ -31780,7 +31800,7 @@
       </c>
       <c r="B2044" s="1" t="inlineStr">
         <is>
-          <t>「Fah, faai... amuu... fah, muuu...」</t>
+          <t>「Fah... faii... amuu... fah, muuu...」</t>
         </is>
       </c>
       <c r="C2044" t="n">
@@ -31842,7 +31862,7 @@
       </c>
       <c r="B2048" s="1" t="inlineStr">
         <is>
-          <t>「Rero, reroo...」</t>
+          <t>「Lick, lick...」</t>
         </is>
       </c>
       <c r="C2048" t="n">
@@ -31872,8 +31892,8 @@
       </c>
       <c r="B2050" s="1" t="inlineStr">
         <is>
-          <t>「Fah... ah... rero, rero. Haa... rero, rero...！ Fuu,
-fah...！」</t>
+          <t>Fah... ah... slurp, slurp... Haa... slurp, slurp...!
+Fuu, fah...!</t>
         </is>
       </c>
       <c r="C2050" t="n">
@@ -31918,7 +31938,7 @@
       </c>
       <c r="B2053" s="1" t="inlineStr">
         <is>
-          <t>But her tongue work is clumsy.</t>
+          <t>However, her tongue movements are awkward.</t>
         </is>
       </c>
       <c r="C2053" t="n">
@@ -31933,8 +31953,8 @@
       </c>
       <c r="B2054" s="1" t="inlineStr">
         <is>
-          <t>It's awkward, but my tongue is tangling with
-theirs...！</t>
+          <t>It's clumsy, but our tongues are properly
+intertwined...!</t>
         </is>
       </c>
       <c r="C2054" t="n">
@@ -31964,7 +31984,7 @@
       </c>
       <c r="B2056" s="1" t="inlineStr">
         <is>
-          <t>「...Feels good, doesn't it？ A lover's kiss？」</t>
+          <t>「...Feels good, doesn't it? A lover's kiss?」</t>
         </is>
       </c>
       <c r="C2056" t="n">
@@ -31994,7 +32014,7 @@
       </c>
       <c r="B2058" s="1" t="inlineStr">
         <is>
-          <t>「Fa... fai！ Kimo hi, ii desu...」</t>
+          <t>「Fah... fai! It feels... so good...」</t>
         </is>
       </c>
       <c r="C2058" t="n">
@@ -32055,8 +32075,8 @@
       </c>
       <c r="B2062" s="1" t="inlineStr">
         <is>
-          <t>「Fah... au... rero, rero！ Amu, u...！ Rero, reru！ Amu,
-chup」</t>
+          <t>"Fah... au... lick, lick! Mmm, u...! Lick, lick! Mmm,
+smooch!"</t>
         </is>
       </c>
       <c r="C2062" t="n">
@@ -32071,7 +32091,8 @@
       </c>
       <c r="B2063" s="1" t="inlineStr">
         <is>
-          <t>The way her tongue moves gradually gets better...</t>
+          <t>Nono-chan gradually gets better at moving her
+tongue...</t>
         </is>
       </c>
       <c r="C2063" t="n">
@@ -32086,8 +32107,8 @@
       </c>
       <c r="B2064" s="1" t="inlineStr">
         <is>
-          <t>The tongue’s mucous membrane tangles too, and saliva
-splashes around inside the mouth.</t>
+          <t>The mucous membranes of our tongues also intertwine,
+and saliva splashes around in our mouths.</t>
         </is>
       </c>
       <c r="C2064" t="n">
@@ -32132,7 +32153,7 @@
       </c>
       <c r="B2067" s="1" t="inlineStr">
         <is>
-          <t>「I'll suck your tongue, okay？」</t>
+          <t>Your tongue... I'll suck it, okay?</t>
         </is>
       </c>
       <c r="C2067" t="n">
@@ -32162,7 +32183,7 @@
       </c>
       <c r="B2069" s="1" t="inlineStr">
         <is>
-          <t>「Ha—, y-yes… ah！？ Auu, ugh, nnh！？」</t>
+          <t>「Ha... y-yes... Ah!? Aah... ugh, mmm!?」</t>
         </is>
       </c>
       <c r="C2069" t="n">
@@ -32177,8 +32198,8 @@
       </c>
       <c r="B2070" s="1" t="inlineStr">
         <is>
-          <t>While entwining our tongues and literally sucking,
-Nono-chan's body gave a little shudder.</t>
+          <t>As I entwined my tongue with hers and, true to my
+word, sucked, Nono-chan's body gave a little shudder.</t>
         </is>
       </c>
       <c r="C2070" t="n">
@@ -32223,8 +32244,8 @@
       </c>
       <c r="B2073" s="1" t="inlineStr">
         <is>
-          <t>「nn, muuuh... chu, chub！ kutchu, chu... fumu, nn！
-nna... ah！」</t>
+          <t>Nn... muuu... smooch, chub! Squelch, chu... mmm, nn!
+Nna... ah!</t>
         </is>
       </c>
       <c r="C2073" t="n">
@@ -32254,7 +32275,7 @@
       </c>
       <c r="B2075" s="1" t="inlineStr">
         <is>
-          <t>「Churu... ？」</t>
+          <t>「Slurp...?」</t>
         </is>
       </c>
       <c r="C2075" t="n">
@@ -32269,7 +32290,7 @@
       </c>
       <c r="B2076" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan’s tongue began to move the same way as
+          <t>Nono-chan's tongue also began to move the same way as
 mine.</t>
         </is>
       </c>
@@ -32285,7 +32306,7 @@
       </c>
       <c r="B2077" s="1" t="inlineStr">
         <is>
-          <t>I think she's trying hard, using mine as an example.</t>
+          <t>I think she's trying her best, using mine as a model.</t>
         </is>
       </c>
       <c r="C2077" t="n">
@@ -32315,8 +32336,8 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>「fah, nng... chu, chu！ chub！ fuu！ chuchu, chuk！
-chuba！ fuh！」</t>
+          <t>"Fah... nn... lick, lick! slurp! Fuu! smooch-smooch,
+suck! smack! Fuh!"</t>
         </is>
       </c>
       <c r="C2079" t="n">
@@ -32361,8 +32382,8 @@
       </c>
       <c r="B2082" s="1" t="inlineStr">
         <is>
-          <t>……When our tongues were sucking at each other, just
-kissing alone made me insanely aroused.</t>
+          <t>……When we sucked on each other's tongues, just the
+kiss alone made me overwhelmingly aroused.</t>
         </is>
       </c>
       <c r="C2082" t="n">
@@ -32422,7 +32443,8 @@
       </c>
       <c r="B2086" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help it and automatically pulled a face.</t>
+          <t>I couldn't help it and instinctively drew my face
+back.</t>
         </is>
       </c>
       <c r="C2086" t="n">
@@ -32497,9 +32519,8 @@
       </c>
       <c r="B2091" s="1" t="inlineStr">
         <is>
-          <t>...Once we both pulled our faces away, it became
-suddenly embarrassing and we both turned our heads
-the other way.</t>
+          <t>After I pulled my face away, we suddenly felt
+embarrassed and both looked away.</t>
         </is>
       </c>
       <c r="C2091" t="n">
@@ -32529,9 +32550,8 @@
       </c>
       <c r="B2093" s="1" t="inlineStr">
         <is>
-          <t>I thought I understood those words in my own way, but
-was saying 'a lover's kiss' halfway through taking it
-too far？</t>
+          <t>I thought I'd interpreted those words in my own way,
+but was calling it 'a lover's kiss' overdoing it?</t>
         </is>
       </c>
       <c r="C2093" t="n">
@@ -32562,8 +32582,8 @@
       </c>
       <c r="B2095" s="1" t="inlineStr">
         <is>
-          <t>From how things are now, I'm sure she's conscious of
-it...</t>
+          <t>Judging from how things stand, I'm sure Nono-chan is
+aware of it...</t>
         </is>
       </c>
       <c r="C2095" t="n">
@@ -32578,7 +32598,7 @@
       </c>
       <c r="B2096" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C2096" t="n">
@@ -32638,7 +32658,7 @@
       </c>
       <c r="B2100" s="1" t="inlineStr">
         <is>
-          <t>...Why is that？</t>
+          <t>...Why is that?</t>
         </is>
       </c>
       <c r="C2100" t="n">
@@ -32653,7 +32673,7 @@
       </c>
       <c r="B2101" s="1" t="inlineStr">
         <is>
-          <t>Ugh...asking myself won't get me anywhere.</t>
+          <t>Ugh... asking myself won't get me anywhere.</t>
         </is>
       </c>
       <c r="C2101" t="n">
@@ -32683,7 +32703,7 @@
       </c>
       <c r="B2103" s="1" t="inlineStr">
         <is>
-          <t>「Um...Nono-chan？」</t>
+          <t>「Um... Nono-chan?」</t>
         </is>
       </c>
       <c r="C2103" t="n">
@@ -32713,7 +32733,7 @@
       </c>
       <c r="B2105" s="1" t="inlineStr">
         <is>
-          <t>「Fuh... faaah........」</t>
+          <t>「Fah... faaah........」</t>
         </is>
       </c>
       <c r="C2105" t="n">
@@ -32728,8 +32748,8 @@
       </c>
       <c r="B2106" s="1" t="inlineStr">
         <is>
-          <t>...Looking back at her, Nono had tears gleaming in
-her eyes and her mouth was all slack and melted.</t>
+          <t>When I looked again, Nono-chan's eyes were moist and
+her mouth hung slack, languidly parted.</t>
         </is>
       </c>
       <c r="C2106" t="n">
@@ -32759,7 +32779,8 @@
       </c>
       <c r="B2108" s="1" t="inlineStr">
         <is>
-          <t>Her face all melty after a kiss, so cute...！</t>
+          <t>Nono-chan's face, all melty after that kiss—so
+cute...!</t>
         </is>
       </c>
       <c r="C2108" t="n">
@@ -32789,7 +32810,7 @@
       </c>
       <c r="B2110" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama~？ Nono-sensei~？ Are you there~？」</t>
+          <t>「Oji-sama~? Nono-chan-sensei~? Are you there~?」</t>
         </is>
       </c>
       <c r="C2110" t="n">
@@ -32804,7 +32825,7 @@
       </c>
       <c r="B2111" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C2111" t="n">
@@ -32819,7 +32840,7 @@
       </c>
       <c r="B2112" s="1" t="inlineStr">
         <is>
-          <t>「Huh！？」</t>
+          <t>「Fuu!?」</t>
         </is>
       </c>
       <c r="C2112" t="n">
@@ -32834,8 +32855,8 @@
       </c>
       <c r="B2113" s="1" t="inlineStr">
         <is>
-          <t>...The moment she heard Rurichiyo-chan's voice, Nono
-sprang up like a cat with its fur on end.</t>
+          <t>...The moment she heard Rurichiyo-chan's voice,
+Nono-chan sprang up like a cat with its fur on end.</t>
         </is>
       </c>
       <c r="C2113" t="n">
@@ -32910,8 +32931,8 @@
       </c>
       <c r="B2118" s="1" t="inlineStr">
         <is>
-          <t>「Heave-ho... Oh？ What are you two doing in a place
-like this？」</t>
+          <t>"Phew... Oh? What are you two doing in a place like
+this?"</t>
         </is>
       </c>
       <c r="C2118" t="n">
@@ -32941,8 +32962,8 @@
       </c>
       <c r="B2120" s="1" t="inlineStr">
         <is>
-          <t>「Ah... no, it's nothing, really？ We were just tidying
-up the storage, that's all, okay？」</t>
+          <t>「Ah... no, it's nothing. We were just tidying up the
+storeroom, that's all.」</t>
         </is>
       </c>
       <c r="C2120" t="n">
@@ -32973,9 +32994,9 @@
       </c>
       <c r="B2122" s="1" t="inlineStr">
         <is>
-          <t>But it's truly barely — if someone poked her even a
-little, she'd be ready to let something slip at any
-moment.</t>
+          <t>But she's really just barely holding it together; if
+someone pressed her even a little, she'd immediately
+give herself away.</t>
         </is>
       </c>
       <c r="C2122" t="n">
@@ -33005,7 +33026,8 @@
       </c>
       <c r="B2124" s="1" t="inlineStr">
         <is>
-          <t>「Oh, you must be tired. That was rough, wasn't it？」</t>
+          <t>「Oh? You must be tired. That must have been tough,
+wasn't it？」</t>
         </is>
       </c>
       <c r="C2124" t="n">
@@ -33035,8 +33057,8 @@
       </c>
       <c r="B2126" s="1" t="inlineStr">
         <is>
-          <t>「Y- Janitor-sensei helped me, so I was totally
-fine...！」</t>
+          <t>「Y- Janitor-sensei helped us, so it was no
+problem...！」</t>
         </is>
       </c>
       <c r="C2126" t="n">
@@ -33099,7 +33121,8 @@
       </c>
       <c r="B2130" s="1" t="inlineStr">
         <is>
-          <t>「I see... Oji-sama, you should be tired too.」</t>
+          <t>"I see... Oji-sama, thank you for your hard work as
+well."</t>
         </is>
       </c>
       <c r="C2130" t="n">
@@ -33174,8 +33197,8 @@
       </c>
       <c r="B2135" s="1" t="inlineStr">
         <is>
-          <t>「Oh my... both of your faces are bright red！ You must
-have worked really hard.」</t>
+          <t>"Oh my... you two are both flushed! You must have
+worked very hard."</t>
         </is>
       </c>
       <c r="C2135" t="n">
@@ -33250,7 +33273,7 @@
       </c>
       <c r="B2140" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, what's the matter？ My goodness...！？」</t>
+          <t>"Oh? What's the matter? Oh my...!?"</t>
         </is>
       </c>
       <c r="C2140" t="n">
@@ -33328,7 +33351,8 @@
       </c>
       <c r="B2145" s="1" t="inlineStr">
         <is>
-          <t>...Rurichiyo-chan was, after all, Rurichiyo-chan.</t>
+          <t>...As I thought, Rurichiyo-chan was just
+Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C2145" t="n">
@@ -33405,7 +33429,7 @@
       </c>
       <c r="B2150" s="1" t="inlineStr">
         <is>
-          <t>「Very well, understood！ Now, shall we be off?」</t>
+          <t>Yes, understood! Now, shall we go?</t>
         </is>
       </c>
       <c r="C2150" t="n">
@@ -33450,8 +33474,8 @@
       </c>
       <c r="B2153" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan gave a small nod, and, taking her hand, was
-led out of the warehouse by Rurichiyo-chan.</t>
+          <t>Nono-chan gave a small nod and was led out of the
+warehouse by Rurichiyo-chan, who took her hand.</t>
         </is>
       </c>
       <c r="C2153" t="n">
